--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A64E35F-B635-4703-B0E8-6967583E304C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381E9AF9-95B0-4221-BE18-37EAE4A4CEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -2626,10 +2626,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오늘은 굽거나 찌기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>혼밥도 그릇에 덜어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2867,6 +2863,10 @@
   </si>
   <si>
     <t>주말에도 저녁 제때</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀김 대신 굽거나 찌기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3743,7 +3743,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>817</v>
@@ -3783,7 +3783,7 @@
         <v>34</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F5" s="10" t="s">
         <v>795</v>
@@ -3823,7 +3823,7 @@
         <v>34</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>818</v>
@@ -3863,7 +3863,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>796</v>
@@ -3903,7 +3903,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>797</v>
@@ -3943,7 +3943,7 @@
         <v>30</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>798</v>
@@ -3983,7 +3983,7 @@
         <v>34</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>799</v>
@@ -4063,7 +4063,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>819</v>
@@ -4223,7 +4223,7 @@
         <v>34</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>800</v>
@@ -4303,7 +4303,7 @@
         <v>17</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>820</v>
@@ -4383,7 +4383,7 @@
         <v>30</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>821</v>
@@ -4423,7 +4423,7 @@
         <v>34</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>822</v>
@@ -4463,7 +4463,7 @@
         <v>34</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>801</v>
@@ -4791,7 +4791,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>823</v>
@@ -4999,7 +4999,7 @@
         <v>17</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>802</v>
@@ -5119,7 +5119,7 @@
         <v>34</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>824</v>
@@ -5159,7 +5159,7 @@
         <v>17</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>803</v>
@@ -5199,7 +5199,7 @@
         <v>17</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>825</v>
@@ -5239,7 +5239,7 @@
         <v>30</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>826</v>
@@ -5279,7 +5279,7 @@
         <v>30</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>804</v>
@@ -5653,7 +5653,7 @@
         <v>30</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>827</v>
@@ -5693,7 +5693,7 @@
         <v>34</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>828</v>
@@ -5733,7 +5733,7 @@
         <v>34</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>805</v>
@@ -5893,7 +5893,7 @@
         <v>30</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>806</v>
@@ -5933,7 +5933,7 @@
         <v>34</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>807</v>
@@ -5973,7 +5973,7 @@
         <v>34</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>829</v>
@@ -6253,7 +6253,7 @@
         <v>17</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>830</v>
@@ -6333,7 +6333,7 @@
         <v>30</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>808</v>
@@ -6373,7 +6373,7 @@
         <v>30</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>831</v>
@@ -6781,7 +6781,7 @@
         <v>30</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F79" s="10" t="s">
         <v>809</v>
@@ -6941,7 +6941,7 @@
         <v>17</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>832</v>
@@ -7021,7 +7021,7 @@
         <v>30</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F85" s="10" t="s">
         <v>833</v>
@@ -7061,7 +7061,7 @@
         <v>30</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F86" s="10" t="s">
         <v>810</v>
@@ -7141,7 +7141,7 @@
         <v>34</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F88" s="10" t="s">
         <v>834</v>
@@ -7221,7 +7221,7 @@
         <v>17</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F90" s="10" t="s">
         <v>811</v>
@@ -7621,10 +7621,10 @@
         <v>34</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G100" s="12">
         <v>9</v>
@@ -7821,7 +7821,7 @@
         <v>34</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F105" s="10" t="s">
         <v>835</v>
@@ -8065,7 +8065,7 @@
         <v>34</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F111" s="10" t="s">
         <v>836</v>
@@ -8105,7 +8105,7 @@
         <v>34</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F112" s="10" t="s">
         <v>837</v>
@@ -8145,7 +8145,7 @@
         <v>17</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F113" s="10" t="s">
         <v>838</v>
@@ -8305,7 +8305,7 @@
         <v>34</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F117" s="10" t="s">
         <v>839</v>
@@ -8425,7 +8425,7 @@
         <v>17</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F120" s="10" t="s">
         <v>840</v>
@@ -8465,10 +8465,10 @@
         <v>30</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G121" s="12">
         <v>10</v>
@@ -9069,7 +9069,7 @@
         <v>30</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F136" s="10" t="s">
         <v>812</v>
@@ -9109,7 +9109,7 @@
         <v>30</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F137" s="10" t="s">
         <v>841</v>
@@ -10211,7 +10211,7 @@
         <v>34</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F164" s="10" t="s">
         <v>842</v>
@@ -10251,7 +10251,7 @@
         <v>34</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F165" s="10" t="s">
         <v>813</v>
@@ -10417,13 +10417,13 @@
         <v>34</v>
       </c>
       <c r="E169" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>843</v>
+        <v>903</v>
       </c>
       <c r="G169" s="12">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H169" s="3" t="s">
         <v>635</v>
@@ -10499,7 +10499,7 @@
         <v>17</v>
       </c>
       <c r="E171" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F171" s="10" t="s">
         <v>814</v>
@@ -10539,10 +10539,10 @@
         <v>17</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G172" s="12">
         <v>10</v>
@@ -10619,10 +10619,10 @@
         <v>17</v>
       </c>
       <c r="E174" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G174" s="12">
         <v>11</v>
@@ -10819,7 +10819,7 @@
         <v>30</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F179" s="10" t="s">
         <v>815</v>
@@ -11019,10 +11019,10 @@
         <v>17</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G184" s="12">
         <v>10</v>
@@ -11139,7 +11139,7 @@
         <v>17</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F187" s="10" t="s">
         <v>816</v>
@@ -11350,7 +11350,7 @@
         <v>701</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G192" s="12">
         <v>10</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381E9AF9-95B0-4221-BE18-37EAE4A4CEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1E828D-85EF-418C-A5E5-381091B4870C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2267" uniqueCount="904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="1032">
   <si>
     <t>ID</t>
   </si>
@@ -2366,9 +2366,6 @@
   </si>
   <si>
     <t>maiReport 식이 문구 세트 · 의학 검수 결과</t>
-  </si>
-  <si>
-    <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조.</t>
   </si>
   <si>
     <t>뜻</t>
@@ -2867,6 +2864,394 @@
   </si>
   <si>
     <t>튀김 대신 굽거나 찌기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N192</t>
+  </si>
+  <si>
+    <t>5차</t>
+  </si>
+  <si>
+    <t>먹을 양 먼저 정하기</t>
+  </si>
+  <si>
+    <t>먹기 전에 먹을 양을 정해 두는 행동이에요.</t>
+  </si>
+  <si>
+    <t>MOHW-DIETGUIDE</t>
+  </si>
+  <si>
+    <t>검수 대기</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0239</t>
+  </si>
+  <si>
+    <t>N193</t>
+  </si>
+  <si>
+    <t>꼭꼭 씹어 먹기</t>
+  </si>
+  <si>
+    <t>평소보다 더 씹어 보는 행동이에요.</t>
+  </si>
+  <si>
+    <t>KSSO-OBESITY</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0240</t>
+  </si>
+  <si>
+    <t>N194</t>
+  </si>
+  <si>
+    <t>마가린·쇼트닝 빼기</t>
+  </si>
+  <si>
+    <t>트랜스지방이 많은 기름을 빼는 행동이에요.</t>
+  </si>
+  <si>
+    <t>KSoLA-2022 / WHO-FAT-2023</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0241</t>
+  </si>
+  <si>
+    <t>N195</t>
+  </si>
+  <si>
+    <t>고기 기름 떼고 먹기</t>
+  </si>
+  <si>
+    <t>눈에 보이는 기름을 떼어 내는 행동이에요.</t>
+  </si>
+  <si>
+    <t>KSoLA-2022</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0242</t>
+  </si>
+  <si>
+    <t>N196</t>
+  </si>
+  <si>
+    <t>포화지방 표시 보기</t>
+  </si>
+  <si>
+    <t>제품의 포화지방·트랜스지방 표시를 보는 행동이에요.</t>
+  </si>
+  <si>
+    <t>WHO-FAT-2023 / KSoLA-2022</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0243</t>
+  </si>
+  <si>
+    <t>N197</t>
+  </si>
+  <si>
+    <t>버섯·다시마로 맛내기</t>
+  </si>
+  <si>
+    <t>소금 대신 재료로 맛을 내는 행동이에요.</t>
+  </si>
+  <si>
+    <t>MFDS-SODIUM</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0244</t>
+  </si>
+  <si>
+    <t>N198</t>
+  </si>
+  <si>
+    <t>덜 짠 제품 고르기</t>
+  </si>
+  <si>
+    <t>같은 제품군에서 나트륨이 적은 것을 고르는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0245</t>
+  </si>
+  <si>
+    <t>N199</t>
+  </si>
+  <si>
+    <t>반찬 하나는 콩·두부로</t>
+  </si>
+  <si>
+    <t>반찬 하나를 콩이나 두부로 하는 행동이에요.</t>
+  </si>
+  <si>
+    <t>KDA-2023 / KSH-2022</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0246</t>
+  </si>
+  <si>
+    <t>N200</t>
+  </si>
+  <si>
+    <t>간식도 당류 표시 보기</t>
+  </si>
+  <si>
+    <t>간식의 당류 표시를 보고 고르는 행동이에요.</t>
+  </si>
+  <si>
+    <t>MFDS-SUGAR</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0247</t>
+  </si>
+  <si>
+    <t>N201</t>
+  </si>
+  <si>
+    <t>세 끼 시간 정해 두기</t>
+  </si>
+  <si>
+    <t>끼니 시각을 미리 정해 두는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0248</t>
+  </si>
+  <si>
+    <t>N202</t>
+  </si>
+  <si>
+    <t>아침 시간 정해 두기</t>
+  </si>
+  <si>
+    <t>아침을 먹는 시각을 정해 두는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0249</t>
+  </si>
+  <si>
+    <t>N203</t>
+  </si>
+  <si>
+    <t>야식도 그릇에 덜기</t>
+  </si>
+  <si>
+    <t>봉지째 먹지 않고 그릇에 덜어 먹는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0250</t>
+  </si>
+  <si>
+    <t>N204</t>
+  </si>
+  <si>
+    <t>저녁 후 물 한 잔</t>
+  </si>
+  <si>
+    <t>저녁 뒤에 물을 한 잔 마셔 보는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0251</t>
+  </si>
+  <si>
+    <t>N205</t>
+  </si>
+  <si>
+    <t>반찬은 먹을 만큼만</t>
+  </si>
+  <si>
+    <t>먹을 만큼만 덜어 담는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0252</t>
+  </si>
+  <si>
+    <t>N206</t>
+  </si>
+  <si>
+    <t>버터 대신 올리브유</t>
+  </si>
+  <si>
+    <t>버터 대신 올리브유를 쓰는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0253</t>
+  </si>
+  <si>
+    <t>N207</t>
+  </si>
+  <si>
+    <t>무침은 들기름으로</t>
+  </si>
+  <si>
+    <t>무침에 들기름을 쓰는 행동이에요.</t>
+  </si>
+  <si>
+    <t>WHO-FAT-2023</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0254</t>
+  </si>
+  <si>
+    <t>N208</t>
+  </si>
+  <si>
+    <t>마요 대신 머스터드</t>
+  </si>
+  <si>
+    <t>마요네즈 대신 머스터드를 쓰는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0255</t>
+  </si>
+  <si>
+    <t>N209</t>
+  </si>
+  <si>
+    <t>크림소스 대신 토마토</t>
+  </si>
+  <si>
+    <t>크림소스 대신 토마토소스를 고르는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0256</t>
+  </si>
+  <si>
+    <t>N210</t>
+  </si>
+  <si>
+    <t>닭은 껍질 빼고</t>
+  </si>
+  <si>
+    <t>닭고기의 껍질을 빼고 먹는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0257</t>
+  </si>
+  <si>
+    <t>N211</t>
+  </si>
+  <si>
+    <t>가공육 대신 살코기</t>
+  </si>
+  <si>
+    <t>햄·소시지 대신 살코기를 고르는 행동이에요.</t>
+  </si>
+  <si>
+    <t>WHO-DIET</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0258</t>
+  </si>
+  <si>
+    <t>N212</t>
+  </si>
+  <si>
+    <t>간장 대신 식초·레몬</t>
+  </si>
+  <si>
+    <t>간장 대신 식초나 레몬으로 맛을 내는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0259</t>
+  </si>
+  <si>
+    <t>N213</t>
+  </si>
+  <si>
+    <t>소금 대신 후추·마늘</t>
+  </si>
+  <si>
+    <t>소금 대신 향신료로 맛을 내는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0260</t>
+  </si>
+  <si>
+    <t>N214</t>
+  </si>
+  <si>
+    <t>시럽 대신 계피 가루</t>
+  </si>
+  <si>
+    <t>시럽 대신 계피 가루로 맛을 더하는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0262</t>
+  </si>
+  <si>
+    <t>N215</t>
+  </si>
+  <si>
+    <t>드레싱은 조금만</t>
+  </si>
+  <si>
+    <t>드레싱 양을 줄여 보는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0263</t>
+  </si>
+  <si>
+    <t>N216</t>
+  </si>
+  <si>
+    <t>주말도 아침 챙기기</t>
+  </si>
+  <si>
+    <t>주말에도 아침을 챙기는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0264</t>
+  </si>
+  <si>
+    <t>N217</t>
+  </si>
+  <si>
+    <t>퇴근 후 바로 저녁</t>
+  </si>
+  <si>
+    <t>집에 오면 미루지 않고 저녁을 먹는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0265</t>
+  </si>
+  <si>
+    <t>N218</t>
+  </si>
+  <si>
+    <t>늦은 끼니는 가볍게</t>
+  </si>
+  <si>
+    <t>늦게 먹는 끼니의 양을 줄여 보는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0266</t>
+  </si>
+  <si>
+    <t>N219</t>
+  </si>
+  <si>
+    <t>오징어·새우로 한 끼</t>
+  </si>
+  <si>
+    <t>고기 대신 해산물로 한 끼를 차리는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0267</t>
+  </si>
+  <si>
+    <t>N220</t>
+  </si>
+  <si>
+    <t>생선은 구이로</t>
+  </si>
+  <si>
+    <t>생선을 튀기지 않고 구워 먹는 행동이에요.</t>
+  </si>
+  <si>
+    <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0268</t>
+  </si>
+  <si>
+    <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3435,7 +3820,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
-        <v>773</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3443,13 +3828,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3457,14 +3842,14 @@
         <v>23</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C5" s="5">
         <f>COUNTIF(검수결과!L:L,"승인")</f>
         <v>164</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3472,14 +3857,14 @@
         <v>130</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C6" s="5">
         <f>COUNTIF(검수결과!L:L,"조건부")</f>
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3487,14 +3872,14 @@
         <v>196</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C7" s="5">
         <f>COUNTIF(검수결과!L:L,"수정")</f>
         <v>6</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3502,14 +3887,14 @@
         <v>144</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C8" s="5">
         <f>COUNTIF(검수결과!L:L,"확인 필요")</f>
         <v>2</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3517,14 +3902,14 @@
         <v>124</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C9" s="5">
         <f>COUNTIF(검수결과!L:L,"보류")</f>
         <v>2</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3532,19 +3917,19 @@
         <v>27</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(검수결과!L:L,"삭제")</f>
         <v>5</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="6">
@@ -3555,27 +3940,27 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="7" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="7" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
   </sheetData>
@@ -3586,7 +3971,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEA781C-07E7-4393-BF75-138E1A6EB613}">
-  <dimension ref="A1:N192"/>
+  <dimension ref="A1:N221"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="7.58203125" customWidth="1"/>
@@ -3743,10 +4128,10 @@
         <v>30</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G4" s="12">
         <v>8</v>
@@ -3783,10 +4168,10 @@
         <v>34</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="G5" s="12">
         <v>10</v>
@@ -3823,10 +4208,10 @@
         <v>34</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="G6" s="12">
         <v>11</v>
@@ -3863,10 +4248,10 @@
         <v>17</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="G7" s="12">
         <v>10</v>
@@ -3903,10 +4288,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="G8" s="12">
         <v>11</v>
@@ -3943,10 +4328,10 @@
         <v>30</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G9" s="12">
         <v>12</v>
@@ -3983,10 +4368,10 @@
         <v>34</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="G10" s="1">
         <v>12</v>
@@ -4063,10 +4448,10 @@
         <v>17</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G12" s="12">
         <v>10</v>
@@ -4223,10 +4608,10 @@
         <v>34</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="G16" s="12">
         <v>10</v>
@@ -4303,10 +4688,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G18" s="12">
         <v>9</v>
@@ -4383,10 +4768,10 @@
         <v>30</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G20" s="12">
         <v>11</v>
@@ -4423,10 +4808,10 @@
         <v>34</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G21" s="12">
         <v>10</v>
@@ -4463,10 +4848,10 @@
         <v>34</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G22" s="12">
         <v>8</v>
@@ -4791,10 +5176,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F30" s="10" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G30" s="12">
         <v>9</v>
@@ -4999,10 +5384,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G35" s="12">
         <v>11</v>
@@ -5119,10 +5504,10 @@
         <v>34</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G38" s="12">
         <v>11</v>
@@ -5159,10 +5544,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G39" s="12">
         <v>12</v>
@@ -5199,10 +5584,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G40" s="12">
         <v>9</v>
@@ -5239,10 +5624,10 @@
         <v>30</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G41" s="12">
         <v>7</v>
@@ -5279,10 +5664,10 @@
         <v>30</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G42" s="12">
         <v>12</v>
@@ -5653,10 +6038,10 @@
         <v>30</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G51" s="12">
         <v>9</v>
@@ -5693,10 +6078,10 @@
         <v>34</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G52" s="12">
         <v>11</v>
@@ -5733,10 +6118,10 @@
         <v>34</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G53" s="12">
         <v>11</v>
@@ -5893,10 +6278,10 @@
         <v>30</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F57" s="10" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G57" s="12">
         <v>9</v>
@@ -5933,10 +6318,10 @@
         <v>34</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F58" s="10" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="G58" s="12">
         <v>9</v>
@@ -5973,10 +6358,10 @@
         <v>34</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F59" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G59" s="12">
         <v>11</v>
@@ -6253,10 +6638,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F66" s="10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G66" s="12">
         <v>8</v>
@@ -6333,10 +6718,10 @@
         <v>30</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="F68" s="10" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G68" s="12">
         <v>11</v>
@@ -6373,10 +6758,10 @@
         <v>30</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="G69" s="12">
         <v>9</v>
@@ -6781,10 +7166,10 @@
         <v>30</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="G79" s="12">
         <v>11</v>
@@ -6941,10 +7326,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G83" s="12">
         <v>9</v>
@@ -7021,10 +7406,10 @@
         <v>30</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="G85" s="12">
         <v>10</v>
@@ -7061,10 +7446,10 @@
         <v>30</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="F86" s="10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="G86" s="12">
         <v>11</v>
@@ -7141,10 +7526,10 @@
         <v>34</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="F88" s="10" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G88" s="12">
         <v>11</v>
@@ -7221,10 +7606,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F90" s="10" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="G90" s="12">
         <v>11</v>
@@ -7621,10 +8006,10 @@
         <v>34</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="G100" s="12">
         <v>9</v>
@@ -7821,10 +8206,10 @@
         <v>34</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="F105" s="10" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G105" s="12">
         <v>12</v>
@@ -8065,10 +8450,10 @@
         <v>34</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F111" s="10" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G111" s="12">
         <v>9</v>
@@ -8105,10 +8490,10 @@
         <v>34</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F112" s="10" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G112" s="12">
         <v>11</v>
@@ -8145,10 +8530,10 @@
         <v>17</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F113" s="10" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G113" s="12">
         <v>11</v>
@@ -8305,10 +8690,10 @@
         <v>34</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F117" s="10" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G117" s="12">
         <v>12</v>
@@ -8425,10 +8810,10 @@
         <v>17</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="F120" s="10" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G120" s="12">
         <v>10</v>
@@ -8465,10 +8850,10 @@
         <v>30</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F121" s="10" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="G121" s="12">
         <v>10</v>
@@ -9069,10 +9454,10 @@
         <v>30</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F136" s="10" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G136" s="12">
         <v>8</v>
@@ -9109,10 +9494,10 @@
         <v>30</v>
       </c>
       <c r="E137" s="11" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F137" s="10" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="G137" s="12">
         <v>12</v>
@@ -10211,10 +10596,10 @@
         <v>34</v>
       </c>
       <c r="E164" s="11" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="F164" s="10" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="G164" s="12">
         <v>10</v>
@@ -10251,10 +10636,10 @@
         <v>34</v>
       </c>
       <c r="E165" s="11" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F165" s="10" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="G165" s="12">
         <v>12</v>
@@ -10417,10 +10802,10 @@
         <v>34</v>
       </c>
       <c r="E169" s="11" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F169" s="10" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="G169" s="12">
         <v>12</v>
@@ -10499,10 +10884,10 @@
         <v>17</v>
       </c>
       <c r="E171" s="11" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="F171" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="G171" s="12">
         <v>12</v>
@@ -10539,10 +10924,10 @@
         <v>17</v>
       </c>
       <c r="E172" s="11" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F172" s="10" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="G172" s="12">
         <v>10</v>
@@ -10619,10 +11004,10 @@
         <v>17</v>
       </c>
       <c r="E174" s="11" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="F174" s="10" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="G174" s="12">
         <v>11</v>
@@ -10819,10 +11204,10 @@
         <v>30</v>
       </c>
       <c r="E179" s="11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F179" s="10" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="G179" s="12">
         <v>12</v>
@@ -11019,10 +11404,10 @@
         <v>17</v>
       </c>
       <c r="E184" s="11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F184" s="10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="G184" s="12">
         <v>10</v>
@@ -11139,10 +11524,10 @@
         <v>17</v>
       </c>
       <c r="E187" s="11" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="F187" s="10" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="G187" s="12">
         <v>9</v>
@@ -11350,7 +11735,7 @@
         <v>701</v>
       </c>
       <c r="F192" s="10" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="G192" s="12">
         <v>10</v>
@@ -11375,6 +11760,1195 @@
       </c>
       <c r="N192" s="3" t="s">
         <v>704</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
+      <c r="A193" t="s">
+        <v>903</v>
+      </c>
+      <c r="B193" t="s">
+        <v>904</v>
+      </c>
+      <c r="C193" t="s">
+        <v>134</v>
+      </c>
+      <c r="D193" t="s">
+        <v>30</v>
+      </c>
+      <c r="E193" t="s">
+        <v>905</v>
+      </c>
+      <c r="F193" t="s">
+        <v>905</v>
+      </c>
+      <c r="G193">
+        <v>11</v>
+      </c>
+      <c r="H193" t="s">
+        <v>906</v>
+      </c>
+      <c r="I193" t="s">
+        <v>22</v>
+      </c>
+      <c r="J193" t="s">
+        <v>907</v>
+      </c>
+      <c r="K193" t="s">
+        <v>22</v>
+      </c>
+      <c r="L193" t="s">
+        <v>908</v>
+      </c>
+      <c r="N193" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
+      <c r="A194" t="s">
+        <v>910</v>
+      </c>
+      <c r="B194" t="s">
+        <v>904</v>
+      </c>
+      <c r="C194" t="s">
+        <v>134</v>
+      </c>
+      <c r="D194" t="s">
+        <v>34</v>
+      </c>
+      <c r="E194" t="s">
+        <v>911</v>
+      </c>
+      <c r="F194" t="s">
+        <v>911</v>
+      </c>
+      <c r="G194">
+        <v>8</v>
+      </c>
+      <c r="H194" t="s">
+        <v>912</v>
+      </c>
+      <c r="I194" t="s">
+        <v>22</v>
+      </c>
+      <c r="J194" t="s">
+        <v>913</v>
+      </c>
+      <c r="K194" t="s">
+        <v>22</v>
+      </c>
+      <c r="L194" t="s">
+        <v>908</v>
+      </c>
+      <c r="N194" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14">
+      <c r="A195" t="s">
+        <v>915</v>
+      </c>
+      <c r="B195" t="s">
+        <v>904</v>
+      </c>
+      <c r="C195" t="s">
+        <v>176</v>
+      </c>
+      <c r="D195" t="s">
+        <v>34</v>
+      </c>
+      <c r="E195" t="s">
+        <v>916</v>
+      </c>
+      <c r="F195" t="s">
+        <v>916</v>
+      </c>
+      <c r="G195">
+        <v>10</v>
+      </c>
+      <c r="H195" t="s">
+        <v>917</v>
+      </c>
+      <c r="I195" t="s">
+        <v>22</v>
+      </c>
+      <c r="J195" t="s">
+        <v>918</v>
+      </c>
+      <c r="K195" t="s">
+        <v>22</v>
+      </c>
+      <c r="L195" t="s">
+        <v>908</v>
+      </c>
+      <c r="N195" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14">
+      <c r="A196" t="s">
+        <v>920</v>
+      </c>
+      <c r="B196" t="s">
+        <v>904</v>
+      </c>
+      <c r="C196" t="s">
+        <v>176</v>
+      </c>
+      <c r="D196" t="s">
+        <v>34</v>
+      </c>
+      <c r="E196" t="s">
+        <v>921</v>
+      </c>
+      <c r="F196" t="s">
+        <v>921</v>
+      </c>
+      <c r="G196">
+        <v>11</v>
+      </c>
+      <c r="H196" t="s">
+        <v>922</v>
+      </c>
+      <c r="I196" t="s">
+        <v>22</v>
+      </c>
+      <c r="J196" t="s">
+        <v>923</v>
+      </c>
+      <c r="K196" t="s">
+        <v>22</v>
+      </c>
+      <c r="L196" t="s">
+        <v>908</v>
+      </c>
+      <c r="N196" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14">
+      <c r="A197" t="s">
+        <v>925</v>
+      </c>
+      <c r="B197" t="s">
+        <v>904</v>
+      </c>
+      <c r="C197" t="s">
+        <v>176</v>
+      </c>
+      <c r="D197" t="s">
+        <v>30</v>
+      </c>
+      <c r="E197" t="s">
+        <v>926</v>
+      </c>
+      <c r="F197" t="s">
+        <v>926</v>
+      </c>
+      <c r="G197">
+        <v>10</v>
+      </c>
+      <c r="H197" t="s">
+        <v>927</v>
+      </c>
+      <c r="I197" t="s">
+        <v>22</v>
+      </c>
+      <c r="J197" t="s">
+        <v>928</v>
+      </c>
+      <c r="K197" t="s">
+        <v>22</v>
+      </c>
+      <c r="L197" t="s">
+        <v>908</v>
+      </c>
+      <c r="N197" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14">
+      <c r="A198" t="s">
+        <v>930</v>
+      </c>
+      <c r="B198" t="s">
+        <v>904</v>
+      </c>
+      <c r="C198" t="s">
+        <v>78</v>
+      </c>
+      <c r="D198" t="s">
+        <v>30</v>
+      </c>
+      <c r="E198" t="s">
+        <v>931</v>
+      </c>
+      <c r="F198" t="s">
+        <v>931</v>
+      </c>
+      <c r="G198">
+        <v>11</v>
+      </c>
+      <c r="H198" t="s">
+        <v>932</v>
+      </c>
+      <c r="I198" t="s">
+        <v>22</v>
+      </c>
+      <c r="J198" t="s">
+        <v>933</v>
+      </c>
+      <c r="K198" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" t="s">
+        <v>908</v>
+      </c>
+      <c r="N198" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14">
+      <c r="A199" t="s">
+        <v>935</v>
+      </c>
+      <c r="B199" t="s">
+        <v>904</v>
+      </c>
+      <c r="C199" t="s">
+        <v>78</v>
+      </c>
+      <c r="D199" t="s">
+        <v>30</v>
+      </c>
+      <c r="E199" t="s">
+        <v>936</v>
+      </c>
+      <c r="F199" t="s">
+        <v>936</v>
+      </c>
+      <c r="G199">
+        <v>10</v>
+      </c>
+      <c r="H199" t="s">
+        <v>937</v>
+      </c>
+      <c r="I199" t="s">
+        <v>22</v>
+      </c>
+      <c r="J199" t="s">
+        <v>933</v>
+      </c>
+      <c r="K199" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" t="s">
+        <v>908</v>
+      </c>
+      <c r="N199" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14">
+      <c r="A200" t="s">
+        <v>939</v>
+      </c>
+      <c r="B200" t="s">
+        <v>904</v>
+      </c>
+      <c r="C200" t="s">
+        <v>156</v>
+      </c>
+      <c r="D200" t="s">
+        <v>30</v>
+      </c>
+      <c r="E200" t="s">
+        <v>940</v>
+      </c>
+      <c r="F200" t="s">
+        <v>940</v>
+      </c>
+      <c r="G200">
+        <v>12</v>
+      </c>
+      <c r="H200" t="s">
+        <v>941</v>
+      </c>
+      <c r="I200" t="s">
+        <v>22</v>
+      </c>
+      <c r="J200" t="s">
+        <v>942</v>
+      </c>
+      <c r="K200" t="s">
+        <v>22</v>
+      </c>
+      <c r="L200" t="s">
+        <v>908</v>
+      </c>
+      <c r="N200" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14">
+      <c r="A201" t="s">
+        <v>944</v>
+      </c>
+      <c r="B201" t="s">
+        <v>904</v>
+      </c>
+      <c r="C201" t="s">
+        <v>60</v>
+      </c>
+      <c r="D201" t="s">
+        <v>30</v>
+      </c>
+      <c r="E201" t="s">
+        <v>945</v>
+      </c>
+      <c r="F201" t="s">
+        <v>945</v>
+      </c>
+      <c r="G201">
+        <v>12</v>
+      </c>
+      <c r="H201" t="s">
+        <v>946</v>
+      </c>
+      <c r="I201" t="s">
+        <v>22</v>
+      </c>
+      <c r="J201" t="s">
+        <v>947</v>
+      </c>
+      <c r="K201" t="s">
+        <v>22</v>
+      </c>
+      <c r="L201" t="s">
+        <v>908</v>
+      </c>
+      <c r="N201" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14">
+      <c r="A202" t="s">
+        <v>949</v>
+      </c>
+      <c r="B202" t="s">
+        <v>904</v>
+      </c>
+      <c r="C202" t="s">
+        <v>109</v>
+      </c>
+      <c r="D202" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" t="s">
+        <v>950</v>
+      </c>
+      <c r="F202" t="s">
+        <v>950</v>
+      </c>
+      <c r="G202">
+        <v>12</v>
+      </c>
+      <c r="H202" t="s">
+        <v>951</v>
+      </c>
+      <c r="I202" t="s">
+        <v>22</v>
+      </c>
+      <c r="J202" t="s">
+        <v>913</v>
+      </c>
+      <c r="K202" t="s">
+        <v>22</v>
+      </c>
+      <c r="L202" t="s">
+        <v>908</v>
+      </c>
+      <c r="N202" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14">
+      <c r="A203" t="s">
+        <v>953</v>
+      </c>
+      <c r="B203" t="s">
+        <v>904</v>
+      </c>
+      <c r="C203" t="s">
+        <v>109</v>
+      </c>
+      <c r="D203" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" t="s">
+        <v>954</v>
+      </c>
+      <c r="F203" t="s">
+        <v>954</v>
+      </c>
+      <c r="G203">
+        <v>11</v>
+      </c>
+      <c r="H203" t="s">
+        <v>955</v>
+      </c>
+      <c r="I203" t="s">
+        <v>22</v>
+      </c>
+      <c r="J203" t="s">
+        <v>907</v>
+      </c>
+      <c r="K203" t="s">
+        <v>22</v>
+      </c>
+      <c r="L203" t="s">
+        <v>908</v>
+      </c>
+      <c r="N203" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14">
+      <c r="A204" t="s">
+        <v>957</v>
+      </c>
+      <c r="B204" t="s">
+        <v>904</v>
+      </c>
+      <c r="C204" t="s">
+        <v>109</v>
+      </c>
+      <c r="D204" t="s">
+        <v>30</v>
+      </c>
+      <c r="E204" t="s">
+        <v>958</v>
+      </c>
+      <c r="F204" t="s">
+        <v>958</v>
+      </c>
+      <c r="G204">
+        <v>10</v>
+      </c>
+      <c r="H204" t="s">
+        <v>959</v>
+      </c>
+      <c r="I204" t="s">
+        <v>112</v>
+      </c>
+      <c r="J204" t="s">
+        <v>913</v>
+      </c>
+      <c r="K204" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" t="s">
+        <v>908</v>
+      </c>
+      <c r="N204" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14">
+      <c r="A205" t="s">
+        <v>961</v>
+      </c>
+      <c r="B205" t="s">
+        <v>904</v>
+      </c>
+      <c r="C205" t="s">
+        <v>109</v>
+      </c>
+      <c r="D205" t="s">
+        <v>34</v>
+      </c>
+      <c r="E205" t="s">
+        <v>962</v>
+      </c>
+      <c r="F205" t="s">
+        <v>962</v>
+      </c>
+      <c r="G205">
+        <v>10</v>
+      </c>
+      <c r="H205" t="s">
+        <v>963</v>
+      </c>
+      <c r="I205" t="s">
+        <v>112</v>
+      </c>
+      <c r="J205" t="s">
+        <v>907</v>
+      </c>
+      <c r="K205" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" t="s">
+        <v>908</v>
+      </c>
+      <c r="N205" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14">
+      <c r="A206" t="s">
+        <v>965</v>
+      </c>
+      <c r="B206" t="s">
+        <v>904</v>
+      </c>
+      <c r="C206" t="s">
+        <v>134</v>
+      </c>
+      <c r="D206" t="s">
+        <v>30</v>
+      </c>
+      <c r="E206" t="s">
+        <v>966</v>
+      </c>
+      <c r="F206" t="s">
+        <v>966</v>
+      </c>
+      <c r="G206">
+        <v>10</v>
+      </c>
+      <c r="H206" t="s">
+        <v>967</v>
+      </c>
+      <c r="I206" t="s">
+        <v>22</v>
+      </c>
+      <c r="J206" t="s">
+        <v>907</v>
+      </c>
+      <c r="K206" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" t="s">
+        <v>908</v>
+      </c>
+      <c r="N206" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14">
+      <c r="A207" t="s">
+        <v>969</v>
+      </c>
+      <c r="B207" t="s">
+        <v>904</v>
+      </c>
+      <c r="C207" t="s">
+        <v>176</v>
+      </c>
+      <c r="D207" t="s">
+        <v>34</v>
+      </c>
+      <c r="E207" t="s">
+        <v>970</v>
+      </c>
+      <c r="F207" t="s">
+        <v>970</v>
+      </c>
+      <c r="G207">
+        <v>10</v>
+      </c>
+      <c r="H207" t="s">
+        <v>971</v>
+      </c>
+      <c r="I207" t="s">
+        <v>22</v>
+      </c>
+      <c r="J207" t="s">
+        <v>928</v>
+      </c>
+      <c r="K207" t="s">
+        <v>22</v>
+      </c>
+      <c r="L207" t="s">
+        <v>908</v>
+      </c>
+      <c r="N207" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14">
+      <c r="A208" t="s">
+        <v>973</v>
+      </c>
+      <c r="B208" t="s">
+        <v>904</v>
+      </c>
+      <c r="C208" t="s">
+        <v>176</v>
+      </c>
+      <c r="D208" t="s">
+        <v>30</v>
+      </c>
+      <c r="E208" t="s">
+        <v>974</v>
+      </c>
+      <c r="F208" t="s">
+        <v>974</v>
+      </c>
+      <c r="G208">
+        <v>9</v>
+      </c>
+      <c r="H208" t="s">
+        <v>975</v>
+      </c>
+      <c r="I208" t="s">
+        <v>22</v>
+      </c>
+      <c r="J208" t="s">
+        <v>976</v>
+      </c>
+      <c r="K208" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" t="s">
+        <v>908</v>
+      </c>
+      <c r="N208" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14">
+      <c r="A209" t="s">
+        <v>978</v>
+      </c>
+      <c r="B209" t="s">
+        <v>904</v>
+      </c>
+      <c r="C209" t="s">
+        <v>176</v>
+      </c>
+      <c r="D209" t="s">
+        <v>30</v>
+      </c>
+      <c r="E209" t="s">
+        <v>979</v>
+      </c>
+      <c r="F209" t="s">
+        <v>979</v>
+      </c>
+      <c r="G209">
+        <v>10</v>
+      </c>
+      <c r="H209" t="s">
+        <v>980</v>
+      </c>
+      <c r="I209" t="s">
+        <v>22</v>
+      </c>
+      <c r="J209" t="s">
+        <v>923</v>
+      </c>
+      <c r="K209" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" t="s">
+        <v>908</v>
+      </c>
+      <c r="N209" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14">
+      <c r="A210" t="s">
+        <v>982</v>
+      </c>
+      <c r="B210" t="s">
+        <v>904</v>
+      </c>
+      <c r="C210" t="s">
+        <v>176</v>
+      </c>
+      <c r="D210" t="s">
+        <v>34</v>
+      </c>
+      <c r="E210" t="s">
+        <v>983</v>
+      </c>
+      <c r="F210" t="s">
+        <v>983</v>
+      </c>
+      <c r="G210">
+        <v>11</v>
+      </c>
+      <c r="H210" t="s">
+        <v>984</v>
+      </c>
+      <c r="I210" t="s">
+        <v>22</v>
+      </c>
+      <c r="J210" t="s">
+        <v>923</v>
+      </c>
+      <c r="K210" t="s">
+        <v>22</v>
+      </c>
+      <c r="L210" t="s">
+        <v>908</v>
+      </c>
+      <c r="N210" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14">
+      <c r="A211" t="s">
+        <v>986</v>
+      </c>
+      <c r="B211" t="s">
+        <v>904</v>
+      </c>
+      <c r="C211" t="s">
+        <v>176</v>
+      </c>
+      <c r="D211" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" t="s">
+        <v>987</v>
+      </c>
+      <c r="F211" t="s">
+        <v>987</v>
+      </c>
+      <c r="G211">
+        <v>8</v>
+      </c>
+      <c r="H211" t="s">
+        <v>988</v>
+      </c>
+      <c r="I211" t="s">
+        <v>22</v>
+      </c>
+      <c r="J211" t="s">
+        <v>923</v>
+      </c>
+      <c r="K211" t="s">
+        <v>22</v>
+      </c>
+      <c r="L211" t="s">
+        <v>908</v>
+      </c>
+      <c r="N211" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14">
+      <c r="A212" t="s">
+        <v>990</v>
+      </c>
+      <c r="B212" t="s">
+        <v>904</v>
+      </c>
+      <c r="C212" t="s">
+        <v>156</v>
+      </c>
+      <c r="D212" t="s">
+        <v>30</v>
+      </c>
+      <c r="E212" t="s">
+        <v>991</v>
+      </c>
+      <c r="F212" t="s">
+        <v>991</v>
+      </c>
+      <c r="G212">
+        <v>10</v>
+      </c>
+      <c r="H212" t="s">
+        <v>992</v>
+      </c>
+      <c r="I212" t="s">
+        <v>22</v>
+      </c>
+      <c r="J212" t="s">
+        <v>993</v>
+      </c>
+      <c r="K212" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" t="s">
+        <v>908</v>
+      </c>
+      <c r="N212" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14">
+      <c r="A213" t="s">
+        <v>995</v>
+      </c>
+      <c r="B213" t="s">
+        <v>904</v>
+      </c>
+      <c r="C213" t="s">
+        <v>78</v>
+      </c>
+      <c r="D213" t="s">
+        <v>30</v>
+      </c>
+      <c r="E213" t="s">
+        <v>996</v>
+      </c>
+      <c r="F213" t="s">
+        <v>996</v>
+      </c>
+      <c r="G213">
+        <v>11</v>
+      </c>
+      <c r="H213" t="s">
+        <v>997</v>
+      </c>
+      <c r="I213" t="s">
+        <v>22</v>
+      </c>
+      <c r="J213" t="s">
+        <v>933</v>
+      </c>
+      <c r="K213" t="s">
+        <v>22</v>
+      </c>
+      <c r="L213" t="s">
+        <v>908</v>
+      </c>
+      <c r="N213" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14">
+      <c r="A214" t="s">
+        <v>999</v>
+      </c>
+      <c r="B214" t="s">
+        <v>904</v>
+      </c>
+      <c r="C214" t="s">
+        <v>78</v>
+      </c>
+      <c r="D214" t="s">
+        <v>17</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G214">
+        <v>11</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I214" t="s">
+        <v>22</v>
+      </c>
+      <c r="J214" t="s">
+        <v>933</v>
+      </c>
+      <c r="K214" t="s">
+        <v>22</v>
+      </c>
+      <c r="L214" t="s">
+        <v>908</v>
+      </c>
+      <c r="N214" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14">
+      <c r="A215" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B215" t="s">
+        <v>904</v>
+      </c>
+      <c r="C215" t="s">
+        <v>60</v>
+      </c>
+      <c r="D215" t="s">
+        <v>30</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G215">
+        <v>11</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I215" t="s">
+        <v>22</v>
+      </c>
+      <c r="J215" t="s">
+        <v>947</v>
+      </c>
+      <c r="K215" t="s">
+        <v>22</v>
+      </c>
+      <c r="L215" t="s">
+        <v>908</v>
+      </c>
+      <c r="N215" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14">
+      <c r="A216" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B216" t="s">
+        <v>904</v>
+      </c>
+      <c r="C216" t="s">
+        <v>42</v>
+      </c>
+      <c r="D216" t="s">
+        <v>30</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G216">
+        <v>8</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I216" t="s">
+        <v>22</v>
+      </c>
+      <c r="J216" t="s">
+        <v>923</v>
+      </c>
+      <c r="K216" t="s">
+        <v>22</v>
+      </c>
+      <c r="L216" t="s">
+        <v>908</v>
+      </c>
+      <c r="N216" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14">
+      <c r="A217" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B217" t="s">
+        <v>904</v>
+      </c>
+      <c r="C217" t="s">
+        <v>109</v>
+      </c>
+      <c r="D217" t="s">
+        <v>17</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G217">
+        <v>10</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1013</v>
+      </c>
+      <c r="I217" t="s">
+        <v>22</v>
+      </c>
+      <c r="J217" t="s">
+        <v>907</v>
+      </c>
+      <c r="K217" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" t="s">
+        <v>908</v>
+      </c>
+      <c r="N217" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14">
+      <c r="A218" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B218" t="s">
+        <v>904</v>
+      </c>
+      <c r="C218" t="s">
+        <v>109</v>
+      </c>
+      <c r="D218" t="s">
+        <v>30</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G218">
+        <v>10</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1017</v>
+      </c>
+      <c r="I218" t="s">
+        <v>22</v>
+      </c>
+      <c r="J218" t="s">
+        <v>913</v>
+      </c>
+      <c r="K218" t="s">
+        <v>22</v>
+      </c>
+      <c r="L218" t="s">
+        <v>908</v>
+      </c>
+      <c r="N218" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14">
+      <c r="A219" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B219" t="s">
+        <v>904</v>
+      </c>
+      <c r="C219" t="s">
+        <v>109</v>
+      </c>
+      <c r="D219" t="s">
+        <v>30</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G219">
+        <v>10</v>
+      </c>
+      <c r="H219" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I219" t="s">
+        <v>112</v>
+      </c>
+      <c r="J219" t="s">
+        <v>913</v>
+      </c>
+      <c r="K219" t="s">
+        <v>22</v>
+      </c>
+      <c r="L219" t="s">
+        <v>908</v>
+      </c>
+      <c r="N219" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14">
+      <c r="A220" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B220" t="s">
+        <v>904</v>
+      </c>
+      <c r="C220" t="s">
+        <v>156</v>
+      </c>
+      <c r="D220" t="s">
+        <v>34</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G220">
+        <v>11</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I220" t="s">
+        <v>22</v>
+      </c>
+      <c r="J220" t="s">
+        <v>993</v>
+      </c>
+      <c r="K220" t="s">
+        <v>22</v>
+      </c>
+      <c r="L220" t="s">
+        <v>908</v>
+      </c>
+      <c r="N220" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14">
+      <c r="A221" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B221" t="s">
+        <v>904</v>
+      </c>
+      <c r="C221" t="s">
+        <v>176</v>
+      </c>
+      <c r="D221" t="s">
+        <v>17</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G221">
+        <v>7</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I221" t="s">
+        <v>22</v>
+      </c>
+      <c r="J221" t="s">
+        <v>923</v>
+      </c>
+      <c r="K221" t="s">
+        <v>22</v>
+      </c>
+      <c r="L221" t="s">
+        <v>908</v>
+      </c>
+      <c r="N221" t="s">
+        <v>1030</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1E828D-85EF-418C-A5E5-381091B4870C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA6A1A1-8AB9-4F22-9D3E-6BB959A71B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2615" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="1167">
   <si>
     <t>ID</t>
   </si>
@@ -3253,6 +3253,411 @@
   <si>
     <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>계약서 문구 ID</t>
+  </si>
+  <si>
+    <t>연결 상태</t>
+  </si>
+  <si>
+    <t>DIET-P-0040</t>
+  </si>
+  <si>
+    <t>근거대조서를 거쳐 연결</t>
+  </si>
+  <si>
+    <t>계약서에 없음</t>
+  </si>
+  <si>
+    <t>DIET-P-0041</t>
+  </si>
+  <si>
+    <t>DIET-P-0042</t>
+  </si>
+  <si>
+    <t>문구 그대로</t>
+  </si>
+  <si>
+    <t>DIET-P-0043</t>
+  </si>
+  <si>
+    <t>DIET-P-0044</t>
+  </si>
+  <si>
+    <t>DIET-P-0045</t>
+  </si>
+  <si>
+    <t>DIET-P-0046</t>
+  </si>
+  <si>
+    <t>DIET-P-0047</t>
+  </si>
+  <si>
+    <t>DIET-P-0048</t>
+  </si>
+  <si>
+    <t>DIET-P-0049</t>
+  </si>
+  <si>
+    <t>DIET-P-0050</t>
+  </si>
+  <si>
+    <t>DIET-P-0051</t>
+  </si>
+  <si>
+    <t>DIET-P-0053</t>
+  </si>
+  <si>
+    <t>DIET-P-0054</t>
+  </si>
+  <si>
+    <t>DIET-P-0055</t>
+  </si>
+  <si>
+    <t>DIET-P-0056</t>
+  </si>
+  <si>
+    <t>DIET-P-0057</t>
+  </si>
+  <si>
+    <t>DIET-P-0058</t>
+  </si>
+  <si>
+    <t>DIET-P-0059</t>
+  </si>
+  <si>
+    <t>DIET-P-0066</t>
+  </si>
+  <si>
+    <t>DIET-P-0070</t>
+  </si>
+  <si>
+    <t>DIET-P-0071</t>
+  </si>
+  <si>
+    <t>DIET-P-0072</t>
+  </si>
+  <si>
+    <t>DIET-P-0073</t>
+  </si>
+  <si>
+    <t>DIET-P-0074</t>
+  </si>
+  <si>
+    <t>DIET-P-0075</t>
+  </si>
+  <si>
+    <t>DIET-P-0076</t>
+  </si>
+  <si>
+    <t>DIET-P-0077</t>
+  </si>
+  <si>
+    <t>DIET-P-0078</t>
+  </si>
+  <si>
+    <t>DIET-P-0079</t>
+  </si>
+  <si>
+    <t>DIET-P-0082</t>
+  </si>
+  <si>
+    <t>DIET-P-0083</t>
+  </si>
+  <si>
+    <t>DIET-P-0087</t>
+  </si>
+  <si>
+    <t>DIET-P-0088</t>
+  </si>
+  <si>
+    <t>DIET-P-0089</t>
+  </si>
+  <si>
+    <t>DIET-P-0093</t>
+  </si>
+  <si>
+    <t>DIET-P-0094</t>
+  </si>
+  <si>
+    <t>DIET-P-0095</t>
+  </si>
+  <si>
+    <t>DIET-P-0100</t>
+  </si>
+  <si>
+    <t>DIET-P-0102</t>
+  </si>
+  <si>
+    <t>DIET-P-0103</t>
+  </si>
+  <si>
+    <t>DIET-P-0104</t>
+  </si>
+  <si>
+    <t>DIET-P-0105</t>
+  </si>
+  <si>
+    <t>DIET-P-0107</t>
+  </si>
+  <si>
+    <t>DIET-P-0110</t>
+  </si>
+  <si>
+    <t>DIET-P-0114</t>
+  </si>
+  <si>
+    <t>DIET-P-0115</t>
+  </si>
+  <si>
+    <t>DIET-P-0118</t>
+  </si>
+  <si>
+    <t>DIET-P-0119</t>
+  </si>
+  <si>
+    <t>DIET-P-0121</t>
+  </si>
+  <si>
+    <t>DIET-P-0122</t>
+  </si>
+  <si>
+    <t>DIET-P-0124</t>
+  </si>
+  <si>
+    <t>DIET-P-0126</t>
+  </si>
+  <si>
+    <t>DIET-P-0131</t>
+  </si>
+  <si>
+    <t>DIET-P-0136</t>
+  </si>
+  <si>
+    <t>DIET-P-0139</t>
+  </si>
+  <si>
+    <t>DIET-P-0141</t>
+  </si>
+  <si>
+    <t>DIET-P-0146</t>
+  </si>
+  <si>
+    <t>DIET-P-0147</t>
+  </si>
+  <si>
+    <t>DIET-P-0148</t>
+  </si>
+  <si>
+    <t>DIET-P-0149</t>
+  </si>
+  <si>
+    <t>DIET-P-0150</t>
+  </si>
+  <si>
+    <t>DIET-P-0153</t>
+  </si>
+  <si>
+    <t>DIET-P-0154</t>
+  </si>
+  <si>
+    <t>DIET-P-0156</t>
+  </si>
+  <si>
+    <t>DIET-P-0157</t>
+  </si>
+  <si>
+    <t>DIET-P-0161</t>
+  </si>
+  <si>
+    <t>DIET-P-0165</t>
+  </si>
+  <si>
+    <t>DIET-P-0169</t>
+  </si>
+  <si>
+    <t>DIET-P-0172</t>
+  </si>
+  <si>
+    <t>DIET-P-0173</t>
+  </si>
+  <si>
+    <t>DIET-P-0180</t>
+  </si>
+  <si>
+    <t>DIET-P-0181</t>
+  </si>
+  <si>
+    <t>DIET-P-0182</t>
+  </si>
+  <si>
+    <t>DIET-P-0183</t>
+  </si>
+  <si>
+    <t>DIET-P-0198</t>
+  </si>
+  <si>
+    <t>DIET-P-0199</t>
+  </si>
+  <si>
+    <t>DIET-P-0200</t>
+  </si>
+  <si>
+    <t>DIET-P-0201</t>
+  </si>
+  <si>
+    <t>DIET-P-0202</t>
+  </si>
+  <si>
+    <t>DIET-P-0204</t>
+  </si>
+  <si>
+    <t>DIET-P-0205</t>
+  </si>
+  <si>
+    <t>DIET-P-0206</t>
+  </si>
+  <si>
+    <t>DIET-P-0207</t>
+  </si>
+  <si>
+    <t>DIET-P-0208</t>
+  </si>
+  <si>
+    <t>DIET-P-0209</t>
+  </si>
+  <si>
+    <t>DIET-P-0210</t>
+  </si>
+  <si>
+    <t>DIET-P-0211</t>
+  </si>
+  <si>
+    <t>DIET-P-0212</t>
+  </si>
+  <si>
+    <t>DIET-P-0213</t>
+  </si>
+  <si>
+    <t>DIET-P-0214</t>
+  </si>
+  <si>
+    <t>DIET-P-0215</t>
+  </si>
+  <si>
+    <t>DIET-P-0217</t>
+  </si>
+  <si>
+    <t>DIET-P-0218</t>
+  </si>
+  <si>
+    <t>DIET-P-0219</t>
+  </si>
+  <si>
+    <t>DIET-P-0220</t>
+  </si>
+  <si>
+    <t>DIET-P-0222</t>
+  </si>
+  <si>
+    <t>DIET-P-0224</t>
+  </si>
+  <si>
+    <t>DIET-P-0225</t>
+  </si>
+  <si>
+    <t>DIET-P-0239</t>
+  </si>
+  <si>
+    <t>DIET-P-0240</t>
+  </si>
+  <si>
+    <t>DIET-P-0241</t>
+  </si>
+  <si>
+    <t>DIET-P-0242</t>
+  </si>
+  <si>
+    <t>DIET-P-0243</t>
+  </si>
+  <si>
+    <t>DIET-P-0244</t>
+  </si>
+  <si>
+    <t>DIET-P-0245</t>
+  </si>
+  <si>
+    <t>DIET-P-0246</t>
+  </si>
+  <si>
+    <t>DIET-P-0247</t>
+  </si>
+  <si>
+    <t>DIET-P-0248</t>
+  </si>
+  <si>
+    <t>DIET-P-0249</t>
+  </si>
+  <si>
+    <t>DIET-P-0250</t>
+  </si>
+  <si>
+    <t>DIET-P-0251</t>
+  </si>
+  <si>
+    <t>DIET-P-0252</t>
+  </si>
+  <si>
+    <t>DIET-P-0253</t>
+  </si>
+  <si>
+    <t>DIET-P-0254</t>
+  </si>
+  <si>
+    <t>DIET-P-0255</t>
+  </si>
+  <si>
+    <t>DIET-P-0256</t>
+  </si>
+  <si>
+    <t>DIET-P-0257</t>
+  </si>
+  <si>
+    <t>DIET-P-0258</t>
+  </si>
+  <si>
+    <t>DIET-P-0259</t>
+  </si>
+  <si>
+    <t>DIET-P-0260</t>
+  </si>
+  <si>
+    <t>DIET-P-0262</t>
+  </si>
+  <si>
+    <t>DIET-P-0263</t>
+  </si>
+  <si>
+    <t>DIET-P-0264</t>
+  </si>
+  <si>
+    <t>DIET-P-0265</t>
+  </si>
+  <si>
+    <t>DIET-P-0266</t>
+  </si>
+  <si>
+    <t>DIET-P-0267</t>
+  </si>
+  <si>
+    <t>DIET-P-0268</t>
+  </si>
+  <si>
+    <t>계약서와의 연결</t>
+  </si>
+  <si>
+    <t>검수결과 시트 오른쪽에 「계약서 문구 ID」와 「연결 상태」 두 열을 두었다. 연결 상태가 「계약서에 없음」인 항목은 검수는 했으나 데이터계약 목표문구에 올라가 있지 않은 것이다. 2026-10-06 기준 연결 128 · 없음 92.</t>
   </si>
 </sst>
 </file>
@@ -3804,7 +4209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2597341E-3ECD-41D3-B650-670B60F066B4}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="14.58203125" customWidth="1"/>
@@ -3963,6 +4368,16 @@
         <v>793</v>
       </c>
     </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>1166</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3971,7 +4386,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEA781C-07E7-4393-BF75-138E1A6EB613}">
-  <dimension ref="A1:N221"/>
+  <dimension ref="A1:P221"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="7.58203125" customWidth="1"/>
@@ -3988,7 +4403,7 @@
     <col min="14" max="14" width="62.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:16">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4031,8 +4446,14 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -4071,8 +4492,14 @@
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" ht="64">
+      <c r="O2" t="s">
+        <v>1034</v>
+      </c>
+      <c r="P2" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="64">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -4113,8 +4540,14 @@
       <c r="N3" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
         <v>29</v>
       </c>
@@ -4153,8 +4586,14 @@
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
         <v>33</v>
       </c>
@@ -4193,8 +4632,14 @@
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="P5" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
         <v>37</v>
       </c>
@@ -4233,8 +4678,14 @@
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" t="s">
+        <v>1040</v>
+      </c>
+      <c r="P6" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -4273,8 +4724,14 @@
       </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
       <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
@@ -4313,8 +4770,14 @@
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -4353,8 +4816,14 @@
       </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="P9" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
         <v>52</v>
       </c>
@@ -4393,8 +4862,14 @@
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>1044</v>
+      </c>
+      <c r="P10" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
         <v>55</v>
       </c>
@@ -4433,8 +4908,14 @@
       </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>1045</v>
+      </c>
+      <c r="P11" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -4473,8 +4954,14 @@
       </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" t="s">
+        <v>1046</v>
+      </c>
+      <c r="P12" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
         <v>63</v>
       </c>
@@ -4513,8 +5000,14 @@
       </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" ht="32">
+      <c r="O13" t="s">
+        <v>1047</v>
+      </c>
+      <c r="P13" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="32">
       <c r="A14" s="1" t="s">
         <v>66</v>
       </c>
@@ -4553,8 +5046,14 @@
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P14" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
       <c r="A15" s="1" t="s">
         <v>70</v>
       </c>
@@ -4593,8 +5092,14 @@
       </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>22</v>
+      </c>
+      <c r="P15" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
       <c r="A16" s="1" t="s">
         <v>74</v>
       </c>
@@ -4633,8 +5138,14 @@
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>1049</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
         <v>77</v>
       </c>
@@ -4673,8 +5184,14 @@
       </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17" t="s">
+        <v>1050</v>
+      </c>
+      <c r="P17" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
         <v>82</v>
       </c>
@@ -4713,8 +5230,14 @@
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18" t="s">
+        <v>1051</v>
+      </c>
+      <c r="P18" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
         <v>85</v>
       </c>
@@ -4753,8 +5276,14 @@
       </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" t="s">
+        <v>1052</v>
+      </c>
+      <c r="P19" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
         <v>89</v>
       </c>
@@ -4793,8 +5322,14 @@
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
         <v>91</v>
       </c>
@@ -4833,8 +5368,14 @@
       </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21" t="s">
+        <v>1054</v>
+      </c>
+      <c r="P21" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
         <v>94</v>
       </c>
@@ -4873,8 +5414,14 @@
       </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="1:14" ht="32">
+      <c r="O22" t="s">
+        <v>1055</v>
+      </c>
+      <c r="P22" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" ht="32">
       <c r="A23" s="1" t="s">
         <v>97</v>
       </c>
@@ -4913,8 +5460,14 @@
       </c>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="O23" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="1" t="s">
         <v>103</v>
       </c>
@@ -4953,8 +5506,14 @@
       </c>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" ht="32">
+      <c r="O24" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" ht="32">
       <c r="A25" s="1" t="s">
         <v>108</v>
       </c>
@@ -4995,8 +5554,14 @@
       <c r="N25" s="3" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="1" t="s">
         <v>116</v>
       </c>
@@ -5035,8 +5600,14 @@
       </c>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:14" ht="32">
+      <c r="O26" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="32">
       <c r="A27" s="1" t="s">
         <v>120</v>
       </c>
@@ -5077,8 +5648,14 @@
       <c r="N27" s="3" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" ht="48">
+      <c r="O27" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="48">
       <c r="A28" s="1" t="s">
         <v>126</v>
       </c>
@@ -5121,8 +5698,14 @@
       <c r="N28" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="O28" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
       <c r="A29" s="1" t="s">
         <v>133</v>
       </c>
@@ -5161,8 +5744,14 @@
       </c>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="O29" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
       <c r="A30" s="1" t="s">
         <v>138</v>
       </c>
@@ -5201,8 +5790,14 @@
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="1:14" ht="48">
+      <c r="O30" t="s">
+        <v>1056</v>
+      </c>
+      <c r="P30" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" ht="48">
       <c r="A31" s="1" t="s">
         <v>140</v>
       </c>
@@ -5245,8 +5840,14 @@
       <c r="N31" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="48">
+      <c r="O31" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" ht="48">
       <c r="A32" s="1" t="s">
         <v>147</v>
       </c>
@@ -5289,8 +5890,14 @@
       <c r="N32" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" ht="32">
+      <c r="O32" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="32">
       <c r="A33" s="1" t="s">
         <v>151</v>
       </c>
@@ -5329,8 +5936,14 @@
       </c>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="O33" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="1" t="s">
         <v>155</v>
       </c>
@@ -5369,8 +5982,14 @@
       </c>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="O34" t="s">
+        <v>1057</v>
+      </c>
+      <c r="P34" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="1" t="s">
         <v>161</v>
       </c>
@@ -5409,8 +6028,14 @@
       </c>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="O35" t="s">
+        <v>1058</v>
+      </c>
+      <c r="P35" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="1" t="s">
         <v>164</v>
       </c>
@@ -5449,8 +6074,14 @@
       </c>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="O36" t="s">
+        <v>1059</v>
+      </c>
+      <c r="P36" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
       <c r="A37" s="1" t="s">
         <v>169</v>
       </c>
@@ -5489,8 +6120,14 @@
       </c>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>1060</v>
+      </c>
+      <c r="P37" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" s="1" t="s">
         <v>173</v>
       </c>
@@ -5529,8 +6166,14 @@
       </c>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="O38" t="s">
+        <v>1061</v>
+      </c>
+      <c r="P38" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
       <c r="A39" s="1" t="s">
         <v>175</v>
       </c>
@@ -5569,8 +6212,14 @@
       </c>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="O39" t="s">
+        <v>1062</v>
+      </c>
+      <c r="P39" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" s="1" t="s">
         <v>179</v>
       </c>
@@ -5609,8 +6258,14 @@
       </c>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="O40" t="s">
+        <v>1063</v>
+      </c>
+      <c r="P40" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" s="1" t="s">
         <v>182</v>
       </c>
@@ -5649,8 +6304,14 @@
       </c>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="O41" t="s">
+        <v>1064</v>
+      </c>
+      <c r="P41" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="1" t="s">
         <v>185</v>
       </c>
@@ -5689,8 +6350,14 @@
       </c>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="1:14" ht="32">
+      <c r="O42" t="s">
+        <v>1065</v>
+      </c>
+      <c r="P42" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" ht="32">
       <c r="A43" s="1" t="s">
         <v>188</v>
       </c>
@@ -5729,8 +6396,14 @@
       </c>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="1:14" ht="48">
+      <c r="O43" t="s">
+        <v>1066</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" ht="48">
       <c r="A44" s="1" t="s">
         <v>192</v>
       </c>
@@ -5771,8 +6444,14 @@
       <c r="N44" s="3" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="45" spans="1:14" ht="48">
+      <c r="O44" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" ht="48">
       <c r="A45" s="1" t="s">
         <v>198</v>
       </c>
@@ -5815,8 +6494,14 @@
       <c r="N45" s="3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="46" spans="1:14" ht="32">
+      <c r="O45" t="s">
+        <v>22</v>
+      </c>
+      <c r="P45" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" ht="32">
       <c r="A46" s="1" t="s">
         <v>206</v>
       </c>
@@ -5859,8 +6544,14 @@
       <c r="N46" s="3" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" t="s">
+        <v>1067</v>
+      </c>
+      <c r="P46" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" s="1" t="s">
         <v>214</v>
       </c>
@@ -5899,8 +6590,14 @@
       </c>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" t="s">
+        <v>1068</v>
+      </c>
+      <c r="P47" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="1" t="s">
         <v>220</v>
       </c>
@@ -5939,8 +6636,14 @@
       </c>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="1:14" ht="32">
+      <c r="O48" t="s">
+        <v>22</v>
+      </c>
+      <c r="P48" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="32">
       <c r="A49" s="1" t="s">
         <v>224</v>
       </c>
@@ -5983,8 +6686,14 @@
       <c r="N49" s="3" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" t="s">
+        <v>22</v>
+      </c>
+      <c r="P49" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
       <c r="A50" s="1" t="s">
         <v>228</v>
       </c>
@@ -6023,8 +6732,14 @@
       </c>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" t="s">
+        <v>22</v>
+      </c>
+      <c r="P50" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
       <c r="A51" s="1" t="s">
         <v>232</v>
       </c>
@@ -6063,8 +6778,14 @@
       </c>
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" t="s">
+        <v>1069</v>
+      </c>
+      <c r="P51" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
       <c r="A52" s="1" t="s">
         <v>234</v>
       </c>
@@ -6103,8 +6824,14 @@
       </c>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="O52" t="s">
+        <v>1070</v>
+      </c>
+      <c r="P52" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
       <c r="A53" s="1" t="s">
         <v>237</v>
       </c>
@@ -6143,8 +6870,14 @@
       </c>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="1:14">
+      <c r="O53" t="s">
+        <v>1071</v>
+      </c>
+      <c r="P53" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
       <c r="A54" s="1" t="s">
         <v>240</v>
       </c>
@@ -6183,8 +6916,14 @@
       </c>
       <c r="M54" s="3"/>
       <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" s="1" t="s">
         <v>244</v>
       </c>
@@ -6223,8 +6962,14 @@
       </c>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" s="1" t="s">
         <v>248</v>
       </c>
@@ -6263,8 +7008,14 @@
       </c>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="1:14" ht="32">
+      <c r="O56" t="s">
+        <v>22</v>
+      </c>
+      <c r="P56" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" ht="32">
       <c r="A57" s="1" t="s">
         <v>253</v>
       </c>
@@ -6303,8 +7054,14 @@
       </c>
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="1:14">
+      <c r="O57" t="s">
+        <v>1072</v>
+      </c>
+      <c r="P57" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
       <c r="A58" s="1" t="s">
         <v>255</v>
       </c>
@@ -6343,8 +7100,14 @@
       </c>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="1:14" ht="32">
+      <c r="O58" t="s">
+        <v>1073</v>
+      </c>
+      <c r="P58" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" ht="32">
       <c r="A59" s="1" t="s">
         <v>258</v>
       </c>
@@ -6383,8 +7146,14 @@
       </c>
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="1:14">
+      <c r="O59" t="s">
+        <v>1074</v>
+      </c>
+      <c r="P59" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" s="1" t="s">
         <v>261</v>
       </c>
@@ -6423,8 +7192,14 @@
       </c>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="1:14">
+      <c r="O60" t="s">
+        <v>22</v>
+      </c>
+      <c r="P60" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
       <c r="A61" s="1" t="s">
         <v>264</v>
       </c>
@@ -6463,8 +7238,14 @@
       </c>
       <c r="M61" s="3"/>
       <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="1:14">
+      <c r="O61" t="s">
+        <v>22</v>
+      </c>
+      <c r="P61" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" s="1" t="s">
         <v>268</v>
       </c>
@@ -6503,8 +7284,14 @@
       </c>
       <c r="M62" s="3"/>
       <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="1:14">
+      <c r="O62" t="s">
+        <v>22</v>
+      </c>
+      <c r="P62" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" s="1" t="s">
         <v>271</v>
       </c>
@@ -6543,8 +7330,14 @@
       </c>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="1:14">
+      <c r="O63" t="s">
+        <v>22</v>
+      </c>
+      <c r="P63" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
       <c r="A64" s="1" t="s">
         <v>274</v>
       </c>
@@ -6583,8 +7376,14 @@
       </c>
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="1:14">
+      <c r="O64" t="s">
+        <v>1075</v>
+      </c>
+      <c r="P64" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
       <c r="A65" s="1" t="s">
         <v>277</v>
       </c>
@@ -6623,8 +7422,14 @@
       </c>
       <c r="M65" s="3"/>
       <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="1:14">
+      <c r="O65" t="s">
+        <v>22</v>
+      </c>
+      <c r="P65" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
       <c r="A66" s="1" t="s">
         <v>280</v>
       </c>
@@ -6663,8 +7468,14 @@
       </c>
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="1:14">
+      <c r="O66" t="s">
+        <v>1076</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
       <c r="A67" s="1" t="s">
         <v>282</v>
       </c>
@@ -6703,8 +7514,14 @@
       </c>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="1:14">
+      <c r="O67" t="s">
+        <v>1077</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
       <c r="A68" s="1" t="s">
         <v>286</v>
       </c>
@@ -6743,8 +7560,14 @@
       </c>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="1:14">
+      <c r="O68" t="s">
+        <v>1078</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
       <c r="A69" s="1" t="s">
         <v>289</v>
       </c>
@@ -6783,8 +7606,14 @@
       </c>
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="1:14">
+      <c r="O69" t="s">
+        <v>1079</v>
+      </c>
+      <c r="P69" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
       <c r="A70" s="1" t="s">
         <v>291</v>
       </c>
@@ -6823,8 +7652,14 @@
       </c>
       <c r="M70" s="3"/>
       <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="1:14">
+      <c r="O70" t="s">
+        <v>22</v>
+      </c>
+      <c r="P70" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
       <c r="A71" s="1" t="s">
         <v>294</v>
       </c>
@@ -6863,8 +7698,14 @@
       </c>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="1:14">
+      <c r="O71" t="s">
+        <v>1080</v>
+      </c>
+      <c r="P71" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
       <c r="A72" s="1" t="s">
         <v>298</v>
       </c>
@@ -6903,8 +7744,14 @@
       </c>
       <c r="M72" s="3"/>
       <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="1:14" ht="48">
+      <c r="O72" t="s">
+        <v>22</v>
+      </c>
+      <c r="P72" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="48">
       <c r="A73" s="1" t="s">
         <v>302</v>
       </c>
@@ -6947,8 +7794,14 @@
       <c r="N73" s="3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="74" spans="1:14">
+      <c r="O73" t="s">
+        <v>22</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
       <c r="A74" s="1" t="s">
         <v>306</v>
       </c>
@@ -6987,8 +7840,14 @@
       </c>
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="1:14">
+      <c r="O74" t="s">
+        <v>1081</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
       <c r="A75" s="1" t="s">
         <v>309</v>
       </c>
@@ -7027,8 +7886,14 @@
       </c>
       <c r="M75" s="3"/>
       <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="1:14" ht="48">
+      <c r="O75" t="s">
+        <v>22</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" ht="48">
       <c r="A76" s="1" t="s">
         <v>313</v>
       </c>
@@ -7071,8 +7936,14 @@
       <c r="N76" s="3" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="77" spans="1:14">
+      <c r="O76" t="s">
+        <v>22</v>
+      </c>
+      <c r="P76" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
       <c r="A77" s="1" t="s">
         <v>317</v>
       </c>
@@ -7111,8 +7982,14 @@
       </c>
       <c r="M77" s="3"/>
       <c r="N77" s="3"/>
-    </row>
-    <row r="78" spans="1:14">
+      <c r="O77" t="s">
+        <v>22</v>
+      </c>
+      <c r="P77" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
       <c r="A78" s="1" t="s">
         <v>320</v>
       </c>
@@ -7151,8 +8028,14 @@
       </c>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
-    </row>
-    <row r="79" spans="1:14">
+      <c r="O78" t="s">
+        <v>1082</v>
+      </c>
+      <c r="P78" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
       <c r="A79" s="1" t="s">
         <v>323</v>
       </c>
@@ -7191,8 +8074,14 @@
       </c>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
-    </row>
-    <row r="80" spans="1:14">
+      <c r="O79" t="s">
+        <v>1083</v>
+      </c>
+      <c r="P79" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
       <c r="A80" s="1" t="s">
         <v>326</v>
       </c>
@@ -7231,8 +8120,14 @@
       </c>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
-    </row>
-    <row r="81" spans="1:14">
+      <c r="O80" t="s">
+        <v>22</v>
+      </c>
+      <c r="P80" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
       <c r="A81" s="1" t="s">
         <v>329</v>
       </c>
@@ -7271,8 +8166,14 @@
       </c>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="1:14" ht="32">
+      <c r="O81" t="s">
+        <v>22</v>
+      </c>
+      <c r="P81" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="32">
       <c r="A82" s="1" t="s">
         <v>333</v>
       </c>
@@ -7311,8 +8212,14 @@
       </c>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="1:14">
+      <c r="O82" t="s">
+        <v>1084</v>
+      </c>
+      <c r="P82" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
       <c r="A83" s="1" t="s">
         <v>337</v>
       </c>
@@ -7351,8 +8258,14 @@
       </c>
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="1:14">
+      <c r="O83" t="s">
+        <v>1085</v>
+      </c>
+      <c r="P83" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
       <c r="A84" s="1" t="s">
         <v>340</v>
       </c>
@@ -7391,8 +8304,14 @@
       </c>
       <c r="M84" s="3"/>
       <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="1:14" ht="32">
+      <c r="O84" t="s">
+        <v>22</v>
+      </c>
+      <c r="P84" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="32">
       <c r="A85" s="1" t="s">
         <v>343</v>
       </c>
@@ -7431,8 +8350,14 @@
       </c>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="1:14">
+      <c r="O85" t="s">
+        <v>1086</v>
+      </c>
+      <c r="P85" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
       <c r="A86" s="1" t="s">
         <v>346</v>
       </c>
@@ -7471,8 +8396,14 @@
       </c>
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="1:14">
+      <c r="O86" t="s">
+        <v>1087</v>
+      </c>
+      <c r="P86" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
       <c r="A87" s="1" t="s">
         <v>349</v>
       </c>
@@ -7511,8 +8442,14 @@
       </c>
       <c r="M87" s="3"/>
       <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="1:14">
+      <c r="O87" t="s">
+        <v>22</v>
+      </c>
+      <c r="P87" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
       <c r="A88" s="1" t="s">
         <v>353</v>
       </c>
@@ -7551,8 +8488,14 @@
       </c>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="1:14">
+      <c r="O88" t="s">
+        <v>1088</v>
+      </c>
+      <c r="P88" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
       <c r="A89" s="1" t="s">
         <v>356</v>
       </c>
@@ -7591,8 +8534,14 @@
       </c>
       <c r="M89" s="3"/>
       <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="1:14">
+      <c r="O89" t="s">
+        <v>22</v>
+      </c>
+      <c r="P89" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
       <c r="A90" s="1" t="s">
         <v>359</v>
       </c>
@@ -7631,8 +8580,14 @@
       </c>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="1:14">
+      <c r="O90" t="s">
+        <v>1089</v>
+      </c>
+      <c r="P90" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
       <c r="A91" s="1" t="s">
         <v>362</v>
       </c>
@@ -7671,8 +8626,14 @@
       </c>
       <c r="M91" s="3"/>
       <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="1:14">
+      <c r="O91" t="s">
+        <v>22</v>
+      </c>
+      <c r="P91" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
       <c r="A92" s="1" t="s">
         <v>365</v>
       </c>
@@ -7711,8 +8672,14 @@
       </c>
       <c r="M92" s="3"/>
       <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="1:14">
+      <c r="O92" t="s">
+        <v>22</v>
+      </c>
+      <c r="P92" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
       <c r="A93" s="1" t="s">
         <v>368</v>
       </c>
@@ -7751,8 +8718,14 @@
       </c>
       <c r="M93" s="3"/>
       <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="1:14">
+      <c r="O93" t="s">
+        <v>22</v>
+      </c>
+      <c r="P93" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
       <c r="A94" s="1" t="s">
         <v>372</v>
       </c>
@@ -7791,8 +8764,14 @@
       </c>
       <c r="M94" s="3"/>
       <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="1:14">
+      <c r="O94" t="s">
+        <v>22</v>
+      </c>
+      <c r="P94" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
       <c r="A95" s="1" t="s">
         <v>376</v>
       </c>
@@ -7831,8 +8810,14 @@
       </c>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="1:14">
+      <c r="O95" t="s">
+        <v>1090</v>
+      </c>
+      <c r="P95" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
       <c r="A96" s="1" t="s">
         <v>380</v>
       </c>
@@ -7871,8 +8856,14 @@
       </c>
       <c r="M96" s="3"/>
       <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="1:14">
+      <c r="O96" t="s">
+        <v>22</v>
+      </c>
+      <c r="P96" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
       <c r="A97" s="1" t="s">
         <v>384</v>
       </c>
@@ -7911,8 +8902,14 @@
       </c>
       <c r="M97" s="3"/>
       <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="1:14">
+      <c r="O97" t="s">
+        <v>22</v>
+      </c>
+      <c r="P97" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
       <c r="A98" s="1" t="s">
         <v>388</v>
       </c>
@@ -7951,8 +8948,14 @@
       </c>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="1:14">
+      <c r="O98" t="s">
+        <v>22</v>
+      </c>
+      <c r="P98" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
       <c r="A99" s="1" t="s">
         <v>392</v>
       </c>
@@ -7991,8 +8994,14 @@
       </c>
       <c r="M99" s="3"/>
       <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="1:14">
+      <c r="O99" t="s">
+        <v>22</v>
+      </c>
+      <c r="P99" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
       <c r="A100" s="1" t="s">
         <v>396</v>
       </c>
@@ -8031,8 +9040,14 @@
       </c>
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="1:14">
+      <c r="O100" t="s">
+        <v>1091</v>
+      </c>
+      <c r="P100" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
       <c r="A101" s="1" t="s">
         <v>399</v>
       </c>
@@ -8071,8 +9086,14 @@
       </c>
       <c r="M101" s="3"/>
       <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="1:14">
+      <c r="O101" t="s">
+        <v>22</v>
+      </c>
+      <c r="P101" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
       <c r="A102" s="1" t="s">
         <v>403</v>
       </c>
@@ -8111,8 +9132,14 @@
       </c>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
-    </row>
-    <row r="103" spans="1:14">
+      <c r="O102" t="s">
+        <v>22</v>
+      </c>
+      <c r="P102" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
       <c r="A103" s="1" t="s">
         <v>406</v>
       </c>
@@ -8151,8 +9178,14 @@
       </c>
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
-    </row>
-    <row r="104" spans="1:14">
+      <c r="O103" t="s">
+        <v>1092</v>
+      </c>
+      <c r="P103" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
       <c r="A104" s="1" t="s">
         <v>409</v>
       </c>
@@ -8191,8 +9224,14 @@
       </c>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
-    </row>
-    <row r="105" spans="1:14">
+      <c r="O104" t="s">
+        <v>22</v>
+      </c>
+      <c r="P104" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
       <c r="A105" s="1" t="s">
         <v>413</v>
       </c>
@@ -8231,8 +9270,14 @@
       </c>
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
-    </row>
-    <row r="106" spans="1:14">
+      <c r="O105" t="s">
+        <v>1093</v>
+      </c>
+      <c r="P105" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
       <c r="A106" s="1" t="s">
         <v>416</v>
       </c>
@@ -8271,8 +9316,14 @@
       </c>
       <c r="M106" s="3"/>
       <c r="N106" s="3"/>
-    </row>
-    <row r="107" spans="1:14" ht="48">
+      <c r="O106" t="s">
+        <v>22</v>
+      </c>
+      <c r="P106" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" ht="48">
       <c r="A107" s="1" t="s">
         <v>419</v>
       </c>
@@ -8315,8 +9366,14 @@
       <c r="N107" s="3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="108" spans="1:14">
+      <c r="O107" t="s">
+        <v>22</v>
+      </c>
+      <c r="P107" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
       <c r="A108" s="1" t="s">
         <v>423</v>
       </c>
@@ -8355,8 +9412,14 @@
       </c>
       <c r="M108" s="3"/>
       <c r="N108" s="3"/>
-    </row>
-    <row r="109" spans="1:14">
+      <c r="O108" t="s">
+        <v>22</v>
+      </c>
+      <c r="P108" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
       <c r="A109" s="1" t="s">
         <v>426</v>
       </c>
@@ -8395,8 +9458,14 @@
       </c>
       <c r="M109" s="3"/>
       <c r="N109" s="3"/>
-    </row>
-    <row r="110" spans="1:14">
+      <c r="O109" t="s">
+        <v>22</v>
+      </c>
+      <c r="P109" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
       <c r="A110" s="1" t="s">
         <v>429</v>
       </c>
@@ -8435,8 +9504,14 @@
       </c>
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
-    </row>
-    <row r="111" spans="1:14">
+      <c r="O110" t="s">
+        <v>1094</v>
+      </c>
+      <c r="P110" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
       <c r="A111" s="1" t="s">
         <v>433</v>
       </c>
@@ -8475,8 +9550,14 @@
       </c>
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
-    </row>
-    <row r="112" spans="1:14">
+      <c r="O111" t="s">
+        <v>1095</v>
+      </c>
+      <c r="P111" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
       <c r="A112" s="1" t="s">
         <v>435</v>
       </c>
@@ -8515,8 +9596,14 @@
       </c>
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
-    </row>
-    <row r="113" spans="1:14">
+      <c r="O112" t="s">
+        <v>1096</v>
+      </c>
+      <c r="P112" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
       <c r="A113" s="1" t="s">
         <v>438</v>
       </c>
@@ -8555,8 +9642,14 @@
       </c>
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
-    </row>
-    <row r="114" spans="1:14">
+      <c r="O113" t="s">
+        <v>1097</v>
+      </c>
+      <c r="P113" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
       <c r="A114" s="1" t="s">
         <v>440</v>
       </c>
@@ -8595,8 +9688,14 @@
       </c>
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
-    </row>
-    <row r="115" spans="1:14">
+      <c r="O114" t="s">
+        <v>1098</v>
+      </c>
+      <c r="P114" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
       <c r="A115" s="1" t="s">
         <v>444</v>
       </c>
@@ -8635,8 +9734,14 @@
       </c>
       <c r="M115" s="3"/>
       <c r="N115" s="3"/>
-    </row>
-    <row r="116" spans="1:14">
+      <c r="O115" t="s">
+        <v>22</v>
+      </c>
+      <c r="P115" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
       <c r="A116" s="1" t="s">
         <v>447</v>
       </c>
@@ -8675,8 +9780,14 @@
       </c>
       <c r="M116" s="3"/>
       <c r="N116" s="3"/>
-    </row>
-    <row r="117" spans="1:14">
+      <c r="O116" t="s">
+        <v>22</v>
+      </c>
+      <c r="P116" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
       <c r="A117" s="1" t="s">
         <v>451</v>
       </c>
@@ -8715,8 +9826,14 @@
       </c>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
-    </row>
-    <row r="118" spans="1:14">
+      <c r="O117" t="s">
+        <v>1099</v>
+      </c>
+      <c r="P117" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
       <c r="A118" s="1" t="s">
         <v>454</v>
       </c>
@@ -8755,8 +9872,14 @@
       </c>
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
-    </row>
-    <row r="119" spans="1:14">
+      <c r="O118" t="s">
+        <v>1100</v>
+      </c>
+      <c r="P118" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
       <c r="A119" s="1" t="s">
         <v>457</v>
       </c>
@@ -8795,8 +9918,14 @@
       </c>
       <c r="M119" s="3"/>
       <c r="N119" s="3"/>
-    </row>
-    <row r="120" spans="1:14">
+      <c r="O119" t="s">
+        <v>22</v>
+      </c>
+      <c r="P119" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
       <c r="A120" s="1" t="s">
         <v>460</v>
       </c>
@@ -8835,8 +9964,14 @@
       </c>
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
-    </row>
-    <row r="121" spans="1:14">
+      <c r="O120" t="s">
+        <v>1101</v>
+      </c>
+      <c r="P120" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
       <c r="A121" s="1" t="s">
         <v>462</v>
       </c>
@@ -8875,8 +10010,14 @@
       </c>
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
-    </row>
-    <row r="122" spans="1:14">
+      <c r="O121" t="s">
+        <v>1102</v>
+      </c>
+      <c r="P121" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
       <c r="A122" s="1" t="s">
         <v>465</v>
       </c>
@@ -8915,8 +10056,14 @@
       </c>
       <c r="M122" s="3"/>
       <c r="N122" s="3"/>
-    </row>
-    <row r="123" spans="1:14">
+      <c r="O122" t="s">
+        <v>22</v>
+      </c>
+      <c r="P122" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
       <c r="A123" s="1" t="s">
         <v>468</v>
       </c>
@@ -8955,8 +10102,14 @@
       </c>
       <c r="M123" s="3"/>
       <c r="N123" s="3"/>
-    </row>
-    <row r="124" spans="1:14">
+      <c r="O123" t="s">
+        <v>22</v>
+      </c>
+      <c r="P123" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
       <c r="A124" s="1" t="s">
         <v>472</v>
       </c>
@@ -8995,8 +10148,14 @@
       </c>
       <c r="M124" s="3"/>
       <c r="N124" s="3"/>
-    </row>
-    <row r="125" spans="1:14">
+      <c r="O124" t="s">
+        <v>22</v>
+      </c>
+      <c r="P124" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
       <c r="A125" s="1" t="s">
         <v>475</v>
       </c>
@@ -9035,8 +10194,14 @@
       </c>
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
-    </row>
-    <row r="126" spans="1:14">
+      <c r="O125" t="s">
+        <v>1103</v>
+      </c>
+      <c r="P125" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
       <c r="A126" s="1" t="s">
         <v>479</v>
       </c>
@@ -9075,8 +10240,14 @@
       </c>
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
-    </row>
-    <row r="127" spans="1:14">
+      <c r="O126" t="s">
+        <v>22</v>
+      </c>
+      <c r="P126" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
       <c r="A127" s="1" t="s">
         <v>482</v>
       </c>
@@ -9115,8 +10286,14 @@
       </c>
       <c r="M127" s="3"/>
       <c r="N127" s="3"/>
-    </row>
-    <row r="128" spans="1:14">
+      <c r="O127" t="s">
+        <v>22</v>
+      </c>
+      <c r="P127" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
       <c r="A128" s="1" t="s">
         <v>485</v>
       </c>
@@ -9155,8 +10332,14 @@
       </c>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
-    </row>
-    <row r="129" spans="1:14">
+      <c r="O128" t="s">
+        <v>22</v>
+      </c>
+      <c r="P128" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
       <c r="A129" s="1" t="s">
         <v>487</v>
       </c>
@@ -9195,8 +10378,14 @@
       </c>
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
-    </row>
-    <row r="130" spans="1:14">
+      <c r="O129" t="s">
+        <v>1104</v>
+      </c>
+      <c r="P129" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
       <c r="A130" s="1" t="s">
         <v>490</v>
       </c>
@@ -9235,8 +10424,14 @@
       </c>
       <c r="M130" s="3"/>
       <c r="N130" s="3"/>
-    </row>
-    <row r="131" spans="1:14">
+      <c r="O130" t="s">
+        <v>22</v>
+      </c>
+      <c r="P130" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
       <c r="A131" s="1" t="s">
         <v>493</v>
       </c>
@@ -9275,8 +10470,14 @@
       </c>
       <c r="M131" s="3"/>
       <c r="N131" s="3"/>
-    </row>
-    <row r="132" spans="1:14">
+      <c r="O131" t="s">
+        <v>22</v>
+      </c>
+      <c r="P131" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
       <c r="A132" s="1" t="s">
         <v>496</v>
       </c>
@@ -9315,8 +10516,14 @@
       </c>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
-    </row>
-    <row r="133" spans="1:14">
+      <c r="O132" t="s">
+        <v>22</v>
+      </c>
+      <c r="P132" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
       <c r="A133" s="1" t="s">
         <v>499</v>
       </c>
@@ -9355,8 +10562,14 @@
       </c>
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
-    </row>
-    <row r="134" spans="1:14" ht="32">
+      <c r="O133" t="s">
+        <v>1105</v>
+      </c>
+      <c r="P133" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="32">
       <c r="A134" s="1" t="s">
         <v>503</v>
       </c>
@@ -9399,8 +10612,14 @@
       <c r="N134" s="3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="135" spans="1:14">
+      <c r="O134" t="s">
+        <v>22</v>
+      </c>
+      <c r="P134" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
       <c r="A135" s="1" t="s">
         <v>509</v>
       </c>
@@ -9439,8 +10658,14 @@
       </c>
       <c r="M135" s="3"/>
       <c r="N135" s="3"/>
-    </row>
-    <row r="136" spans="1:14">
+      <c r="O135" t="s">
+        <v>22</v>
+      </c>
+      <c r="P135" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
       <c r="A136" s="1" t="s">
         <v>512</v>
       </c>
@@ -9479,8 +10704,14 @@
       </c>
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
-    </row>
-    <row r="137" spans="1:14">
+      <c r="O136" t="s">
+        <v>1106</v>
+      </c>
+      <c r="P136" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
       <c r="A137" s="1" t="s">
         <v>514</v>
       </c>
@@ -9519,8 +10750,14 @@
       </c>
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
-    </row>
-    <row r="138" spans="1:14">
+      <c r="O137" t="s">
+        <v>1107</v>
+      </c>
+      <c r="P137" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
       <c r="A138" s="1" t="s">
         <v>516</v>
       </c>
@@ -9559,8 +10796,14 @@
       </c>
       <c r="M138" s="3"/>
       <c r="N138" s="3"/>
-    </row>
-    <row r="139" spans="1:14">
+      <c r="O138" t="s">
+        <v>22</v>
+      </c>
+      <c r="P138" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
       <c r="A139" s="1" t="s">
         <v>519</v>
       </c>
@@ -9599,8 +10842,14 @@
       </c>
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
-    </row>
-    <row r="140" spans="1:14">
+      <c r="O139" t="s">
+        <v>22</v>
+      </c>
+      <c r="P139" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
       <c r="A140" s="1" t="s">
         <v>524</v>
       </c>
@@ -9639,8 +10888,14 @@
       </c>
       <c r="M140" s="3"/>
       <c r="N140" s="3"/>
-    </row>
-    <row r="141" spans="1:14">
+      <c r="O140" t="s">
+        <v>22</v>
+      </c>
+      <c r="P140" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
       <c r="A141" s="1" t="s">
         <v>529</v>
       </c>
@@ -9679,8 +10934,14 @@
       </c>
       <c r="M141" s="3"/>
       <c r="N141" s="3"/>
-    </row>
-    <row r="142" spans="1:14">
+      <c r="O141" t="s">
+        <v>22</v>
+      </c>
+      <c r="P141" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
       <c r="A142" s="1" t="s">
         <v>533</v>
       </c>
@@ -9719,8 +10980,14 @@
       </c>
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
-    </row>
-    <row r="143" spans="1:14" ht="32">
+      <c r="O142" t="s">
+        <v>22</v>
+      </c>
+      <c r="P142" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" ht="32">
       <c r="A143" s="1" t="s">
         <v>536</v>
       </c>
@@ -9759,8 +11026,14 @@
       </c>
       <c r="M143" s="3"/>
       <c r="N143" s="3"/>
-    </row>
-    <row r="144" spans="1:14">
+      <c r="O143" t="s">
+        <v>22</v>
+      </c>
+      <c r="P143" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
       <c r="A144" s="1" t="s">
         <v>540</v>
       </c>
@@ -9799,8 +11072,14 @@
       </c>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
-    </row>
-    <row r="145" spans="1:14">
+      <c r="O144" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P144" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
       <c r="A145" s="1" t="s">
         <v>544</v>
       </c>
@@ -9839,8 +11118,14 @@
       </c>
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
-    </row>
-    <row r="146" spans="1:14">
+      <c r="O145" t="s">
+        <v>1109</v>
+      </c>
+      <c r="P145" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
       <c r="A146" s="1" t="s">
         <v>548</v>
       </c>
@@ -9879,8 +11164,14 @@
       </c>
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
-    </row>
-    <row r="147" spans="1:14">
+      <c r="O146" t="s">
+        <v>1110</v>
+      </c>
+      <c r="P146" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
       <c r="A147" s="1" t="s">
         <v>551</v>
       </c>
@@ -9919,8 +11210,14 @@
       </c>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
-    </row>
-    <row r="148" spans="1:14">
+      <c r="O147" t="s">
+        <v>1111</v>
+      </c>
+      <c r="P147" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
       <c r="A148" s="1" t="s">
         <v>555</v>
       </c>
@@ -9959,8 +11256,14 @@
       </c>
       <c r="M148" s="3"/>
       <c r="N148" s="3"/>
-    </row>
-    <row r="149" spans="1:14">
+      <c r="O148" t="s">
+        <v>22</v>
+      </c>
+      <c r="P148" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
       <c r="A149" s="1" t="s">
         <v>560</v>
       </c>
@@ -9999,8 +11302,14 @@
       </c>
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
-    </row>
-    <row r="150" spans="1:14" ht="32">
+      <c r="O149" t="s">
+        <v>22</v>
+      </c>
+      <c r="P149" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" ht="32">
       <c r="A150" s="1" t="s">
         <v>563</v>
       </c>
@@ -10043,8 +11352,14 @@
       <c r="N150" s="3" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="151" spans="1:14">
+      <c r="O150" t="s">
+        <v>22</v>
+      </c>
+      <c r="P150" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
       <c r="A151" s="1" t="s">
         <v>568</v>
       </c>
@@ -10085,8 +11400,14 @@
       <c r="N151" s="3" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="152" spans="1:14">
+      <c r="O151" t="s">
+        <v>22</v>
+      </c>
+      <c r="P151" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
       <c r="A152" s="1" t="s">
         <v>574</v>
       </c>
@@ -10125,8 +11446,14 @@
       </c>
       <c r="M152" s="3"/>
       <c r="N152" s="3"/>
-    </row>
-    <row r="153" spans="1:14">
+      <c r="O152" t="s">
+        <v>22</v>
+      </c>
+      <c r="P152" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
       <c r="A153" s="1" t="s">
         <v>577</v>
       </c>
@@ -10165,8 +11492,14 @@
       </c>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
-    </row>
-    <row r="154" spans="1:14">
+      <c r="O153" t="s">
+        <v>22</v>
+      </c>
+      <c r="P153" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
       <c r="A154" s="1" t="s">
         <v>580</v>
       </c>
@@ -10205,8 +11538,14 @@
       </c>
       <c r="M154" s="3"/>
       <c r="N154" s="3"/>
-    </row>
-    <row r="155" spans="1:14" ht="48">
+      <c r="O154" t="s">
+        <v>22</v>
+      </c>
+      <c r="P154" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" ht="48">
       <c r="A155" s="1" t="s">
         <v>583</v>
       </c>
@@ -10247,8 +11586,14 @@
       <c r="N155" s="3" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="156" spans="1:14">
+      <c r="O155" t="s">
+        <v>22</v>
+      </c>
+      <c r="P155" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
       <c r="A156" s="1" t="s">
         <v>587</v>
       </c>
@@ -10287,8 +11632,14 @@
       </c>
       <c r="M156" s="3"/>
       <c r="N156" s="3"/>
-    </row>
-    <row r="157" spans="1:14">
+      <c r="O156" t="s">
+        <v>22</v>
+      </c>
+      <c r="P156" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
       <c r="A157" s="1" t="s">
         <v>591</v>
       </c>
@@ -10327,8 +11678,14 @@
       </c>
       <c r="M157" s="3"/>
       <c r="N157" s="3"/>
-    </row>
-    <row r="158" spans="1:14" ht="32">
+      <c r="O157" t="s">
+        <v>22</v>
+      </c>
+      <c r="P157" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" ht="32">
       <c r="A158" s="1" t="s">
         <v>595</v>
       </c>
@@ -10371,8 +11728,14 @@
       <c r="N158" s="3" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="159" spans="1:14">
+      <c r="O158" t="s">
+        <v>22</v>
+      </c>
+      <c r="P158" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
       <c r="A159" s="1" t="s">
         <v>600</v>
       </c>
@@ -10411,8 +11774,14 @@
       </c>
       <c r="M159" s="3"/>
       <c r="N159" s="3"/>
-    </row>
-    <row r="160" spans="1:14" ht="32">
+      <c r="O159" t="s">
+        <v>22</v>
+      </c>
+      <c r="P159" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" ht="32">
       <c r="A160" s="1" t="s">
         <v>603</v>
       </c>
@@ -10453,8 +11822,14 @@
       <c r="N160" s="3" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="161" spans="1:14" ht="32">
+      <c r="O160" t="s">
+        <v>22</v>
+      </c>
+      <c r="P160" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" ht="32">
       <c r="A161" s="1" t="s">
         <v>607</v>
       </c>
@@ -10497,8 +11872,14 @@
       <c r="N161" s="3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="162" spans="1:14">
+      <c r="O161" t="s">
+        <v>22</v>
+      </c>
+      <c r="P161" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
       <c r="A162" s="1" t="s">
         <v>611</v>
       </c>
@@ -10537,8 +11918,14 @@
       </c>
       <c r="M162" s="3"/>
       <c r="N162" s="3"/>
-    </row>
-    <row r="163" spans="1:14" ht="32">
+      <c r="O162" t="s">
+        <v>22</v>
+      </c>
+      <c r="P162" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" ht="32">
       <c r="A163" s="1" t="s">
         <v>614</v>
       </c>
@@ -10581,8 +11968,14 @@
       <c r="N163" s="3" t="s">
         <v>599</v>
       </c>
-    </row>
-    <row r="164" spans="1:14">
+      <c r="O163" t="s">
+        <v>22</v>
+      </c>
+      <c r="P163" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16">
       <c r="A164" s="1" t="s">
         <v>617</v>
       </c>
@@ -10621,8 +12014,14 @@
       </c>
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
-    </row>
-    <row r="165" spans="1:14">
+      <c r="O164" t="s">
+        <v>1112</v>
+      </c>
+      <c r="P164" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16">
       <c r="A165" s="1" t="s">
         <v>620</v>
       </c>
@@ -10661,8 +12060,14 @@
       </c>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
-    </row>
-    <row r="166" spans="1:14">
+      <c r="O165" t="s">
+        <v>1113</v>
+      </c>
+      <c r="P165" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16">
       <c r="A166" s="1" t="s">
         <v>622</v>
       </c>
@@ -10703,8 +12108,14 @@
       <c r="N166" s="3" t="s">
         <v>625</v>
       </c>
-    </row>
-    <row r="167" spans="1:14" ht="32">
+      <c r="O166" t="s">
+        <v>22</v>
+      </c>
+      <c r="P166" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" ht="32">
       <c r="A167" s="1" t="s">
         <v>626</v>
       </c>
@@ -10747,8 +12158,14 @@
       <c r="N167" s="3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="168" spans="1:14">
+      <c r="O167" t="s">
+        <v>1114</v>
+      </c>
+      <c r="P167" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16">
       <c r="A168" s="1" t="s">
         <v>629</v>
       </c>
@@ -10787,8 +12204,14 @@
       </c>
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
-    </row>
-    <row r="169" spans="1:14">
+      <c r="O168" t="s">
+        <v>1115</v>
+      </c>
+      <c r="P168" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16">
       <c r="A169" s="1" t="s">
         <v>634</v>
       </c>
@@ -10827,8 +12250,14 @@
       </c>
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
-    </row>
-    <row r="170" spans="1:14" ht="32">
+      <c r="O169" t="s">
+        <v>1116</v>
+      </c>
+      <c r="P169" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" ht="32">
       <c r="A170" s="1" t="s">
         <v>636</v>
       </c>
@@ -10869,8 +12298,14 @@
       <c r="N170" s="3" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="171" spans="1:14">
+      <c r="O170" t="s">
+        <v>22</v>
+      </c>
+      <c r="P170" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16">
       <c r="A171" s="1" t="s">
         <v>640</v>
       </c>
@@ -10909,8 +12344,14 @@
       </c>
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
-    </row>
-    <row r="172" spans="1:14">
+      <c r="O171" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P171" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16">
       <c r="A172" s="1" t="s">
         <v>642</v>
       </c>
@@ -10949,8 +12390,14 @@
       </c>
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
-    </row>
-    <row r="173" spans="1:14">
+      <c r="O172" t="s">
+        <v>1118</v>
+      </c>
+      <c r="P172" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16">
       <c r="A173" s="1" t="s">
         <v>644</v>
       </c>
@@ -10989,8 +12436,14 @@
       </c>
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
-    </row>
-    <row r="174" spans="1:14">
+      <c r="O173" t="s">
+        <v>1119</v>
+      </c>
+      <c r="P173" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16">
       <c r="A174" s="1" t="s">
         <v>647</v>
       </c>
@@ -11029,8 +12482,14 @@
       </c>
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
-    </row>
-    <row r="175" spans="1:14">
+      <c r="O174" t="s">
+        <v>1120</v>
+      </c>
+      <c r="P174" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16">
       <c r="A175" s="1" t="s">
         <v>649</v>
       </c>
@@ -11069,8 +12528,14 @@
       </c>
       <c r="M175" s="3"/>
       <c r="N175" s="3"/>
-    </row>
-    <row r="176" spans="1:14">
+      <c r="O175" t="s">
+        <v>1121</v>
+      </c>
+      <c r="P175" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16">
       <c r="A176" s="1" t="s">
         <v>652</v>
       </c>
@@ -11109,8 +12574,14 @@
       </c>
       <c r="M176" s="3"/>
       <c r="N176" s="3"/>
-    </row>
-    <row r="177" spans="1:14">
+      <c r="O176" t="s">
+        <v>1122</v>
+      </c>
+      <c r="P176" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16">
       <c r="A177" s="1" t="s">
         <v>655</v>
       </c>
@@ -11149,8 +12620,14 @@
       </c>
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
-    </row>
-    <row r="178" spans="1:14">
+      <c r="O177" t="s">
+        <v>1123</v>
+      </c>
+      <c r="P177" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
       <c r="A178" s="1" t="s">
         <v>658</v>
       </c>
@@ -11189,8 +12666,14 @@
       </c>
       <c r="M178" s="3"/>
       <c r="N178" s="3"/>
-    </row>
-    <row r="179" spans="1:14">
+      <c r="O178" t="s">
+        <v>1124</v>
+      </c>
+      <c r="P178" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16">
       <c r="A179" s="1" t="s">
         <v>661</v>
       </c>
@@ -11229,8 +12712,14 @@
       </c>
       <c r="M179" s="3"/>
       <c r="N179" s="3"/>
-    </row>
-    <row r="180" spans="1:14">
+      <c r="O179" t="s">
+        <v>1125</v>
+      </c>
+      <c r="P179" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16">
       <c r="A180" s="1" t="s">
         <v>663</v>
       </c>
@@ -11269,8 +12758,14 @@
       </c>
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
-    </row>
-    <row r="181" spans="1:14">
+      <c r="O180" t="s">
+        <v>1126</v>
+      </c>
+      <c r="P180" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16">
       <c r="A181" s="1" t="s">
         <v>666</v>
       </c>
@@ -11309,8 +12804,14 @@
       </c>
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
-    </row>
-    <row r="182" spans="1:14">
+      <c r="O181" t="s">
+        <v>1127</v>
+      </c>
+      <c r="P181" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16">
       <c r="A182" s="1" t="s">
         <v>669</v>
       </c>
@@ -11349,8 +12850,14 @@
       </c>
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
-    </row>
-    <row r="183" spans="1:14">
+      <c r="O182" t="s">
+        <v>1128</v>
+      </c>
+      <c r="P182" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16">
       <c r="A183" s="1" t="s">
         <v>672</v>
       </c>
@@ -11389,8 +12896,14 @@
       </c>
       <c r="M183" s="3"/>
       <c r="N183" s="3"/>
-    </row>
-    <row r="184" spans="1:14">
+      <c r="O183" t="s">
+        <v>22</v>
+      </c>
+      <c r="P183" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16">
       <c r="A184" s="1" t="s">
         <v>675</v>
       </c>
@@ -11429,8 +12942,14 @@
       </c>
       <c r="M184" s="3"/>
       <c r="N184" s="3"/>
-    </row>
-    <row r="185" spans="1:14">
+      <c r="O184" t="s">
+        <v>1129</v>
+      </c>
+      <c r="P184" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16">
       <c r="A185" s="1" t="s">
         <v>677</v>
       </c>
@@ -11469,8 +12988,14 @@
       </c>
       <c r="M185" s="3"/>
       <c r="N185" s="3"/>
-    </row>
-    <row r="186" spans="1:14">
+      <c r="O185" t="s">
+        <v>1130</v>
+      </c>
+      <c r="P185" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16">
       <c r="A186" s="1" t="s">
         <v>680</v>
       </c>
@@ -11509,8 +13034,14 @@
       </c>
       <c r="M186" s="3"/>
       <c r="N186" s="3"/>
-    </row>
-    <row r="187" spans="1:14" ht="48">
+      <c r="O186" t="s">
+        <v>1131</v>
+      </c>
+      <c r="P186" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16" ht="48">
       <c r="A187" s="1" t="s">
         <v>683</v>
       </c>
@@ -11553,8 +13084,14 @@
       <c r="N187" s="3" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="188" spans="1:14">
+      <c r="O187" t="s">
+        <v>1132</v>
+      </c>
+      <c r="P187" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16">
       <c r="A188" s="1" t="s">
         <v>685</v>
       </c>
@@ -11593,8 +13130,14 @@
       </c>
       <c r="M188" s="3"/>
       <c r="N188" s="3"/>
-    </row>
-    <row r="189" spans="1:14">
+      <c r="O188" t="s">
+        <v>22</v>
+      </c>
+      <c r="P188" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16">
       <c r="A189" s="1" t="s">
         <v>688</v>
       </c>
@@ -11633,8 +13176,14 @@
       </c>
       <c r="M189" s="3"/>
       <c r="N189" s="3"/>
-    </row>
-    <row r="190" spans="1:14" ht="32">
+      <c r="O189" t="s">
+        <v>1133</v>
+      </c>
+      <c r="P189" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16" ht="32">
       <c r="A190" s="1" t="s">
         <v>692</v>
       </c>
@@ -11677,8 +13226,14 @@
       <c r="N190" s="3" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="191" spans="1:14">
+      <c r="O190" t="s">
+        <v>22</v>
+      </c>
+      <c r="P190" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16">
       <c r="A191" s="1" t="s">
         <v>697</v>
       </c>
@@ -11717,8 +13272,14 @@
       </c>
       <c r="M191" s="3"/>
       <c r="N191" s="3"/>
-    </row>
-    <row r="192" spans="1:14" ht="32">
+      <c r="O191" t="s">
+        <v>1134</v>
+      </c>
+      <c r="P191" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16" ht="32">
       <c r="A192" s="1" t="s">
         <v>700</v>
       </c>
@@ -11761,8 +13322,14 @@
       <c r="N192" s="3" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="193" spans="1:14">
+      <c r="O192" t="s">
+        <v>1135</v>
+      </c>
+      <c r="P192" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16">
       <c r="A193" t="s">
         <v>903</v>
       </c>
@@ -11802,8 +13369,14 @@
       <c r="N193" t="s">
         <v>909</v>
       </c>
-    </row>
-    <row r="194" spans="1:14">
+      <c r="O193" t="s">
+        <v>1136</v>
+      </c>
+      <c r="P193" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16">
       <c r="A194" t="s">
         <v>910</v>
       </c>
@@ -11843,8 +13416,14 @@
       <c r="N194" t="s">
         <v>914</v>
       </c>
-    </row>
-    <row r="195" spans="1:14">
+      <c r="O194" t="s">
+        <v>1137</v>
+      </c>
+      <c r="P194" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16">
       <c r="A195" t="s">
         <v>915</v>
       </c>
@@ -11884,8 +13463,14 @@
       <c r="N195" t="s">
         <v>919</v>
       </c>
-    </row>
-    <row r="196" spans="1:14">
+      <c r="O195" t="s">
+        <v>1138</v>
+      </c>
+      <c r="P195" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16">
       <c r="A196" t="s">
         <v>920</v>
       </c>
@@ -11925,8 +13510,14 @@
       <c r="N196" t="s">
         <v>924</v>
       </c>
-    </row>
-    <row r="197" spans="1:14">
+      <c r="O196" t="s">
+        <v>1139</v>
+      </c>
+      <c r="P196" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16">
       <c r="A197" t="s">
         <v>925</v>
       </c>
@@ -11966,8 +13557,14 @@
       <c r="N197" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="198" spans="1:14">
+      <c r="O197" t="s">
+        <v>1140</v>
+      </c>
+      <c r="P197" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16">
       <c r="A198" t="s">
         <v>930</v>
       </c>
@@ -12007,8 +13604,14 @@
       <c r="N198" t="s">
         <v>934</v>
       </c>
-    </row>
-    <row r="199" spans="1:14">
+      <c r="O198" t="s">
+        <v>1141</v>
+      </c>
+      <c r="P198" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16">
       <c r="A199" t="s">
         <v>935</v>
       </c>
@@ -12048,8 +13651,14 @@
       <c r="N199" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="200" spans="1:14">
+      <c r="O199" t="s">
+        <v>1142</v>
+      </c>
+      <c r="P199" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16">
       <c r="A200" t="s">
         <v>939</v>
       </c>
@@ -12089,8 +13698,14 @@
       <c r="N200" t="s">
         <v>943</v>
       </c>
-    </row>
-    <row r="201" spans="1:14">
+      <c r="O200" t="s">
+        <v>1143</v>
+      </c>
+      <c r="P200" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16">
       <c r="A201" t="s">
         <v>944</v>
       </c>
@@ -12130,8 +13745,14 @@
       <c r="N201" t="s">
         <v>948</v>
       </c>
-    </row>
-    <row r="202" spans="1:14">
+      <c r="O201" t="s">
+        <v>1144</v>
+      </c>
+      <c r="P201" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16">
       <c r="A202" t="s">
         <v>949</v>
       </c>
@@ -12171,8 +13792,14 @@
       <c r="N202" t="s">
         <v>952</v>
       </c>
-    </row>
-    <row r="203" spans="1:14">
+      <c r="O202" t="s">
+        <v>1145</v>
+      </c>
+      <c r="P202" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16">
       <c r="A203" t="s">
         <v>953</v>
       </c>
@@ -12212,8 +13839,14 @@
       <c r="N203" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="204" spans="1:14">
+      <c r="O203" t="s">
+        <v>1146</v>
+      </c>
+      <c r="P203" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16">
       <c r="A204" t="s">
         <v>957</v>
       </c>
@@ -12253,8 +13886,14 @@
       <c r="N204" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="205" spans="1:14">
+      <c r="O204" t="s">
+        <v>1147</v>
+      </c>
+      <c r="P204" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16">
       <c r="A205" t="s">
         <v>961</v>
       </c>
@@ -12294,8 +13933,14 @@
       <c r="N205" t="s">
         <v>964</v>
       </c>
-    </row>
-    <row r="206" spans="1:14">
+      <c r="O205" t="s">
+        <v>1148</v>
+      </c>
+      <c r="P205" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16">
       <c r="A206" t="s">
         <v>965</v>
       </c>
@@ -12335,8 +13980,14 @@
       <c r="N206" t="s">
         <v>968</v>
       </c>
-    </row>
-    <row r="207" spans="1:14">
+      <c r="O206" t="s">
+        <v>1149</v>
+      </c>
+      <c r="P206" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16">
       <c r="A207" t="s">
         <v>969</v>
       </c>
@@ -12376,8 +14027,14 @@
       <c r="N207" t="s">
         <v>972</v>
       </c>
-    </row>
-    <row r="208" spans="1:14">
+      <c r="O207" t="s">
+        <v>1150</v>
+      </c>
+      <c r="P207" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16">
       <c r="A208" t="s">
         <v>973</v>
       </c>
@@ -12417,8 +14074,14 @@
       <c r="N208" t="s">
         <v>977</v>
       </c>
-    </row>
-    <row r="209" spans="1:14">
+      <c r="O208" t="s">
+        <v>1151</v>
+      </c>
+      <c r="P208" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16">
       <c r="A209" t="s">
         <v>978</v>
       </c>
@@ -12458,8 +14121,14 @@
       <c r="N209" t="s">
         <v>981</v>
       </c>
-    </row>
-    <row r="210" spans="1:14">
+      <c r="O209" t="s">
+        <v>1152</v>
+      </c>
+      <c r="P209" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16">
       <c r="A210" t="s">
         <v>982</v>
       </c>
@@ -12499,8 +14168,14 @@
       <c r="N210" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="211" spans="1:14">
+      <c r="O210" t="s">
+        <v>1153</v>
+      </c>
+      <c r="P210" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16">
       <c r="A211" t="s">
         <v>986</v>
       </c>
@@ -12540,8 +14215,14 @@
       <c r="N211" t="s">
         <v>989</v>
       </c>
-    </row>
-    <row r="212" spans="1:14">
+      <c r="O211" t="s">
+        <v>1154</v>
+      </c>
+      <c r="P211" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16">
       <c r="A212" t="s">
         <v>990</v>
       </c>
@@ -12581,8 +14262,14 @@
       <c r="N212" t="s">
         <v>994</v>
       </c>
-    </row>
-    <row r="213" spans="1:14">
+      <c r="O212" t="s">
+        <v>1155</v>
+      </c>
+      <c r="P212" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16">
       <c r="A213" t="s">
         <v>995</v>
       </c>
@@ -12622,8 +14309,14 @@
       <c r="N213" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="214" spans="1:14">
+      <c r="O213" t="s">
+        <v>1156</v>
+      </c>
+      <c r="P213" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16">
       <c r="A214" t="s">
         <v>999</v>
       </c>
@@ -12663,8 +14356,14 @@
       <c r="N214" t="s">
         <v>1002</v>
       </c>
-    </row>
-    <row r="215" spans="1:14">
+      <c r="O214" t="s">
+        <v>1157</v>
+      </c>
+      <c r="P214" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16">
       <c r="A215" t="s">
         <v>1003</v>
       </c>
@@ -12704,8 +14403,14 @@
       <c r="N215" t="s">
         <v>1006</v>
       </c>
-    </row>
-    <row r="216" spans="1:14">
+      <c r="O215" t="s">
+        <v>1158</v>
+      </c>
+      <c r="P215" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16">
       <c r="A216" t="s">
         <v>1007</v>
       </c>
@@ -12745,8 +14450,14 @@
       <c r="N216" t="s">
         <v>1010</v>
       </c>
-    </row>
-    <row r="217" spans="1:14">
+      <c r="O216" t="s">
+        <v>1159</v>
+      </c>
+      <c r="P216" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16">
       <c r="A217" t="s">
         <v>1011</v>
       </c>
@@ -12786,8 +14497,14 @@
       <c r="N217" t="s">
         <v>1014</v>
       </c>
-    </row>
-    <row r="218" spans="1:14">
+      <c r="O217" t="s">
+        <v>1160</v>
+      </c>
+      <c r="P217" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16">
       <c r="A218" t="s">
         <v>1015</v>
       </c>
@@ -12827,8 +14544,14 @@
       <c r="N218" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="219" spans="1:14">
+      <c r="O218" t="s">
+        <v>1161</v>
+      </c>
+      <c r="P218" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16">
       <c r="A219" t="s">
         <v>1019</v>
       </c>
@@ -12868,8 +14591,14 @@
       <c r="N219" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="220" spans="1:14">
+      <c r="O219" t="s">
+        <v>1162</v>
+      </c>
+      <c r="P219" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16">
       <c r="A220" t="s">
         <v>1023</v>
       </c>
@@ -12909,8 +14638,14 @@
       <c r="N220" t="s">
         <v>1026</v>
       </c>
-    </row>
-    <row r="221" spans="1:14">
+      <c r="O220" t="s">
+        <v>1163</v>
+      </c>
+      <c r="P220" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16">
       <c r="A221" t="s">
         <v>1027</v>
       </c>
@@ -12949,6 +14684,12 @@
       </c>
       <c r="N221" t="s">
         <v>1030</v>
+      </c>
+      <c r="O221" t="s">
+        <v>1164</v>
+      </c>
+      <c r="P221" t="s">
+        <v>1039</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA6A1A1-8AB9-4F22-9D3E-6BB959A71B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D1811C-1C79-4CEB-B38F-1286F3D2EE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1169">
   <si>
     <t>ID</t>
   </si>
@@ -3251,413 +3251,419 @@
     <t>2026-10-06 추가. 국내외 학회 가이드라인 근거. 계약서 DIET-P-0268</t>
   </si>
   <si>
-    <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다.</t>
+    <t>계약서 문구 ID</t>
+  </si>
+  <si>
+    <t>연결 상태</t>
+  </si>
+  <si>
+    <t>DIET-P-0040</t>
+  </si>
+  <si>
+    <t>근거대조서를 거쳐 연결</t>
+  </si>
+  <si>
+    <t>계약서에 없음</t>
+  </si>
+  <si>
+    <t>DIET-P-0041</t>
+  </si>
+  <si>
+    <t>DIET-P-0042</t>
+  </si>
+  <si>
+    <t>문구 그대로</t>
+  </si>
+  <si>
+    <t>DIET-P-0043</t>
+  </si>
+  <si>
+    <t>DIET-P-0044</t>
+  </si>
+  <si>
+    <t>DIET-P-0045</t>
+  </si>
+  <si>
+    <t>DIET-P-0046</t>
+  </si>
+  <si>
+    <t>DIET-P-0047</t>
+  </si>
+  <si>
+    <t>DIET-P-0048</t>
+  </si>
+  <si>
+    <t>DIET-P-0049</t>
+  </si>
+  <si>
+    <t>DIET-P-0050</t>
+  </si>
+  <si>
+    <t>DIET-P-0051</t>
+  </si>
+  <si>
+    <t>DIET-P-0053</t>
+  </si>
+  <si>
+    <t>DIET-P-0054</t>
+  </si>
+  <si>
+    <t>DIET-P-0055</t>
+  </si>
+  <si>
+    <t>DIET-P-0056</t>
+  </si>
+  <si>
+    <t>DIET-P-0057</t>
+  </si>
+  <si>
+    <t>DIET-P-0058</t>
+  </si>
+  <si>
+    <t>DIET-P-0059</t>
+  </si>
+  <si>
+    <t>DIET-P-0066</t>
+  </si>
+  <si>
+    <t>DIET-P-0070</t>
+  </si>
+  <si>
+    <t>DIET-P-0071</t>
+  </si>
+  <si>
+    <t>DIET-P-0072</t>
+  </si>
+  <si>
+    <t>DIET-P-0073</t>
+  </si>
+  <si>
+    <t>DIET-P-0074</t>
+  </si>
+  <si>
+    <t>DIET-P-0075</t>
+  </si>
+  <si>
+    <t>DIET-P-0076</t>
+  </si>
+  <si>
+    <t>DIET-P-0077</t>
+  </si>
+  <si>
+    <t>DIET-P-0078</t>
+  </si>
+  <si>
+    <t>DIET-P-0079</t>
+  </si>
+  <si>
+    <t>DIET-P-0082</t>
+  </si>
+  <si>
+    <t>DIET-P-0083</t>
+  </si>
+  <si>
+    <t>DIET-P-0087</t>
+  </si>
+  <si>
+    <t>DIET-P-0088</t>
+  </si>
+  <si>
+    <t>DIET-P-0089</t>
+  </si>
+  <si>
+    <t>DIET-P-0093</t>
+  </si>
+  <si>
+    <t>DIET-P-0094</t>
+  </si>
+  <si>
+    <t>DIET-P-0095</t>
+  </si>
+  <si>
+    <t>DIET-P-0100</t>
+  </si>
+  <si>
+    <t>DIET-P-0102</t>
+  </si>
+  <si>
+    <t>DIET-P-0103</t>
+  </si>
+  <si>
+    <t>DIET-P-0104</t>
+  </si>
+  <si>
+    <t>DIET-P-0105</t>
+  </si>
+  <si>
+    <t>DIET-P-0107</t>
+  </si>
+  <si>
+    <t>DIET-P-0110</t>
+  </si>
+  <si>
+    <t>DIET-P-0114</t>
+  </si>
+  <si>
+    <t>DIET-P-0115</t>
+  </si>
+  <si>
+    <t>DIET-P-0118</t>
+  </si>
+  <si>
+    <t>DIET-P-0119</t>
+  </si>
+  <si>
+    <t>DIET-P-0121</t>
+  </si>
+  <si>
+    <t>DIET-P-0122</t>
+  </si>
+  <si>
+    <t>DIET-P-0124</t>
+  </si>
+  <si>
+    <t>DIET-P-0126</t>
+  </si>
+  <si>
+    <t>DIET-P-0131</t>
+  </si>
+  <si>
+    <t>DIET-P-0136</t>
+  </si>
+  <si>
+    <t>DIET-P-0139</t>
+  </si>
+  <si>
+    <t>DIET-P-0141</t>
+  </si>
+  <si>
+    <t>DIET-P-0146</t>
+  </si>
+  <si>
+    <t>DIET-P-0147</t>
+  </si>
+  <si>
+    <t>DIET-P-0148</t>
+  </si>
+  <si>
+    <t>DIET-P-0149</t>
+  </si>
+  <si>
+    <t>DIET-P-0150</t>
+  </si>
+  <si>
+    <t>DIET-P-0153</t>
+  </si>
+  <si>
+    <t>DIET-P-0154</t>
+  </si>
+  <si>
+    <t>DIET-P-0156</t>
+  </si>
+  <si>
+    <t>DIET-P-0157</t>
+  </si>
+  <si>
+    <t>DIET-P-0161</t>
+  </si>
+  <si>
+    <t>DIET-P-0165</t>
+  </si>
+  <si>
+    <t>DIET-P-0169</t>
+  </si>
+  <si>
+    <t>DIET-P-0172</t>
+  </si>
+  <si>
+    <t>DIET-P-0173</t>
+  </si>
+  <si>
+    <t>DIET-P-0180</t>
+  </si>
+  <si>
+    <t>DIET-P-0181</t>
+  </si>
+  <si>
+    <t>DIET-P-0182</t>
+  </si>
+  <si>
+    <t>DIET-P-0183</t>
+  </si>
+  <si>
+    <t>DIET-P-0198</t>
+  </si>
+  <si>
+    <t>DIET-P-0199</t>
+  </si>
+  <si>
+    <t>DIET-P-0200</t>
+  </si>
+  <si>
+    <t>DIET-P-0201</t>
+  </si>
+  <si>
+    <t>DIET-P-0202</t>
+  </si>
+  <si>
+    <t>DIET-P-0204</t>
+  </si>
+  <si>
+    <t>DIET-P-0205</t>
+  </si>
+  <si>
+    <t>DIET-P-0206</t>
+  </si>
+  <si>
+    <t>DIET-P-0207</t>
+  </si>
+  <si>
+    <t>DIET-P-0208</t>
+  </si>
+  <si>
+    <t>DIET-P-0209</t>
+  </si>
+  <si>
+    <t>DIET-P-0210</t>
+  </si>
+  <si>
+    <t>DIET-P-0211</t>
+  </si>
+  <si>
+    <t>DIET-P-0212</t>
+  </si>
+  <si>
+    <t>DIET-P-0213</t>
+  </si>
+  <si>
+    <t>DIET-P-0214</t>
+  </si>
+  <si>
+    <t>DIET-P-0215</t>
+  </si>
+  <si>
+    <t>DIET-P-0217</t>
+  </si>
+  <si>
+    <t>DIET-P-0218</t>
+  </si>
+  <si>
+    <t>DIET-P-0219</t>
+  </si>
+  <si>
+    <t>DIET-P-0220</t>
+  </si>
+  <si>
+    <t>DIET-P-0222</t>
+  </si>
+  <si>
+    <t>DIET-P-0224</t>
+  </si>
+  <si>
+    <t>DIET-P-0225</t>
+  </si>
+  <si>
+    <t>DIET-P-0239</t>
+  </si>
+  <si>
+    <t>DIET-P-0240</t>
+  </si>
+  <si>
+    <t>DIET-P-0241</t>
+  </si>
+  <si>
+    <t>DIET-P-0242</t>
+  </si>
+  <si>
+    <t>DIET-P-0243</t>
+  </si>
+  <si>
+    <t>DIET-P-0244</t>
+  </si>
+  <si>
+    <t>DIET-P-0245</t>
+  </si>
+  <si>
+    <t>DIET-P-0246</t>
+  </si>
+  <si>
+    <t>DIET-P-0247</t>
+  </si>
+  <si>
+    <t>DIET-P-0248</t>
+  </si>
+  <si>
+    <t>DIET-P-0249</t>
+  </si>
+  <si>
+    <t>DIET-P-0250</t>
+  </si>
+  <si>
+    <t>DIET-P-0251</t>
+  </si>
+  <si>
+    <t>DIET-P-0252</t>
+  </si>
+  <si>
+    <t>DIET-P-0253</t>
+  </si>
+  <si>
+    <t>DIET-P-0254</t>
+  </si>
+  <si>
+    <t>DIET-P-0255</t>
+  </si>
+  <si>
+    <t>DIET-P-0256</t>
+  </si>
+  <si>
+    <t>DIET-P-0257</t>
+  </si>
+  <si>
+    <t>DIET-P-0258</t>
+  </si>
+  <si>
+    <t>DIET-P-0259</t>
+  </si>
+  <si>
+    <t>DIET-P-0260</t>
+  </si>
+  <si>
+    <t>DIET-P-0262</t>
+  </si>
+  <si>
+    <t>DIET-P-0263</t>
+  </si>
+  <si>
+    <t>DIET-P-0264</t>
+  </si>
+  <si>
+    <t>DIET-P-0265</t>
+  </si>
+  <si>
+    <t>DIET-P-0266</t>
+  </si>
+  <si>
+    <t>DIET-P-0267</t>
+  </si>
+  <si>
+    <t>DIET-P-0268</t>
+  </si>
+  <si>
+    <t>계약서와의 연결</t>
+  </si>
+  <si>
+    <t>검수결과 시트 오른쪽에 「계약서 문구 ID」와 「연결 상태」 두 열을 두었다. 연결 상태가 「계약서에 없음」인 항목은 검수는 했으나 데이터계약 목표문구에 올라가 있지 않은 것이다. 2026-10-06 기준 연결 128 · 없음 92.</t>
+  </si>
+  <si>
+    <t>N221 6차 회복 풀 회복 영양 상담 예약 확인하기 영양 상담 예약 확인하기 13 신장질환 식사는 개인별 영양 상담이 도움이 돼요. — 근거 확인 필요 (질환규칙 DX-05 개별화 원칙) — 검수 대기  2026-10-07 추가. 만성 신장질환처럼 먹는 양을 늘리라고 자동으로 말할 수 없는 사용자의 결식 시 문구. 먹는 양을 바꾸지 않음. 계약서 미반영 — 계약서에 없음</t>
+  </si>
+  <si>
+    <t>N222 6차 회복 풀 회복 식사 시간 정해 두기 식사 시간 정해 두기 11 시간이 일정하면 끼니를 놓치기 어려워요. — 근거 확인 필요 (질환규칙 DX-05 개별화 원칙) — 검수 대기  2026-10-07 추가. 만성 신장질환처럼 먹는 양을 늘리라고 자동으로 말할 수 없는 사용자의 결식 시 문구. 먹는 양을 바꾸지 않음. 계약서 미반영 — 계약서에 없음</t>
+  </si>
+  <si>
+    <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다. 2026-10-07에 만성 신장질환 결식 시 쓸 회복 풀 문구 2개를 6차로 올렸고 이 2개도 검수 전이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>계약서 문구 ID</t>
-  </si>
-  <si>
-    <t>연결 상태</t>
-  </si>
-  <si>
-    <t>DIET-P-0040</t>
-  </si>
-  <si>
-    <t>근거대조서를 거쳐 연결</t>
-  </si>
-  <si>
-    <t>계약서에 없음</t>
-  </si>
-  <si>
-    <t>DIET-P-0041</t>
-  </si>
-  <si>
-    <t>DIET-P-0042</t>
-  </si>
-  <si>
-    <t>문구 그대로</t>
-  </si>
-  <si>
-    <t>DIET-P-0043</t>
-  </si>
-  <si>
-    <t>DIET-P-0044</t>
-  </si>
-  <si>
-    <t>DIET-P-0045</t>
-  </si>
-  <si>
-    <t>DIET-P-0046</t>
-  </si>
-  <si>
-    <t>DIET-P-0047</t>
-  </si>
-  <si>
-    <t>DIET-P-0048</t>
-  </si>
-  <si>
-    <t>DIET-P-0049</t>
-  </si>
-  <si>
-    <t>DIET-P-0050</t>
-  </si>
-  <si>
-    <t>DIET-P-0051</t>
-  </si>
-  <si>
-    <t>DIET-P-0053</t>
-  </si>
-  <si>
-    <t>DIET-P-0054</t>
-  </si>
-  <si>
-    <t>DIET-P-0055</t>
-  </si>
-  <si>
-    <t>DIET-P-0056</t>
-  </si>
-  <si>
-    <t>DIET-P-0057</t>
-  </si>
-  <si>
-    <t>DIET-P-0058</t>
-  </si>
-  <si>
-    <t>DIET-P-0059</t>
-  </si>
-  <si>
-    <t>DIET-P-0066</t>
-  </si>
-  <si>
-    <t>DIET-P-0070</t>
-  </si>
-  <si>
-    <t>DIET-P-0071</t>
-  </si>
-  <si>
-    <t>DIET-P-0072</t>
-  </si>
-  <si>
-    <t>DIET-P-0073</t>
-  </si>
-  <si>
-    <t>DIET-P-0074</t>
-  </si>
-  <si>
-    <t>DIET-P-0075</t>
-  </si>
-  <si>
-    <t>DIET-P-0076</t>
-  </si>
-  <si>
-    <t>DIET-P-0077</t>
-  </si>
-  <si>
-    <t>DIET-P-0078</t>
-  </si>
-  <si>
-    <t>DIET-P-0079</t>
-  </si>
-  <si>
-    <t>DIET-P-0082</t>
-  </si>
-  <si>
-    <t>DIET-P-0083</t>
-  </si>
-  <si>
-    <t>DIET-P-0087</t>
-  </si>
-  <si>
-    <t>DIET-P-0088</t>
-  </si>
-  <si>
-    <t>DIET-P-0089</t>
-  </si>
-  <si>
-    <t>DIET-P-0093</t>
-  </si>
-  <si>
-    <t>DIET-P-0094</t>
-  </si>
-  <si>
-    <t>DIET-P-0095</t>
-  </si>
-  <si>
-    <t>DIET-P-0100</t>
-  </si>
-  <si>
-    <t>DIET-P-0102</t>
-  </si>
-  <si>
-    <t>DIET-P-0103</t>
-  </si>
-  <si>
-    <t>DIET-P-0104</t>
-  </si>
-  <si>
-    <t>DIET-P-0105</t>
-  </si>
-  <si>
-    <t>DIET-P-0107</t>
-  </si>
-  <si>
-    <t>DIET-P-0110</t>
-  </si>
-  <si>
-    <t>DIET-P-0114</t>
-  </si>
-  <si>
-    <t>DIET-P-0115</t>
-  </si>
-  <si>
-    <t>DIET-P-0118</t>
-  </si>
-  <si>
-    <t>DIET-P-0119</t>
-  </si>
-  <si>
-    <t>DIET-P-0121</t>
-  </si>
-  <si>
-    <t>DIET-P-0122</t>
-  </si>
-  <si>
-    <t>DIET-P-0124</t>
-  </si>
-  <si>
-    <t>DIET-P-0126</t>
-  </si>
-  <si>
-    <t>DIET-P-0131</t>
-  </si>
-  <si>
-    <t>DIET-P-0136</t>
-  </si>
-  <si>
-    <t>DIET-P-0139</t>
-  </si>
-  <si>
-    <t>DIET-P-0141</t>
-  </si>
-  <si>
-    <t>DIET-P-0146</t>
-  </si>
-  <si>
-    <t>DIET-P-0147</t>
-  </si>
-  <si>
-    <t>DIET-P-0148</t>
-  </si>
-  <si>
-    <t>DIET-P-0149</t>
-  </si>
-  <si>
-    <t>DIET-P-0150</t>
-  </si>
-  <si>
-    <t>DIET-P-0153</t>
-  </si>
-  <si>
-    <t>DIET-P-0154</t>
-  </si>
-  <si>
-    <t>DIET-P-0156</t>
-  </si>
-  <si>
-    <t>DIET-P-0157</t>
-  </si>
-  <si>
-    <t>DIET-P-0161</t>
-  </si>
-  <si>
-    <t>DIET-P-0165</t>
-  </si>
-  <si>
-    <t>DIET-P-0169</t>
-  </si>
-  <si>
-    <t>DIET-P-0172</t>
-  </si>
-  <si>
-    <t>DIET-P-0173</t>
-  </si>
-  <si>
-    <t>DIET-P-0180</t>
-  </si>
-  <si>
-    <t>DIET-P-0181</t>
-  </si>
-  <si>
-    <t>DIET-P-0182</t>
-  </si>
-  <si>
-    <t>DIET-P-0183</t>
-  </si>
-  <si>
-    <t>DIET-P-0198</t>
-  </si>
-  <si>
-    <t>DIET-P-0199</t>
-  </si>
-  <si>
-    <t>DIET-P-0200</t>
-  </si>
-  <si>
-    <t>DIET-P-0201</t>
-  </si>
-  <si>
-    <t>DIET-P-0202</t>
-  </si>
-  <si>
-    <t>DIET-P-0204</t>
-  </si>
-  <si>
-    <t>DIET-P-0205</t>
-  </si>
-  <si>
-    <t>DIET-P-0206</t>
-  </si>
-  <si>
-    <t>DIET-P-0207</t>
-  </si>
-  <si>
-    <t>DIET-P-0208</t>
-  </si>
-  <si>
-    <t>DIET-P-0209</t>
-  </si>
-  <si>
-    <t>DIET-P-0210</t>
-  </si>
-  <si>
-    <t>DIET-P-0211</t>
-  </si>
-  <si>
-    <t>DIET-P-0212</t>
-  </si>
-  <si>
-    <t>DIET-P-0213</t>
-  </si>
-  <si>
-    <t>DIET-P-0214</t>
-  </si>
-  <si>
-    <t>DIET-P-0215</t>
-  </si>
-  <si>
-    <t>DIET-P-0217</t>
-  </si>
-  <si>
-    <t>DIET-P-0218</t>
-  </si>
-  <si>
-    <t>DIET-P-0219</t>
-  </si>
-  <si>
-    <t>DIET-P-0220</t>
-  </si>
-  <si>
-    <t>DIET-P-0222</t>
-  </si>
-  <si>
-    <t>DIET-P-0224</t>
-  </si>
-  <si>
-    <t>DIET-P-0225</t>
-  </si>
-  <si>
-    <t>DIET-P-0239</t>
-  </si>
-  <si>
-    <t>DIET-P-0240</t>
-  </si>
-  <si>
-    <t>DIET-P-0241</t>
-  </si>
-  <si>
-    <t>DIET-P-0242</t>
-  </si>
-  <si>
-    <t>DIET-P-0243</t>
-  </si>
-  <si>
-    <t>DIET-P-0244</t>
-  </si>
-  <si>
-    <t>DIET-P-0245</t>
-  </si>
-  <si>
-    <t>DIET-P-0246</t>
-  </si>
-  <si>
-    <t>DIET-P-0247</t>
-  </si>
-  <si>
-    <t>DIET-P-0248</t>
-  </si>
-  <si>
-    <t>DIET-P-0249</t>
-  </si>
-  <si>
-    <t>DIET-P-0250</t>
-  </si>
-  <si>
-    <t>DIET-P-0251</t>
-  </si>
-  <si>
-    <t>DIET-P-0252</t>
-  </si>
-  <si>
-    <t>DIET-P-0253</t>
-  </si>
-  <si>
-    <t>DIET-P-0254</t>
-  </si>
-  <si>
-    <t>DIET-P-0255</t>
-  </si>
-  <si>
-    <t>DIET-P-0256</t>
-  </si>
-  <si>
-    <t>DIET-P-0257</t>
-  </si>
-  <si>
-    <t>DIET-P-0258</t>
-  </si>
-  <si>
-    <t>DIET-P-0259</t>
-  </si>
-  <si>
-    <t>DIET-P-0260</t>
-  </si>
-  <si>
-    <t>DIET-P-0262</t>
-  </si>
-  <si>
-    <t>DIET-P-0263</t>
-  </si>
-  <si>
-    <t>DIET-P-0264</t>
-  </si>
-  <si>
-    <t>DIET-P-0265</t>
-  </si>
-  <si>
-    <t>DIET-P-0266</t>
-  </si>
-  <si>
-    <t>DIET-P-0267</t>
-  </si>
-  <si>
-    <t>DIET-P-0268</t>
-  </si>
-  <si>
-    <t>계약서와의 연결</t>
-  </si>
-  <si>
-    <t>검수결과 시트 오른쪽에 「계약서 문구 ID」와 「연결 상태」 두 열을 두었다. 연결 상태가 「계약서에 없음」인 항목은 검수는 했으나 데이터계약 목표문구에 올라가 있지 않은 것이다. 2026-10-06 기준 연결 128 · 없음 92.</t>
   </si>
 </sst>
 </file>
@@ -4225,7 +4231,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
-        <v>1031</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4370,12 +4376,12 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
   </sheetData>
@@ -4386,7 +4392,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEA781C-07E7-4393-BF75-138E1A6EB613}">
-  <dimension ref="A1:P221"/>
+  <dimension ref="A1:P223"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="7.58203125" customWidth="1"/>
@@ -4447,10 +4453,10 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="P1" t="s">
         <v>1032</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="2" spans="1:16">
@@ -4493,10 +4499,10 @@
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="P2" t="s">
         <v>1034</v>
-      </c>
-      <c r="P2" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="64">
@@ -4544,7 +4550,7 @@
         <v>22</v>
       </c>
       <c r="P3" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -4587,10 +4593,10 @@
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="P4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -4633,10 +4639,10 @@
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="P5" t="s">
         <v>1038</v>
-      </c>
-      <c r="P5" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -4679,10 +4685,10 @@
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="P6" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -4725,10 +4731,10 @@
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="P7" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -4771,10 +4777,10 @@
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="P8" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -4817,10 +4823,10 @@
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="P9" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -4863,10 +4869,10 @@
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="P10" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -4909,10 +4915,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="P11" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -4955,10 +4961,10 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="P12" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -5001,10 +5007,10 @@
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="P13" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="32">
@@ -5047,10 +5053,10 @@
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="P14" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -5096,7 +5102,7 @@
         <v>22</v>
       </c>
       <c r="P15" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -5139,10 +5145,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="P16" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -5185,10 +5191,10 @@
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="P17" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -5231,10 +5237,10 @@
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="P18" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -5277,10 +5283,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="P19" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -5323,10 +5329,10 @@
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="P20" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -5369,10 +5375,10 @@
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="P21" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -5415,10 +5421,10 @@
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="P22" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="32">
@@ -5464,7 +5470,7 @@
         <v>22</v>
       </c>
       <c r="P23" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -5510,7 +5516,7 @@
         <v>22</v>
       </c>
       <c r="P24" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="32">
@@ -5558,7 +5564,7 @@
         <v>22</v>
       </c>
       <c r="P25" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -5604,7 +5610,7 @@
         <v>22</v>
       </c>
       <c r="P26" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="32">
@@ -5652,7 +5658,7 @@
         <v>22</v>
       </c>
       <c r="P27" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="48">
@@ -5702,7 +5708,7 @@
         <v>22</v>
       </c>
       <c r="P28" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -5748,7 +5754,7 @@
         <v>22</v>
       </c>
       <c r="P29" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -5791,10 +5797,10 @@
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="P30" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="48">
@@ -5844,7 +5850,7 @@
         <v>22</v>
       </c>
       <c r="P31" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="48">
@@ -5894,7 +5900,7 @@
         <v>22</v>
       </c>
       <c r="P32" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="32">
@@ -5940,7 +5946,7 @@
         <v>22</v>
       </c>
       <c r="P33" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -5983,10 +5989,10 @@
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="P34" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -6029,10 +6035,10 @@
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="P35" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -6075,10 +6081,10 @@
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="P36" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -6121,10 +6127,10 @@
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="P37" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -6167,10 +6173,10 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="P38" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -6213,10 +6219,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="P39" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -6259,10 +6265,10 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="P40" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -6305,10 +6311,10 @@
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="P41" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="42" spans="1:16">
@@ -6351,10 +6357,10 @@
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="P42" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="32">
@@ -6397,10 +6403,10 @@
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="P43" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="48">
@@ -6448,7 +6454,7 @@
         <v>22</v>
       </c>
       <c r="P44" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="48">
@@ -6498,7 +6504,7 @@
         <v>22</v>
       </c>
       <c r="P45" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="32">
@@ -6545,10 +6551,10 @@
         <v>213</v>
       </c>
       <c r="O46" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="P46" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -6591,10 +6597,10 @@
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="P47" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -6640,7 +6646,7 @@
         <v>22</v>
       </c>
       <c r="P48" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="32">
@@ -6690,7 +6696,7 @@
         <v>22</v>
       </c>
       <c r="P49" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -6736,7 +6742,7 @@
         <v>22</v>
       </c>
       <c r="P50" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -6779,10 +6785,10 @@
       <c r="M51" s="3"/>
       <c r="N51" s="3"/>
       <c r="O51" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="P51" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -6825,10 +6831,10 @@
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
       <c r="O52" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="P52" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -6871,10 +6877,10 @@
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
       <c r="O53" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="P53" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -6920,7 +6926,7 @@
         <v>22</v>
       </c>
       <c r="P54" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -6966,7 +6972,7 @@
         <v>22</v>
       </c>
       <c r="P55" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -7012,7 +7018,7 @@
         <v>22</v>
       </c>
       <c r="P56" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="32">
@@ -7055,10 +7061,10 @@
       <c r="M57" s="3"/>
       <c r="N57" s="3"/>
       <c r="O57" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="P57" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -7101,10 +7107,10 @@
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
       <c r="O58" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="P58" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="32">
@@ -7147,10 +7153,10 @@
       <c r="M59" s="3"/>
       <c r="N59" s="3"/>
       <c r="O59" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="P59" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -7196,7 +7202,7 @@
         <v>22</v>
       </c>
       <c r="P60" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -7242,7 +7248,7 @@
         <v>22</v>
       </c>
       <c r="P61" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -7288,7 +7294,7 @@
         <v>22</v>
       </c>
       <c r="P62" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -7334,7 +7340,7 @@
         <v>22</v>
       </c>
       <c r="P63" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -7377,10 +7383,10 @@
       <c r="M64" s="3"/>
       <c r="N64" s="3"/>
       <c r="O64" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="P64" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -7426,7 +7432,7 @@
         <v>22</v>
       </c>
       <c r="P65" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -7469,10 +7475,10 @@
       <c r="M66" s="3"/>
       <c r="N66" s="3"/>
       <c r="O66" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="P66" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -7515,10 +7521,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="P67" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -7561,10 +7567,10 @@
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
       <c r="O68" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="P68" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -7607,10 +7613,10 @@
       <c r="M69" s="3"/>
       <c r="N69" s="3"/>
       <c r="O69" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="P69" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -7656,7 +7662,7 @@
         <v>22</v>
       </c>
       <c r="P70" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -7699,10 +7705,10 @@
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
       <c r="O71" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="P71" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -7748,7 +7754,7 @@
         <v>22</v>
       </c>
       <c r="P72" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="48">
@@ -7798,7 +7804,7 @@
         <v>22</v>
       </c>
       <c r="P73" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -7841,10 +7847,10 @@
       <c r="M74" s="3"/>
       <c r="N74" s="3"/>
       <c r="O74" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="P74" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -7890,7 +7896,7 @@
         <v>22</v>
       </c>
       <c r="P75" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="48">
@@ -7940,7 +7946,7 @@
         <v>22</v>
       </c>
       <c r="P76" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -7986,7 +7992,7 @@
         <v>22</v>
       </c>
       <c r="P77" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -8029,10 +8035,10 @@
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
       <c r="O78" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="P78" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -8075,10 +8081,10 @@
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
       <c r="O79" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="P79" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -8124,7 +8130,7 @@
         <v>22</v>
       </c>
       <c r="P80" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -8170,7 +8176,7 @@
         <v>22</v>
       </c>
       <c r="P81" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="32">
@@ -8213,10 +8219,10 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="P82" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -8259,10 +8265,10 @@
       <c r="M83" s="3"/>
       <c r="N83" s="3"/>
       <c r="O83" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="P83" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -8308,7 +8314,7 @@
         <v>22</v>
       </c>
       <c r="P84" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="32">
@@ -8351,10 +8357,10 @@
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
       <c r="O85" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="P85" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -8397,10 +8403,10 @@
       <c r="M86" s="3"/>
       <c r="N86" s="3"/>
       <c r="O86" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="P86" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -8446,7 +8452,7 @@
         <v>22</v>
       </c>
       <c r="P87" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -8489,10 +8495,10 @@
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
       <c r="O88" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="P88" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -8538,7 +8544,7 @@
         <v>22</v>
       </c>
       <c r="P89" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -8581,10 +8587,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="P90" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -8630,7 +8636,7 @@
         <v>22</v>
       </c>
       <c r="P91" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -8676,7 +8682,7 @@
         <v>22</v>
       </c>
       <c r="P92" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -8722,7 +8728,7 @@
         <v>22</v>
       </c>
       <c r="P93" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -8768,7 +8774,7 @@
         <v>22</v>
       </c>
       <c r="P94" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -8811,10 +8817,10 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="P95" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -8860,7 +8866,7 @@
         <v>22</v>
       </c>
       <c r="P96" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -8906,7 +8912,7 @@
         <v>22</v>
       </c>
       <c r="P97" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -8952,7 +8958,7 @@
         <v>22</v>
       </c>
       <c r="P98" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -8998,7 +9004,7 @@
         <v>22</v>
       </c>
       <c r="P99" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -9041,10 +9047,10 @@
       <c r="M100" s="3"/>
       <c r="N100" s="3"/>
       <c r="O100" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="P100" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -9090,7 +9096,7 @@
         <v>22</v>
       </c>
       <c r="P101" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -9136,7 +9142,7 @@
         <v>22</v>
       </c>
       <c r="P102" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -9179,10 +9185,10 @@
       <c r="M103" s="3"/>
       <c r="N103" s="3"/>
       <c r="O103" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="P103" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -9228,7 +9234,7 @@
         <v>22</v>
       </c>
       <c r="P104" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -9271,10 +9277,10 @@
       <c r="M105" s="3"/>
       <c r="N105" s="3"/>
       <c r="O105" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="P105" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -9320,7 +9326,7 @@
         <v>22</v>
       </c>
       <c r="P106" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="107" spans="1:16" ht="48">
@@ -9370,7 +9376,7 @@
         <v>22</v>
       </c>
       <c r="P107" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -9416,7 +9422,7 @@
         <v>22</v>
       </c>
       <c r="P108" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -9462,7 +9468,7 @@
         <v>22</v>
       </c>
       <c r="P109" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -9505,10 +9511,10 @@
       <c r="M110" s="3"/>
       <c r="N110" s="3"/>
       <c r="O110" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="P110" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -9551,10 +9557,10 @@
       <c r="M111" s="3"/>
       <c r="N111" s="3"/>
       <c r="O111" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="P111" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -9597,10 +9603,10 @@
       <c r="M112" s="3"/>
       <c r="N112" s="3"/>
       <c r="O112" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="P112" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -9643,10 +9649,10 @@
       <c r="M113" s="3"/>
       <c r="N113" s="3"/>
       <c r="O113" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="P113" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -9689,10 +9695,10 @@
       <c r="M114" s="3"/>
       <c r="N114" s="3"/>
       <c r="O114" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="P114" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -9738,7 +9744,7 @@
         <v>22</v>
       </c>
       <c r="P115" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -9784,7 +9790,7 @@
         <v>22</v>
       </c>
       <c r="P116" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -9827,10 +9833,10 @@
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
       <c r="O117" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="P117" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -9873,10 +9879,10 @@
       <c r="M118" s="3"/>
       <c r="N118" s="3"/>
       <c r="O118" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="P118" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -9922,7 +9928,7 @@
         <v>22</v>
       </c>
       <c r="P119" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -9965,10 +9971,10 @@
       <c r="M120" s="3"/>
       <c r="N120" s="3"/>
       <c r="O120" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="P120" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -10011,10 +10017,10 @@
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
       <c r="O121" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="P121" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -10060,7 +10066,7 @@
         <v>22</v>
       </c>
       <c r="P122" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -10106,7 +10112,7 @@
         <v>22</v>
       </c>
       <c r="P123" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -10152,7 +10158,7 @@
         <v>22</v>
       </c>
       <c r="P124" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -10195,10 +10201,10 @@
       <c r="M125" s="3"/>
       <c r="N125" s="3"/>
       <c r="O125" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="P125" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -10244,7 +10250,7 @@
         <v>22</v>
       </c>
       <c r="P126" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -10290,7 +10296,7 @@
         <v>22</v>
       </c>
       <c r="P127" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -10336,7 +10342,7 @@
         <v>22</v>
       </c>
       <c r="P128" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -10379,10 +10385,10 @@
       <c r="M129" s="3"/>
       <c r="N129" s="3"/>
       <c r="O129" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="P129" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -10428,7 +10434,7 @@
         <v>22</v>
       </c>
       <c r="P130" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -10474,7 +10480,7 @@
         <v>22</v>
       </c>
       <c r="P131" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -10520,7 +10526,7 @@
         <v>22</v>
       </c>
       <c r="P132" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -10563,10 +10569,10 @@
       <c r="M133" s="3"/>
       <c r="N133" s="3"/>
       <c r="O133" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="P133" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="134" spans="1:16" ht="32">
@@ -10616,7 +10622,7 @@
         <v>22</v>
       </c>
       <c r="P134" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -10662,7 +10668,7 @@
         <v>22</v>
       </c>
       <c r="P135" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -10705,10 +10711,10 @@
       <c r="M136" s="3"/>
       <c r="N136" s="3"/>
       <c r="O136" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="P136" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -10751,10 +10757,10 @@
       <c r="M137" s="3"/>
       <c r="N137" s="3"/>
       <c r="O137" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="P137" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -10800,7 +10806,7 @@
         <v>22</v>
       </c>
       <c r="P138" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -10846,7 +10852,7 @@
         <v>22</v>
       </c>
       <c r="P139" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -10892,7 +10898,7 @@
         <v>22</v>
       </c>
       <c r="P140" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -10938,7 +10944,7 @@
         <v>22</v>
       </c>
       <c r="P141" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -10984,7 +10990,7 @@
         <v>22</v>
       </c>
       <c r="P142" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="143" spans="1:16" ht="32">
@@ -11030,7 +11036,7 @@
         <v>22</v>
       </c>
       <c r="P143" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -11073,10 +11079,10 @@
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
       <c r="O144" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="P144" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -11119,10 +11125,10 @@
       <c r="M145" s="3"/>
       <c r="N145" s="3"/>
       <c r="O145" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="P145" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -11165,10 +11171,10 @@
       <c r="M146" s="3"/>
       <c r="N146" s="3"/>
       <c r="O146" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="P146" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -11211,10 +11217,10 @@
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
       <c r="O147" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="P147" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -11260,7 +11266,7 @@
         <v>22</v>
       </c>
       <c r="P148" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -11306,7 +11312,7 @@
         <v>22</v>
       </c>
       <c r="P149" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="150" spans="1:16" ht="32">
@@ -11356,7 +11362,7 @@
         <v>22</v>
       </c>
       <c r="P150" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -11404,7 +11410,7 @@
         <v>22</v>
       </c>
       <c r="P151" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -11450,7 +11456,7 @@
         <v>22</v>
       </c>
       <c r="P152" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -11496,7 +11502,7 @@
         <v>22</v>
       </c>
       <c r="P153" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -11542,7 +11548,7 @@
         <v>22</v>
       </c>
       <c r="P154" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="155" spans="1:16" ht="48">
@@ -11590,7 +11596,7 @@
         <v>22</v>
       </c>
       <c r="P155" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -11636,7 +11642,7 @@
         <v>22</v>
       </c>
       <c r="P156" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -11682,7 +11688,7 @@
         <v>22</v>
       </c>
       <c r="P157" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="32">
@@ -11732,7 +11738,7 @@
         <v>22</v>
       </c>
       <c r="P158" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -11778,7 +11784,7 @@
         <v>22</v>
       </c>
       <c r="P159" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="32">
@@ -11826,7 +11832,7 @@
         <v>22</v>
       </c>
       <c r="P160" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="161" spans="1:16" ht="32">
@@ -11876,7 +11882,7 @@
         <v>22</v>
       </c>
       <c r="P161" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -11922,7 +11928,7 @@
         <v>22</v>
       </c>
       <c r="P162" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="163" spans="1:16" ht="32">
@@ -11972,7 +11978,7 @@
         <v>22</v>
       </c>
       <c r="P163" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -12015,10 +12021,10 @@
       <c r="M164" s="3"/>
       <c r="N164" s="3"/>
       <c r="O164" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="P164" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -12061,10 +12067,10 @@
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
       <c r="O165" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="P165" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -12112,7 +12118,7 @@
         <v>22</v>
       </c>
       <c r="P166" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="167" spans="1:16" ht="32">
@@ -12159,10 +12165,10 @@
         <v>508</v>
       </c>
       <c r="O167" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="P167" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -12205,10 +12211,10 @@
       <c r="M168" s="3"/>
       <c r="N168" s="3"/>
       <c r="O168" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="P168" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -12251,10 +12257,10 @@
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
       <c r="O169" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="P169" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="170" spans="1:16" ht="32">
@@ -12302,7 +12308,7 @@
         <v>22</v>
       </c>
       <c r="P170" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -12345,10 +12351,10 @@
       <c r="M171" s="3"/>
       <c r="N171" s="3"/>
       <c r="O171" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="P171" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -12391,10 +12397,10 @@
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
       <c r="O172" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="P172" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -12437,10 +12443,10 @@
       <c r="M173" s="3"/>
       <c r="N173" s="3"/>
       <c r="O173" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="P173" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -12483,10 +12489,10 @@
       <c r="M174" s="3"/>
       <c r="N174" s="3"/>
       <c r="O174" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="P174" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -12529,10 +12535,10 @@
       <c r="M175" s="3"/>
       <c r="N175" s="3"/>
       <c r="O175" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="P175" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -12575,10 +12581,10 @@
       <c r="M176" s="3"/>
       <c r="N176" s="3"/>
       <c r="O176" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="P176" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -12621,10 +12627,10 @@
       <c r="M177" s="3"/>
       <c r="N177" s="3"/>
       <c r="O177" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="P177" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -12667,10 +12673,10 @@
       <c r="M178" s="3"/>
       <c r="N178" s="3"/>
       <c r="O178" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="P178" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -12713,10 +12719,10 @@
       <c r="M179" s="3"/>
       <c r="N179" s="3"/>
       <c r="O179" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="P179" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -12759,10 +12765,10 @@
       <c r="M180" s="3"/>
       <c r="N180" s="3"/>
       <c r="O180" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="P180" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -12805,10 +12811,10 @@
       <c r="M181" s="3"/>
       <c r="N181" s="3"/>
       <c r="O181" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="P181" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -12851,10 +12857,10 @@
       <c r="M182" s="3"/>
       <c r="N182" s="3"/>
       <c r="O182" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="P182" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -12900,7 +12906,7 @@
         <v>22</v>
       </c>
       <c r="P183" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -12943,10 +12949,10 @@
       <c r="M184" s="3"/>
       <c r="N184" s="3"/>
       <c r="O184" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="P184" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -12989,10 +12995,10 @@
       <c r="M185" s="3"/>
       <c r="N185" s="3"/>
       <c r="O185" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="P185" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -13035,10 +13041,10 @@
       <c r="M186" s="3"/>
       <c r="N186" s="3"/>
       <c r="O186" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="P186" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="48">
@@ -13085,10 +13091,10 @@
         <v>205</v>
       </c>
       <c r="O187" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="P187" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -13134,7 +13140,7 @@
         <v>22</v>
       </c>
       <c r="P188" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -13177,10 +13183,10 @@
       <c r="M189" s="3"/>
       <c r="N189" s="3"/>
       <c r="O189" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="P189" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="190" spans="1:16" ht="32">
@@ -13230,7 +13236,7 @@
         <v>22</v>
       </c>
       <c r="P190" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -13273,10 +13279,10 @@
       <c r="M191" s="3"/>
       <c r="N191" s="3"/>
       <c r="O191" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="P191" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="192" spans="1:16" ht="32">
@@ -13323,10 +13329,10 @@
         <v>704</v>
       </c>
       <c r="O192" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="P192" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -13370,10 +13376,10 @@
         <v>909</v>
       </c>
       <c r="O193" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="P193" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -13417,10 +13423,10 @@
         <v>914</v>
       </c>
       <c r="O194" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="P194" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="195" spans="1:16">
@@ -13464,10 +13470,10 @@
         <v>919</v>
       </c>
       <c r="O195" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="P195" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -13511,10 +13517,10 @@
         <v>924</v>
       </c>
       <c r="O196" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="P196" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -13558,10 +13564,10 @@
         <v>929</v>
       </c>
       <c r="O197" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="P197" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -13605,10 +13611,10 @@
         <v>934</v>
       </c>
       <c r="O198" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="P198" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -13652,10 +13658,10 @@
         <v>938</v>
       </c>
       <c r="O199" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="P199" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -13699,10 +13705,10 @@
         <v>943</v>
       </c>
       <c r="O200" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="P200" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -13746,10 +13752,10 @@
         <v>948</v>
       </c>
       <c r="O201" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="P201" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -13793,10 +13799,10 @@
         <v>952</v>
       </c>
       <c r="O202" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="P202" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -13840,10 +13846,10 @@
         <v>956</v>
       </c>
       <c r="O203" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="P203" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -13887,10 +13893,10 @@
         <v>960</v>
       </c>
       <c r="O204" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="P204" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -13934,10 +13940,10 @@
         <v>964</v>
       </c>
       <c r="O205" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="P205" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -13981,10 +13987,10 @@
         <v>968</v>
       </c>
       <c r="O206" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="P206" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -14028,10 +14034,10 @@
         <v>972</v>
       </c>
       <c r="O207" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="P207" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -14075,10 +14081,10 @@
         <v>977</v>
       </c>
       <c r="O208" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="P208" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="209" spans="1:16">
@@ -14122,10 +14128,10 @@
         <v>981</v>
       </c>
       <c r="O209" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="P209" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="210" spans="1:16">
@@ -14169,10 +14175,10 @@
         <v>985</v>
       </c>
       <c r="O210" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="P210" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -14216,10 +14222,10 @@
         <v>989</v>
       </c>
       <c r="O211" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="P211" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -14263,10 +14269,10 @@
         <v>994</v>
       </c>
       <c r="O212" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="P212" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -14310,10 +14316,10 @@
         <v>998</v>
       </c>
       <c r="O213" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="P213" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -14357,10 +14363,10 @@
         <v>1002</v>
       </c>
       <c r="O214" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="P214" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -14404,10 +14410,10 @@
         <v>1006</v>
       </c>
       <c r="O215" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="P215" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="216" spans="1:16">
@@ -14451,10 +14457,10 @@
         <v>1010</v>
       </c>
       <c r="O216" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="P216" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="217" spans="1:16">
@@ -14498,10 +14504,10 @@
         <v>1014</v>
       </c>
       <c r="O217" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="P217" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="218" spans="1:16">
@@ -14545,10 +14551,10 @@
         <v>1018</v>
       </c>
       <c r="O218" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="P218" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="219" spans="1:16">
@@ -14592,10 +14598,10 @@
         <v>1022</v>
       </c>
       <c r="O219" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="P219" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="220" spans="1:16">
@@ -14639,10 +14645,10 @@
         <v>1026</v>
       </c>
       <c r="O220" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="P220" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="221" spans="1:16">
@@ -14686,10 +14692,20 @@
         <v>1030</v>
       </c>
       <c r="O221" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="P221" t="s">
-        <v>1039</v>
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16">
+      <c r="A222" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16">
+      <c r="A223" t="s">
+        <v>1167</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D1811C-1C79-4CEB-B38F-1286F3D2EE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DA9DA6-8DA7-416B-8ED8-BC01B2345FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="1177">
   <si>
     <t>ID</t>
   </si>
@@ -3656,14 +3656,40 @@
     <t>검수결과 시트 오른쪽에 「계약서 문구 ID」와 「연결 상태」 두 열을 두었다. 연결 상태가 「계약서에 없음」인 항목은 검수는 했으나 데이터계약 목표문구에 올라가 있지 않은 것이다. 2026-10-06 기준 연결 128 · 없음 92.</t>
   </si>
   <si>
-    <t>N221 6차 회복 풀 회복 영양 상담 예약 확인하기 영양 상담 예약 확인하기 13 신장질환 식사는 개인별 영양 상담이 도움이 돼요. — 근거 확인 필요 (질환규칙 DX-05 개별화 원칙) — 검수 대기  2026-10-07 추가. 만성 신장질환처럼 먹는 양을 늘리라고 자동으로 말할 수 없는 사용자의 결식 시 문구. 먹는 양을 바꾸지 않음. 계약서 미반영 — 계약서에 없음</t>
-  </si>
-  <si>
-    <t>N222 6차 회복 풀 회복 식사 시간 정해 두기 식사 시간 정해 두기 11 시간이 일정하면 끼니를 놓치기 어려워요. — 근거 확인 필요 (질환규칙 DX-05 개별화 원칙) — 검수 대기  2026-10-07 추가. 만성 신장질환처럼 먹는 양을 늘리라고 자동으로 말할 수 없는 사용자의 결식 시 문구. 먹는 양을 바꾸지 않음. 계약서 미반영 — 계약서에 없음</t>
-  </si>
-  <si>
     <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다. 2026-10-07에 만성 신장질환 결식 시 쓸 회복 풀 문구 2개를 6차로 올렸고 이 2개도 검수 전이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N221</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6차</t>
+  </si>
+  <si>
+    <t>입맛 없는 날 적어 두기</t>
+  </si>
+  <si>
+    <t>식욕이 떨어지는 때를 알면 식사를 챙기기 쉬워요.</t>
+  </si>
+  <si>
+    <t>근거 확인 필요 (질환규칙 DX-05 개별화 원칙)</t>
+  </si>
+  <si>
+    <t>2026-10-07 추가. 먹는 양을 바꾸지 않는 기록 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있고, 진료나 상담을 받지 않는 사용자도 실행할 수 있다. 계약서 미반영</t>
+  </si>
+  <si>
+    <t>N222</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식사 시간 정해 두기</t>
+  </si>
+  <si>
+    <t>시간이 일정하면 끼니를 놓치기 어려워요.</t>
+  </si>
+  <si>
+    <t>2026-10-07 추가. 먹는 양이 아니라 규칙성만 다루는 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있다. 계약서 미반영</t>
   </si>
 </sst>
 </file>
@@ -4231,7 +4257,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -14700,12 +14726,96 @@
     </row>
     <row r="222" spans="1:16">
       <c r="A222" t="s">
-        <v>1166</v>
+        <v>1167</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C222" t="s">
+        <v>199</v>
+      </c>
+      <c r="D222" t="s">
+        <v>200</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G222">
+        <v>13</v>
+      </c>
+      <c r="H222" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I222" t="s">
+        <v>22</v>
+      </c>
+      <c r="J222" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K222" t="s">
+        <v>22</v>
+      </c>
+      <c r="L222" t="s">
+        <v>908</v>
+      </c>
+      <c r="N222" t="s">
+        <v>1172</v>
+      </c>
+      <c r="O222" t="s">
+        <v>22</v>
+      </c>
+      <c r="P222" t="s">
+        <v>1035</v>
       </c>
     </row>
     <row r="223" spans="1:16">
       <c r="A223" t="s">
-        <v>1167</v>
+        <v>1173</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C223" t="s">
+        <v>199</v>
+      </c>
+      <c r="D223" t="s">
+        <v>200</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G223">
+        <v>11</v>
+      </c>
+      <c r="H223" t="s">
+        <v>1175</v>
+      </c>
+      <c r="I223" t="s">
+        <v>22</v>
+      </c>
+      <c r="J223" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K223" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" t="s">
+        <v>908</v>
+      </c>
+      <c r="N223" t="s">
+        <v>1176</v>
+      </c>
+      <c r="O223" t="s">
+        <v>22</v>
+      </c>
+      <c r="P223" t="s">
+        <v>1035</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63DA9DA6-8DA7-416B-8ED8-BC01B2345FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC687F-B39A-4F4B-9932-FAE165AE65D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="1191">
   <si>
     <t>ID</t>
   </si>
@@ -3656,10 +3656,6 @@
     <t>검수결과 시트 오른쪽에 「계약서 문구 ID」와 「연결 상태」 두 열을 두었다. 연결 상태가 「계약서에 없음」인 항목은 검수는 했으나 데이터계약 목표문구에 올라가 있지 않은 것이다. 2026-10-06 기준 연결 128 · 없음 92.</t>
   </si>
   <si>
-    <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다. 2026-10-07에 만성 신장질환 결식 시 쓸 회복 풀 문구 2개를 6차로 올렸고 이 2개도 검수 전이다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>N221</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3690,6 +3686,52 @@
   </si>
   <si>
     <t>2026-10-07 추가. 먹는 양이 아니라 규칙성만 다루는 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있다. 계약서 미반영</t>
+  </si>
+  <si>
+    <t>N223</t>
+  </si>
+  <si>
+    <t>출출하면 가볍게 요기하기</t>
+  </si>
+  <si>
+    <t>저녁을 적게 먹어 허기가 지면 소화가 편한 음식을 조금 먹어요.</t>
+  </si>
+  <si>
+    <t>자정 전</t>
+  </si>
+  <si>
+    <t>2026-10-07 추가. 저녁에 「조금 적게」「거의 못 먹거나 걸렀어요」를 답한 사용자의 회복 목표. 증량 성격이라 만성 신장질환은 기존 규칙대로 제외. 기획·가정의학 관점 검토 후 승인</t>
+  </si>
+  <si>
+    <t>DIET-P-0269</t>
+  </si>
+  <si>
+    <t>N224</t>
+  </si>
+  <si>
+    <t>따뜻한 우유나 두유 한 잔</t>
+  </si>
+  <si>
+    <t>따뜻한 음료로 속을 달래며 부족한 한 끼를 조금 채워요. 한 끼 전체를 대신하지는 않아요.</t>
+  </si>
+  <si>
+    <t>DIET-P-0270</t>
+  </si>
+  <si>
+    <t>N225</t>
+  </si>
+  <si>
+    <t>내일 아침 챙길 것 준비하기</t>
+  </si>
+  <si>
+    <t>저녁을 적게 먹은 날은 내일 아침거리를 미리 준비해 둬요.</t>
+  </si>
+  <si>
+    <t>DIET-P-0271</t>
+  </si>
+  <si>
+    <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다. 2026-10-07에 만성 신장질환 결식 시 쓸 회복 풀 문구 2개를 6차로 올렸고 이 2개도 검수 전이다. 2026-10-07에 저녁 회복 문구 3개를 6차로 올리고 승인했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4257,7 +4299,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
-        <v>1166</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4283,7 +4325,7 @@
       </c>
       <c r="C5" s="5">
         <f>COUNTIF(검수결과!L:L,"승인")</f>
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>777</v>
@@ -4371,7 +4413,7 @@
       <c r="B11" s="5"/>
       <c r="C11" s="6">
         <f>SUM(C5:C10)</f>
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D11" s="5"/>
     </row>
@@ -4418,7 +4460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEA781C-07E7-4393-BF75-138E1A6EB613}">
-  <dimension ref="A1:P223"/>
+  <dimension ref="A1:P226"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="2" width="7.58203125" customWidth="1"/>
@@ -14726,10 +14768,10 @@
     </row>
     <row r="222" spans="1:16">
       <c r="A222" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B222" t="s">
         <v>1167</v>
-      </c>
-      <c r="B222" t="s">
-        <v>1168</v>
       </c>
       <c r="C222" t="s">
         <v>199</v>
@@ -14738,22 +14780,22 @@
         <v>200</v>
       </c>
       <c r="E222" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="F222" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G222">
         <v>13</v>
       </c>
       <c r="H222" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I222" t="s">
+        <v>22</v>
+      </c>
+      <c r="J222" t="s">
         <v>1170</v>
-      </c>
-      <c r="I222" t="s">
-        <v>22</v>
-      </c>
-      <c r="J222" t="s">
-        <v>1171</v>
       </c>
       <c r="K222" t="s">
         <v>22</v>
@@ -14762,7 +14804,7 @@
         <v>908</v>
       </c>
       <c r="N222" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="O222" t="s">
         <v>22</v>
@@ -14773,10 +14815,10 @@
     </row>
     <row r="223" spans="1:16">
       <c r="A223" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B223" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="C223" t="s">
         <v>199</v>
@@ -14785,22 +14827,22 @@
         <v>200</v>
       </c>
       <c r="E223" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="F223" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="G223">
         <v>11</v>
       </c>
       <c r="H223" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="I223" t="s">
         <v>22</v>
       </c>
       <c r="J223" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="K223" t="s">
         <v>22</v>
@@ -14809,13 +14851,154 @@
         <v>908</v>
       </c>
       <c r="N223" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="O223" t="s">
         <v>22</v>
       </c>
       <c r="P223" t="s">
         <v>1035</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16">
+      <c r="A224" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C224" t="s">
+        <v>199</v>
+      </c>
+      <c r="D224" t="s">
+        <v>200</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1177</v>
+      </c>
+      <c r="G224">
+        <v>13</v>
+      </c>
+      <c r="H224" t="s">
+        <v>1178</v>
+      </c>
+      <c r="I224" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J224" t="s">
+        <v>993</v>
+      </c>
+      <c r="K224" t="s">
+        <v>22</v>
+      </c>
+      <c r="L224" t="s">
+        <v>23</v>
+      </c>
+      <c r="N224" t="s">
+        <v>1180</v>
+      </c>
+      <c r="O224" t="s">
+        <v>1181</v>
+      </c>
+      <c r="P224" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16">
+      <c r="A225" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C225" t="s">
+        <v>199</v>
+      </c>
+      <c r="D225" t="s">
+        <v>200</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1183</v>
+      </c>
+      <c r="G225">
+        <v>14</v>
+      </c>
+      <c r="H225" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I225" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J225" t="s">
+        <v>993</v>
+      </c>
+      <c r="K225" t="s">
+        <v>22</v>
+      </c>
+      <c r="L225" t="s">
+        <v>23</v>
+      </c>
+      <c r="N225" t="s">
+        <v>1180</v>
+      </c>
+      <c r="O225" t="s">
+        <v>1185</v>
+      </c>
+      <c r="P225" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16">
+      <c r="A226" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C226" t="s">
+        <v>199</v>
+      </c>
+      <c r="D226" t="s">
+        <v>200</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G226">
+        <v>15</v>
+      </c>
+      <c r="H226" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I226" t="s">
+        <v>1179</v>
+      </c>
+      <c r="J226" t="s">
+        <v>993</v>
+      </c>
+      <c r="K226" t="s">
+        <v>22</v>
+      </c>
+      <c r="L226" t="s">
+        <v>23</v>
+      </c>
+      <c r="N226" t="s">
+        <v>1180</v>
+      </c>
+      <c r="O226" t="s">
+        <v>1189</v>
+      </c>
+      <c r="P226" t="s">
+        <v>1038</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC687F-B39A-4F4B-9932-FAE165AE65D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9D66DD-6FCD-4A15-AA59-940687ACDECE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="1191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3129" uniqueCount="1196">
   <si>
     <t>ID</t>
   </si>
@@ -3669,12 +3669,6 @@
     <t>식욕이 떨어지는 때를 알면 식사를 챙기기 쉬워요.</t>
   </si>
   <si>
-    <t>근거 확인 필요 (질환규칙 DX-05 개별화 원칙)</t>
-  </si>
-  <si>
-    <t>2026-10-07 추가. 먹는 양을 바꾸지 않는 기록 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있고, 진료나 상담을 받지 않는 사용자도 실행할 수 있다. 계약서 미반영</t>
-  </si>
-  <si>
     <t>N222</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3685,9 +3679,6 @@
     <t>시간이 일정하면 끼니를 놓치기 어려워요.</t>
   </si>
   <si>
-    <t>2026-10-07 추가. 먹는 양이 아니라 규칙성만 다루는 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있다. 계약서 미반영</t>
-  </si>
-  <si>
     <t>N223</t>
   </si>
   <si>
@@ -3731,6 +3722,38 @@
   </si>
   <si>
     <t>확장 초안 191개를 가정의학 임상 관점에서 검수했다. 실제 의학팀 최종 승인을 대체하지 않는다 — 쟁점 8번 참조. 2026-10-06에 국내외 학회 가이드라인 근거 문구 29개를 5차로 올렸고 이 29개는 아직 검수 전이다. 2026-10-07에 만성 신장질환 결식 시 쓸 회복 풀 문구 2개를 6차로 올렸고 이 2개도 검수 전이다. 2026-10-07에 저녁 회복 문구 3개를 6차로 올리고 승인했다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>승인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 확인 필요 (기록 행동, 섭취 지시 없음)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-07 추가. 먹는 양을 바꾸지 않는 기록 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있고, 진료나 상담을 받지 않는 사용자도 실행할 수 있다. 계약서 DIET-P-0272. 기획·가정의학 관점 검토 후 승인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIET-P-0272</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>문구 그대로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOHW-DIETGUIDE (식생활지침 규칙성)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-07 추가. 먹는 양이 아니라 규칙성만 다루는 행동이라 만성 신장질환 사용자의 결식 시에도 쓸 수 있다. 계약서 DIET-P-0273. 기획·가정의학 관점 검토 후 승인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DIET-P-0273</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4299,7 +4322,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -4325,7 +4348,7 @@
       </c>
       <c r="C5" s="5">
         <f>COUNTIF(검수결과!L:L,"승인")</f>
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>777</v>
@@ -4413,7 +4436,7 @@
       <c r="B11" s="5"/>
       <c r="C11" s="6">
         <f>SUM(C5:C10)</f>
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D11" s="5"/>
     </row>
@@ -14795,27 +14818,27 @@
         <v>22</v>
       </c>
       <c r="J222" t="s">
-        <v>1170</v>
+        <v>1189</v>
       </c>
       <c r="K222" t="s">
         <v>22</v>
       </c>
       <c r="L222" t="s">
-        <v>908</v>
+        <v>1188</v>
       </c>
       <c r="N222" t="s">
-        <v>1171</v>
+        <v>1190</v>
       </c>
       <c r="O222" t="s">
-        <v>22</v>
+        <v>1191</v>
       </c>
       <c r="P222" t="s">
-        <v>1035</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="223" spans="1:16">
       <c r="A223" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="B223" t="s">
         <v>1167</v>
@@ -14827,42 +14850,42 @@
         <v>200</v>
       </c>
       <c r="E223" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F223" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="G223">
         <v>11</v>
       </c>
       <c r="H223" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="I223" t="s">
         <v>22</v>
       </c>
       <c r="J223" t="s">
-        <v>1170</v>
+        <v>1193</v>
       </c>
       <c r="K223" t="s">
         <v>22</v>
       </c>
       <c r="L223" t="s">
-        <v>908</v>
+        <v>1188</v>
       </c>
       <c r="N223" t="s">
-        <v>1175</v>
+        <v>1194</v>
       </c>
       <c r="O223" t="s">
-        <v>22</v>
+        <v>1195</v>
       </c>
       <c r="P223" t="s">
-        <v>1035</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="224" spans="1:16">
       <c r="A224" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B224" t="s">
         <v>1167</v>
@@ -14874,19 +14897,19 @@
         <v>200</v>
       </c>
       <c r="E224" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="F224" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="G224">
         <v>13</v>
       </c>
       <c r="H224" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="I224" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="J224" t="s">
         <v>993</v>
@@ -14898,10 +14921,10 @@
         <v>23</v>
       </c>
       <c r="N224" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="O224" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="P224" t="s">
         <v>1038</v>
@@ -14909,7 +14932,7 @@
     </row>
     <row r="225" spans="1:16">
       <c r="A225" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="B225" t="s">
         <v>1167</v>
@@ -14921,19 +14944,19 @@
         <v>200</v>
       </c>
       <c r="E225" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="F225" t="s">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="G225">
         <v>14</v>
       </c>
       <c r="H225" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="I225" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="J225" t="s">
         <v>993</v>
@@ -14945,10 +14968,10 @@
         <v>23</v>
       </c>
       <c r="N225" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="O225" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="P225" t="s">
         <v>1038</v>
@@ -14956,7 +14979,7 @@
     </row>
     <row r="226" spans="1:16">
       <c r="A226" t="s">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="B226" t="s">
         <v>1167</v>
@@ -14968,19 +14991,19 @@
         <v>200</v>
       </c>
       <c r="E226" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="F226" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="G226">
         <v>15</v>
       </c>
       <c r="H226" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="I226" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="J226" t="s">
         <v>993</v>
@@ -14992,10 +15015,10 @@
         <v>23</v>
       </c>
       <c r="N226" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="O226" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="P226" t="s">
         <v>1038</v>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31F79BB-2334-40B9-9473-AFCB17CF0950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A29011A-1EF6-4FF9-B686-DC83AB60AEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
   <sheets>
     <sheet name="안내" sheetId="1" r:id="rId1"/>
@@ -3781,14 +3781,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
@@ -3798,6 +3790,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF808080"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
@@ -3865,9 +3865,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3877,7 +3874,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3904,7 +3901,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -4285,47 +4285,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2597341E-3ECD-41D3-B650-670B60F066B4}">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="60.59765625" customWidth="1"/>
-    <col min="2" max="2" width="34.59765625" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="4" max="4" width="28.59765625" customWidth="1"/>
+    <col min="1" max="1" width="60.58203125" customWidth="1"/>
+    <col min="2" max="2" width="34.58203125" customWidth="1"/>
+    <col min="3" max="3" width="10.58203125" customWidth="1"/>
+    <col min="4" max="4" width="28.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>769</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-    </row>
-    <row r="2" spans="1:4" ht="78">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" ht="80">
+      <c r="A2" s="7" t="s">
         <v>1181</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="10"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>770</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>771</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>772</v>
       </c>
     </row>
@@ -4420,83 +4420,83 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>785</v>
       </c>
       <c r="B11" s="1"/>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <f>SUM(C5:C10)</f>
         <v>195</v>
       </c>
       <c r="D11" s="1"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="10"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>786</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:4" ht="31.2">
-      <c r="A14" s="16" t="s">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+    </row>
+    <row r="14" spans="1:4" ht="32">
+      <c r="A14" s="15" t="s">
         <v>787</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:4" ht="31.2">
-      <c r="A15" s="16" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+    </row>
+    <row r="15" spans="1:4" ht="32">
+      <c r="A15" s="15" t="s">
         <v>788</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:4" ht="31.2">
-      <c r="A16" s="16" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:4" ht="32">
+      <c r="A16" s="15" t="s">
         <v>789</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4" ht="31.2">
-      <c r="A17" s="16" t="s">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="1:4" ht="32">
+      <c r="A17" s="15" t="s">
         <v>790</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="10"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>1158</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-    </row>
-    <row r="20" spans="1:4" ht="46.8">
-      <c r="A20" s="10" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" ht="48">
+      <c r="A20" s="9" t="s">
         <v>1159</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4507,25 +4507,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBEA781C-07E7-4393-BF75-138E1A6EB613}">
   <dimension ref="A1:P225"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="2" width="10.59765625" customWidth="1"/>
-    <col min="3" max="3" width="16.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.59765625" customWidth="1"/>
-    <col min="5" max="6" width="29.59765625" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" customWidth="1"/>
-    <col min="8" max="8" width="60.59765625" customWidth="1"/>
-    <col min="9" max="9" width="16.59765625" customWidth="1"/>
-    <col min="10" max="10" width="46.59765625" customWidth="1"/>
-    <col min="11" max="11" width="29.59765625" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" customWidth="1"/>
-    <col min="13" max="13" width="22.59765625" customWidth="1"/>
-    <col min="14" max="14" width="60.59765625" customWidth="1"/>
-    <col min="15" max="15" width="14.59765625" customWidth="1"/>
-    <col min="16" max="16" width="21.59765625" customWidth="1"/>
+    <col min="1" max="2" width="10.58203125" customWidth="1"/>
+    <col min="3" max="3" width="16.58203125" customWidth="1"/>
+    <col min="4" max="4" width="10.58203125" customWidth="1"/>
+    <col min="5" max="6" width="29.58203125" customWidth="1"/>
+    <col min="7" max="7" width="10.58203125" customWidth="1"/>
+    <col min="8" max="8" width="60.58203125" customWidth="1"/>
+    <col min="9" max="9" width="16.58203125" customWidth="1"/>
+    <col min="10" max="10" width="46.58203125" customWidth="1"/>
+    <col min="11" max="11" width="29.58203125" customWidth="1"/>
+    <col min="12" max="12" width="10.58203125" customWidth="1"/>
+    <col min="13" max="13" width="22.58203125" customWidth="1"/>
+    <col min="14" max="14" width="60.58203125" customWidth="1"/>
+    <col min="15" max="15" width="14.58203125" customWidth="1"/>
+    <col min="16" max="16" width="21.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="28.05" customHeight="1">
+    <row r="1" spans="1:16" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4568,10 +4568,10 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>1026</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="6" t="s">
         <v>1027</v>
       </c>
     </row>
@@ -4588,7 +4588,7 @@
       <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="16" t="s">
         <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -4614,14 +4614,14 @@
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="9" t="s">
+      <c r="O2" s="8" t="s">
         <v>1028</v>
       </c>
-      <c r="P2" s="9" t="s">
+      <c r="P2" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="62.4">
+    <row r="3" spans="1:16" ht="64">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
@@ -4634,7 +4634,7 @@
       <c r="D3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="16" t="s">
         <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -4662,10 +4662,10 @@
       <c r="N3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="9" t="s">
+      <c r="O3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P3" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -4682,13 +4682,13 @@
       <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="16" t="s">
         <v>842</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="17" t="s">
         <v>813</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="17">
         <v>8</v>
       </c>
       <c r="H4" s="3" t="s">
@@ -4708,10 +4708,10 @@
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="3"/>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -4728,13 +4728,13 @@
       <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>843</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="17" t="s">
         <v>791</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="17">
         <v>10</v>
       </c>
       <c r="H5" s="3" t="s">
@@ -4754,10 +4754,10 @@
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="P5" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -4774,13 +4774,13 @@
       <c r="D6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>844</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="17" t="s">
         <v>792</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="17">
         <v>10</v>
       </c>
       <c r="H6" s="3" t="s">
@@ -4800,10 +4800,10 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="8" t="s">
         <v>1034</v>
       </c>
-      <c r="P6" s="9" t="s">
+      <c r="P6" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -4820,13 +4820,13 @@
       <c r="D7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>845</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="17" t="s">
         <v>793</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="17">
         <v>11</v>
       </c>
       <c r="H7" s="3" t="s">
@@ -4846,10 +4846,10 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="8" t="s">
         <v>1035</v>
       </c>
-      <c r="P7" s="9" t="s">
+      <c r="P7" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -4866,13 +4866,13 @@
       <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="16" t="s">
         <v>846</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="17" t="s">
         <v>794</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="17">
         <v>12</v>
       </c>
       <c r="H8" s="3" t="s">
@@ -4892,10 +4892,10 @@
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="8" t="s">
         <v>1036</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -4912,10 +4912,10 @@
       <c r="D9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>847</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="17" t="s">
         <v>795</v>
       </c>
       <c r="G9" s="1">
@@ -4938,10 +4938,10 @@
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="9" t="s">
+      <c r="O9" s="8" t="s">
         <v>1037</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="P9" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       <c r="D10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="16" t="s">
         <v>53</v>
       </c>
       <c r="F10" s="1" t="s">
@@ -4984,10 +4984,10 @@
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="9" t="s">
+      <c r="O10" s="8" t="s">
         <v>1038</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -5004,13 +5004,13 @@
       <c r="D11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>848</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="17" t="s">
         <v>814</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="17">
         <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
@@ -5030,10 +5030,10 @@
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="9" t="s">
+      <c r="O11" s="8" t="s">
         <v>1039</v>
       </c>
-      <c r="P11" s="9" t="s">
+      <c r="P11" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="16" t="s">
         <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -5076,10 +5076,10 @@
       </c>
       <c r="M12" s="1"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="P12" s="9" t="s">
+      <c r="P12" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -5096,7 +5096,7 @@
       <c r="D13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -5122,10 +5122,10 @@
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="8" t="s">
         <v>1041</v>
       </c>
-      <c r="P13" s="9" t="s">
+      <c r="P13" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       <c r="D14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="16" t="s">
         <v>68</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -5168,10 +5168,10 @@
       </c>
       <c r="M14" s="1"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="9" t="s">
+      <c r="O14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5188,13 +5188,13 @@
       <c r="D15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="16" t="s">
         <v>849</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="17" t="s">
         <v>796</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="17">
         <v>10</v>
       </c>
       <c r="H15" s="3" t="s">
@@ -5214,10 +5214,10 @@
       </c>
       <c r="M15" s="1"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="9" t="s">
+      <c r="O15" s="8" t="s">
         <v>1042</v>
       </c>
-      <c r="P15" s="9" t="s">
+      <c r="P15" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       <c r="D16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="16" t="s">
         <v>76</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -5260,10 +5260,10 @@
       </c>
       <c r="M16" s="1"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="9" t="s">
+      <c r="O16" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="P16" s="9" t="s">
+      <c r="P16" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -5280,13 +5280,13 @@
       <c r="D17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="16" t="s">
         <v>850</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="17" t="s">
         <v>815</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G17" s="17">
         <v>9</v>
       </c>
       <c r="H17" s="3" t="s">
@@ -5306,10 +5306,10 @@
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="9" t="s">
+      <c r="O17" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="P17" s="9" t="s">
+      <c r="P17" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       <c r="D18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="16" t="s">
         <v>83</v>
       </c>
       <c r="F18" s="1" t="s">
@@ -5352,10 +5352,10 @@
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="9" t="s">
+      <c r="O18" s="8" t="s">
         <v>1045</v>
       </c>
-      <c r="P18" s="9" t="s">
+      <c r="P18" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -5372,13 +5372,13 @@
       <c r="D19" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="16" t="s">
         <v>851</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="17" t="s">
         <v>816</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="17">
         <v>11</v>
       </c>
       <c r="H19" s="3" t="s">
@@ -5398,10 +5398,10 @@
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="9" t="s">
+      <c r="O19" s="8" t="s">
         <v>1046</v>
       </c>
-      <c r="P19" s="9" t="s">
+      <c r="P19" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -5418,13 +5418,13 @@
       <c r="D20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="16" t="s">
         <v>852</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="17" t="s">
         <v>817</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="17">
         <v>10</v>
       </c>
       <c r="H20" s="3" t="s">
@@ -5444,10 +5444,10 @@
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="3"/>
-      <c r="O20" s="9" t="s">
+      <c r="O20" s="8" t="s">
         <v>1047</v>
       </c>
-      <c r="P20" s="9" t="s">
+      <c r="P20" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -5464,13 +5464,13 @@
       <c r="D21" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="E21" s="16" t="s">
         <v>853</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="17" t="s">
         <v>797</v>
       </c>
-      <c r="G21" s="4">
+      <c r="G21" s="17">
         <v>8</v>
       </c>
       <c r="H21" s="3" t="s">
@@ -5490,10 +5490,10 @@
       </c>
       <c r="M21" s="1"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="9" t="s">
+      <c r="O21" s="8" t="s">
         <v>1048</v>
       </c>
-      <c r="P21" s="9" t="s">
+      <c r="P21" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -5510,7 +5510,7 @@
       <c r="D22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="16" t="s">
         <v>95</v>
       </c>
       <c r="F22" s="1" t="s">
@@ -5536,10 +5536,10 @@
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="3"/>
-      <c r="O22" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P22" s="9" t="s">
+      <c r="O22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       <c r="D23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="16" t="s">
         <v>101</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -5582,14 +5582,14 @@
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P23" s="9" t="s">
+      <c r="O23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="31.2">
+    <row r="24" spans="1:16" ht="32">
       <c r="A24" s="1" t="s">
         <v>105</v>
       </c>
@@ -5602,7 +5602,7 @@
       <c r="D24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -5630,10 +5630,10 @@
       <c r="N24" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="O24" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P24" s="9" t="s">
+      <c r="O24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5650,7 +5650,7 @@
       <c r="D25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="17" t="s">
+      <c r="E25" s="16" t="s">
         <v>114</v>
       </c>
       <c r="F25" s="1" t="s">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="3"/>
-      <c r="O25" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P25" s="9" t="s">
+      <c r="O25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="31.2">
+    <row r="26" spans="1:16" ht="32">
       <c r="A26" s="1" t="s">
         <v>117</v>
       </c>
@@ -5696,7 +5696,7 @@
       <c r="D26" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="16" t="s">
         <v>118</v>
       </c>
       <c r="F26" s="1" t="s">
@@ -5724,14 +5724,14 @@
       <c r="N26" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="O26" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P26" s="9" t="s">
+      <c r="O26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="46.8">
+    <row r="27" spans="1:16" ht="48">
       <c r="A27" s="1" t="s">
         <v>123</v>
       </c>
@@ -5744,7 +5744,7 @@
       <c r="D27" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E27" s="17" t="s">
+      <c r="E27" s="16" t="s">
         <v>124</v>
       </c>
       <c r="F27" s="1" t="s">
@@ -5774,10 +5774,10 @@
       <c r="N27" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="O27" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P27" s="9" t="s">
+      <c r="O27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5794,7 +5794,7 @@
       <c r="D28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="16" t="s">
         <v>132</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -5820,10 +5820,10 @@
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="3"/>
-      <c r="O28" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P28" s="9" t="s">
+      <c r="O28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5840,13 +5840,13 @@
       <c r="D29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="17" t="s">
+      <c r="E29" s="16" t="s">
         <v>854</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="17" t="s">
         <v>818</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="17">
         <v>9</v>
       </c>
       <c r="H29" s="3" t="s">
@@ -5866,14 +5866,14 @@
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="3"/>
-      <c r="O29" s="9" t="s">
+      <c r="O29" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="P29" s="9" t="s">
+      <c r="P29" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="46.8">
+    <row r="30" spans="1:16" ht="48">
       <c r="A30" s="1" t="s">
         <v>137</v>
       </c>
@@ -5886,7 +5886,7 @@
       <c r="D30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>138</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -5916,14 +5916,14 @@
       <c r="N30" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="O30" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P30" s="9" t="s">
+      <c r="O30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="46.8">
+    <row r="31" spans="1:16" ht="48">
       <c r="A31" s="1" t="s">
         <v>144</v>
       </c>
@@ -5936,7 +5936,7 @@
       <c r="D31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="17" t="s">
+      <c r="E31" s="16" t="s">
         <v>145</v>
       </c>
       <c r="F31" s="1" t="s">
@@ -5966,10 +5966,10 @@
       <c r="N31" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="O31" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P31" s="9" t="s">
+      <c r="O31" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       <c r="D32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E32" s="17" t="s">
+      <c r="E32" s="16" t="s">
         <v>149</v>
       </c>
       <c r="F32" s="1" t="s">
@@ -6012,10 +6012,10 @@
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="3"/>
-      <c r="O32" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P32" s="9" t="s">
+      <c r="O32" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       <c r="D33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>154</v>
       </c>
       <c r="F33" s="1" t="s">
@@ -6058,10 +6058,10 @@
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="3"/>
-      <c r="O33" s="9" t="s">
+      <c r="O33" s="8" t="s">
         <v>1050</v>
       </c>
-      <c r="P33" s="9" t="s">
+      <c r="P33" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6078,13 +6078,13 @@
       <c r="D34" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="16" t="s">
         <v>855</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="17" t="s">
         <v>798</v>
       </c>
-      <c r="G34" s="4">
+      <c r="G34" s="17">
         <v>11</v>
       </c>
       <c r="H34" s="3" t="s">
@@ -6104,10 +6104,10 @@
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="9" t="s">
+      <c r="O34" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="P34" s="9" t="s">
+      <c r="P34" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       <c r="D35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E35" s="17" t="s">
+      <c r="E35" s="16" t="s">
         <v>162</v>
       </c>
       <c r="F35" s="1" t="s">
@@ -6150,10 +6150,10 @@
       </c>
       <c r="M35" s="1"/>
       <c r="N35" s="3"/>
-      <c r="O35" s="9" t="s">
+      <c r="O35" s="8" t="s">
         <v>1052</v>
       </c>
-      <c r="P35" s="9" t="s">
+      <c r="P35" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
       <c r="D36" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E36" s="17" t="s">
+      <c r="E36" s="16" t="s">
         <v>167</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -6196,10 +6196,10 @@
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="3"/>
-      <c r="O36" s="9" t="s">
+      <c r="O36" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="P36" s="9" t="s">
+      <c r="P36" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6216,13 +6216,13 @@
       <c r="D37" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E37" s="17" t="s">
+      <c r="E37" s="16" t="s">
         <v>856</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F37" s="17" t="s">
         <v>819</v>
       </c>
-      <c r="G37" s="4">
+      <c r="G37" s="17">
         <v>11</v>
       </c>
       <c r="H37" s="3" t="s">
@@ -6242,10 +6242,10 @@
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="3"/>
-      <c r="O37" s="9" t="s">
+      <c r="O37" s="8" t="s">
         <v>1054</v>
       </c>
-      <c r="P37" s="9" t="s">
+      <c r="P37" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6262,13 +6262,13 @@
       <c r="D38" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E38" s="17" t="s">
+      <c r="E38" s="16" t="s">
         <v>857</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="F38" s="17" t="s">
         <v>799</v>
       </c>
-      <c r="G38" s="4">
+      <c r="G38" s="17">
         <v>12</v>
       </c>
       <c r="H38" s="3" t="s">
@@ -6288,10 +6288,10 @@
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="3"/>
-      <c r="O38" s="9" t="s">
+      <c r="O38" s="8" t="s">
         <v>1055</v>
       </c>
-      <c r="P38" s="9" t="s">
+      <c r="P38" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6308,13 +6308,13 @@
       <c r="D39" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="17" t="s">
+      <c r="E39" s="16" t="s">
         <v>858</v>
       </c>
-      <c r="F39" s="4" t="s">
+      <c r="F39" s="17" t="s">
         <v>820</v>
       </c>
-      <c r="G39" s="4">
+      <c r="G39" s="17">
         <v>9</v>
       </c>
       <c r="H39" s="3" t="s">
@@ -6334,10 +6334,10 @@
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="3"/>
-      <c r="O39" s="9" t="s">
+      <c r="O39" s="8" t="s">
         <v>1056</v>
       </c>
-      <c r="P39" s="9" t="s">
+      <c r="P39" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6354,13 +6354,13 @@
       <c r="D40" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E40" s="17" t="s">
+      <c r="E40" s="16" t="s">
         <v>859</v>
       </c>
-      <c r="F40" s="4" t="s">
+      <c r="F40" s="17" t="s">
         <v>821</v>
       </c>
-      <c r="G40" s="4">
+      <c r="G40" s="17">
         <v>7</v>
       </c>
       <c r="H40" s="3" t="s">
@@ -6380,10 +6380,10 @@
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="3"/>
-      <c r="O40" s="9" t="s">
+      <c r="O40" s="8" t="s">
         <v>1057</v>
       </c>
-      <c r="P40" s="9" t="s">
+      <c r="P40" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6400,13 +6400,13 @@
       <c r="D41" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="17" t="s">
+      <c r="E41" s="16" t="s">
         <v>860</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="F41" s="17" t="s">
         <v>800</v>
       </c>
-      <c r="G41" s="4">
+      <c r="G41" s="17">
         <v>12</v>
       </c>
       <c r="H41" s="3" t="s">
@@ -6426,10 +6426,10 @@
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="3"/>
-      <c r="O41" s="9" t="s">
+      <c r="O41" s="8" t="s">
         <v>1058</v>
       </c>
-      <c r="P41" s="9" t="s">
+      <c r="P41" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       <c r="D42" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E42" s="17" t="s">
+      <c r="E42" s="16" t="s">
         <v>186</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -6472,14 +6472,14 @@
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="3"/>
-      <c r="O42" s="9" t="s">
+      <c r="O42" s="8" t="s">
         <v>1059</v>
       </c>
-      <c r="P42" s="9" t="s">
+      <c r="P42" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="46.8">
+    <row r="43" spans="1:16" ht="48">
       <c r="A43" s="1" t="s">
         <v>189</v>
       </c>
@@ -6492,7 +6492,7 @@
       <c r="D43" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E43" s="17" t="s">
+      <c r="E43" s="16" t="s">
         <v>190</v>
       </c>
       <c r="F43" s="1" t="s">
@@ -6520,14 +6520,14 @@
       <c r="N43" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="O43" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P43" s="9" t="s">
+      <c r="O43" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="46.8">
+    <row r="44" spans="1:16" ht="48">
       <c r="A44" s="1" t="s">
         <v>195</v>
       </c>
@@ -6540,7 +6540,7 @@
       <c r="D44" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E44" s="17" t="s">
+      <c r="E44" s="16" t="s">
         <v>198</v>
       </c>
       <c r="F44" s="1" t="s">
@@ -6570,14 +6570,14 @@
       <c r="N44" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="O44" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P44" s="9" t="s">
+      <c r="O44" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="31.2">
+    <row r="45" spans="1:16" ht="32">
       <c r="A45" s="1" t="s">
         <v>203</v>
       </c>
@@ -6590,7 +6590,7 @@
       <c r="D45" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E45" s="17" t="s">
+      <c r="E45" s="16" t="s">
         <v>204</v>
       </c>
       <c r="F45" s="1" t="s">
@@ -6620,10 +6620,10 @@
       <c r="N45" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="O45" s="9" t="s">
+      <c r="O45" s="8" t="s">
         <v>1060</v>
       </c>
-      <c r="P45" s="9" t="s">
+      <c r="P45" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6640,7 +6640,7 @@
       <c r="D46" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E46" s="17" t="s">
+      <c r="E46" s="16" t="s">
         <v>214</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -6666,10 +6666,10 @@
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="3"/>
-      <c r="O46" s="9" t="s">
+      <c r="O46" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="P46" s="9" t="s">
+      <c r="P46" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       <c r="D47" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E47" s="17" t="s">
+      <c r="E47" s="16" t="s">
         <v>219</v>
       </c>
       <c r="F47" s="1" t="s">
@@ -6712,14 +6712,14 @@
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="3"/>
-      <c r="O47" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P47" s="9" t="s">
+      <c r="O47" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P47" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="31.2">
+    <row r="48" spans="1:16" ht="32">
       <c r="A48" s="1" t="s">
         <v>221</v>
       </c>
@@ -6732,7 +6732,7 @@
       <c r="D48" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="17" t="s">
+      <c r="E48" s="16" t="s">
         <v>222</v>
       </c>
       <c r="F48" s="1" t="s">
@@ -6762,10 +6762,10 @@
       <c r="N48" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="O48" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P48" s="9" t="s">
+      <c r="O48" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P48" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       <c r="D49" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E49" s="17" t="s">
+      <c r="E49" s="16" t="s">
         <v>226</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -6808,10 +6808,10 @@
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="3"/>
-      <c r="O49" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P49" s="9" t="s">
+      <c r="O49" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P49" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -6828,13 +6828,13 @@
       <c r="D50" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E50" s="17" t="s">
+      <c r="E50" s="16" t="s">
         <v>861</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="F50" s="17" t="s">
         <v>822</v>
       </c>
-      <c r="G50" s="4">
+      <c r="G50" s="17">
         <v>9</v>
       </c>
       <c r="H50" s="3" t="s">
@@ -6854,10 +6854,10 @@
       </c>
       <c r="M50" s="1"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="9" t="s">
+      <c r="O50" s="8" t="s">
         <v>1062</v>
       </c>
-      <c r="P50" s="9" t="s">
+      <c r="P50" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6874,13 +6874,13 @@
       <c r="D51" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E51" s="17" t="s">
+      <c r="E51" s="16" t="s">
         <v>862</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F51" s="17" t="s">
         <v>823</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G51" s="17">
         <v>11</v>
       </c>
       <c r="H51" s="3" t="s">
@@ -6900,10 +6900,10 @@
       </c>
       <c r="M51" s="1"/>
       <c r="N51" s="3"/>
-      <c r="O51" s="9" t="s">
+      <c r="O51" s="8" t="s">
         <v>1063</v>
       </c>
-      <c r="P51" s="9" t="s">
+      <c r="P51" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -6920,13 +6920,13 @@
       <c r="D52" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E52" s="17" t="s">
+      <c r="E52" s="16" t="s">
         <v>863</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="17" t="s">
         <v>801</v>
       </c>
-      <c r="G52" s="4">
+      <c r="G52" s="17">
         <v>11</v>
       </c>
       <c r="H52" s="3" t="s">
@@ -6946,10 +6946,10 @@
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="3"/>
-      <c r="O52" s="9" t="s">
+      <c r="O52" s="8" t="s">
         <v>1064</v>
       </c>
-      <c r="P52" s="9" t="s">
+      <c r="P52" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -6966,7 +6966,7 @@
       <c r="D53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="16" t="s">
         <v>238</v>
       </c>
       <c r="F53" s="1" t="s">
@@ -6992,10 +6992,10 @@
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="3"/>
-      <c r="O53" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P53" s="9" t="s">
+      <c r="O53" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P53" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
       <c r="D54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E54" s="17" t="s">
+      <c r="E54" s="16" t="s">
         <v>242</v>
       </c>
       <c r="F54" s="1" t="s">
@@ -7038,10 +7038,10 @@
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="3"/>
-      <c r="O54" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P54" s="9" t="s">
+      <c r="O54" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P54" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       <c r="D55" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E55" s="17" t="s">
+      <c r="E55" s="16" t="s">
         <v>246</v>
       </c>
       <c r="F55" s="1" t="s">
@@ -7084,10 +7084,10 @@
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="3"/>
-      <c r="O55" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P55" s="9" t="s">
+      <c r="O55" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P55" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7104,13 +7104,13 @@
       <c r="D56" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E56" s="17" t="s">
+      <c r="E56" s="16" t="s">
         <v>864</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="F56" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="G56" s="4">
+      <c r="G56" s="17">
         <v>9</v>
       </c>
       <c r="H56" s="3" t="s">
@@ -7130,10 +7130,10 @@
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="3"/>
-      <c r="O56" s="9" t="s">
+      <c r="O56" s="8" t="s">
         <v>1065</v>
       </c>
-      <c r="P56" s="9" t="s">
+      <c r="P56" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -7150,13 +7150,13 @@
       <c r="D57" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E57" s="17" t="s">
+      <c r="E57" s="16" t="s">
         <v>865</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="F57" s="17" t="s">
         <v>803</v>
       </c>
-      <c r="G57" s="4">
+      <c r="G57" s="17">
         <v>9</v>
       </c>
       <c r="H57" s="3" t="s">
@@ -7176,10 +7176,10 @@
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="3"/>
-      <c r="O57" s="9" t="s">
+      <c r="O57" s="8" t="s">
         <v>1066</v>
       </c>
-      <c r="P57" s="9" t="s">
+      <c r="P57" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -7196,13 +7196,13 @@
       <c r="D58" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E58" s="17" t="s">
+      <c r="E58" s="16" t="s">
         <v>866</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="F58" s="17" t="s">
         <v>824</v>
       </c>
-      <c r="G58" s="4">
+      <c r="G58" s="17">
         <v>11</v>
       </c>
       <c r="H58" s="3" t="s">
@@ -7222,10 +7222,10 @@
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="3"/>
-      <c r="O58" s="9" t="s">
+      <c r="O58" s="8" t="s">
         <v>1067</v>
       </c>
-      <c r="P58" s="9" t="s">
+      <c r="P58" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
       <c r="D59" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E59" s="17" t="s">
+      <c r="E59" s="16" t="s">
         <v>259</v>
       </c>
       <c r="F59" s="1" t="s">
@@ -7268,10 +7268,10 @@
       </c>
       <c r="M59" s="1"/>
       <c r="N59" s="3"/>
-      <c r="O59" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P59" s="9" t="s">
+      <c r="O59" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P59" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       <c r="D60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E60" s="17" t="s">
+      <c r="E60" s="16" t="s">
         <v>262</v>
       </c>
       <c r="F60" s="1" t="s">
@@ -7314,10 +7314,10 @@
       </c>
       <c r="M60" s="1"/>
       <c r="N60" s="3"/>
-      <c r="O60" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P60" s="9" t="s">
+      <c r="O60" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P60" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       <c r="D61" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E61" s="17" t="s">
+      <c r="E61" s="16" t="s">
         <v>266</v>
       </c>
       <c r="F61" s="1" t="s">
@@ -7360,10 +7360,10 @@
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="3"/>
-      <c r="O61" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P61" s="9" t="s">
+      <c r="O61" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P61" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       <c r="D62" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E62" s="17" t="s">
+      <c r="E62" s="16" t="s">
         <v>269</v>
       </c>
       <c r="F62" s="1" t="s">
@@ -7406,10 +7406,10 @@
       </c>
       <c r="M62" s="1"/>
       <c r="N62" s="3"/>
-      <c r="O62" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P62" s="9" t="s">
+      <c r="O62" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P62" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       <c r="D63" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E63" s="17" t="s">
+      <c r="E63" s="16" t="s">
         <v>272</v>
       </c>
       <c r="F63" s="1" t="s">
@@ -7452,10 +7452,10 @@
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="3"/>
-      <c r="O63" s="9" t="s">
+      <c r="O63" s="8" t="s">
         <v>1068</v>
       </c>
-      <c r="P63" s="9" t="s">
+      <c r="P63" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       <c r="D64" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E64" s="17" t="s">
+      <c r="E64" s="16" t="s">
         <v>275</v>
       </c>
       <c r="F64" s="1" t="s">
@@ -7498,10 +7498,10 @@
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="3"/>
-      <c r="O64" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P64" s="9" t="s">
+      <c r="O64" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P64" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7518,13 +7518,13 @@
       <c r="D65" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E65" s="17" t="s">
+      <c r="E65" s="16" t="s">
         <v>867</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="F65" s="17" t="s">
         <v>825</v>
       </c>
-      <c r="G65" s="4">
+      <c r="G65" s="17">
         <v>8</v>
       </c>
       <c r="H65" s="3" t="s">
@@ -7544,10 +7544,10 @@
       </c>
       <c r="M65" s="1"/>
       <c r="N65" s="3"/>
-      <c r="O65" s="9" t="s">
+      <c r="O65" s="8" t="s">
         <v>1069</v>
       </c>
-      <c r="P65" s="9" t="s">
+      <c r="P65" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -7564,7 +7564,7 @@
       <c r="D66" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="16" t="s">
         <v>280</v>
       </c>
       <c r="F66" s="1" t="s">
@@ -7590,10 +7590,10 @@
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="3"/>
-      <c r="O66" s="9" t="s">
+      <c r="O66" s="8" t="s">
         <v>1070</v>
       </c>
-      <c r="P66" s="9" t="s">
+      <c r="P66" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -7610,13 +7610,13 @@
       <c r="D67" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E67" s="17" t="s">
+      <c r="E67" s="16" t="s">
         <v>868</v>
       </c>
-      <c r="F67" s="4" t="s">
+      <c r="F67" s="17" t="s">
         <v>804</v>
       </c>
-      <c r="G67" s="4">
+      <c r="G67" s="17">
         <v>11</v>
       </c>
       <c r="H67" s="3" t="s">
@@ -7636,10 +7636,10 @@
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="3"/>
-      <c r="O67" s="9" t="s">
+      <c r="O67" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="P67" s="9" t="s">
+      <c r="P67" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -7656,13 +7656,13 @@
       <c r="D68" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E68" s="17" t="s">
+      <c r="E68" s="16" t="s">
         <v>869</v>
       </c>
-      <c r="F68" s="4" t="s">
+      <c r="F68" s="17" t="s">
         <v>826</v>
       </c>
-      <c r="G68" s="4">
+      <c r="G68" s="17">
         <v>9</v>
       </c>
       <c r="H68" s="3" t="s">
@@ -7682,10 +7682,10 @@
       </c>
       <c r="M68" s="1"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="9" t="s">
+      <c r="O68" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="P68" s="9" t="s">
+      <c r="P68" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       <c r="D69" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E69" s="17" t="s">
+      <c r="E69" s="16" t="s">
         <v>289</v>
       </c>
       <c r="F69" s="1" t="s">
@@ -7728,10 +7728,10 @@
       </c>
       <c r="M69" s="1"/>
       <c r="N69" s="3"/>
-      <c r="O69" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P69" s="9" t="s">
+      <c r="O69" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P69" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7748,7 +7748,7 @@
       <c r="D70" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E70" s="17" t="s">
+      <c r="E70" s="16" t="s">
         <v>292</v>
       </c>
       <c r="F70" s="1" t="s">
@@ -7774,10 +7774,10 @@
       </c>
       <c r="M70" s="1"/>
       <c r="N70" s="3"/>
-      <c r="O70" s="9" t="s">
+      <c r="O70" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="P70" s="9" t="s">
+      <c r="P70" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       <c r="D71" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E71" s="17" t="s">
+      <c r="E71" s="16" t="s">
         <v>296</v>
       </c>
       <c r="F71" s="1" t="s">
@@ -7820,14 +7820,14 @@
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="3"/>
-      <c r="O71" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P71" s="9" t="s">
+      <c r="O71" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P71" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="72" spans="1:16" ht="46.8">
+    <row r="72" spans="1:16" ht="48">
       <c r="A72" s="1" t="s">
         <v>299</v>
       </c>
@@ -7840,7 +7840,7 @@
       <c r="D72" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E72" s="17" t="s">
+      <c r="E72" s="16" t="s">
         <v>300</v>
       </c>
       <c r="F72" s="1" t="s">
@@ -7870,10 +7870,10 @@
       <c r="N72" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="O72" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P72" s="9" t="s">
+      <c r="O72" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P72" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       <c r="D73" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="16" t="s">
         <v>304</v>
       </c>
       <c r="F73" s="1" t="s">
@@ -7916,10 +7916,10 @@
       </c>
       <c r="M73" s="1"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="9" t="s">
+      <c r="O73" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="P73" s="9" t="s">
+      <c r="P73" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -7936,7 +7936,7 @@
       <c r="D74" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E74" s="17" t="s">
+      <c r="E74" s="16" t="s">
         <v>307</v>
       </c>
       <c r="F74" s="1" t="s">
@@ -7962,14 +7962,14 @@
       </c>
       <c r="M74" s="1"/>
       <c r="N74" s="3"/>
-      <c r="O74" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P74" s="9" t="s">
+      <c r="O74" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P74" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="46.8">
+    <row r="75" spans="1:16" ht="48">
       <c r="A75" s="1" t="s">
         <v>310</v>
       </c>
@@ -7982,7 +7982,7 @@
       <c r="D75" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="16" t="s">
         <v>311</v>
       </c>
       <c r="F75" s="1" t="s">
@@ -8012,10 +8012,10 @@
       <c r="N75" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="O75" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P75" s="9" t="s">
+      <c r="O75" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P75" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8032,7 +8032,7 @@
       <c r="D76" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E76" s="17" t="s">
+      <c r="E76" s="16" t="s">
         <v>315</v>
       </c>
       <c r="F76" s="1" t="s">
@@ -8058,10 +8058,10 @@
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="3"/>
-      <c r="O76" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P76" s="9" t="s">
+      <c r="O76" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P76" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8078,7 +8078,7 @@
       <c r="D77" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="16" t="s">
         <v>318</v>
       </c>
       <c r="F77" s="1" t="s">
@@ -8104,10 +8104,10 @@
       </c>
       <c r="M77" s="1"/>
       <c r="N77" s="3"/>
-      <c r="O77" s="9" t="s">
+      <c r="O77" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="P77" s="9" t="s">
+      <c r="P77" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -8124,13 +8124,13 @@
       <c r="D78" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E78" s="17" t="s">
+      <c r="E78" s="16" t="s">
         <v>870</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F78" s="17" t="s">
         <v>805</v>
       </c>
-      <c r="G78" s="4">
+      <c r="G78" s="17">
         <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
@@ -8150,10 +8150,10 @@
       </c>
       <c r="M78" s="1"/>
       <c r="N78" s="3"/>
-      <c r="O78" s="9" t="s">
+      <c r="O78" s="8" t="s">
         <v>1076</v>
       </c>
-      <c r="P78" s="9" t="s">
+      <c r="P78" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       <c r="D79" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="16" t="s">
         <v>324</v>
       </c>
       <c r="F79" s="1" t="s">
@@ -8196,10 +8196,10 @@
       </c>
       <c r="M79" s="1"/>
       <c r="N79" s="3"/>
-      <c r="O79" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P79" s="9" t="s">
+      <c r="O79" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P79" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       <c r="D80" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E80" s="17" t="s">
+      <c r="E80" s="16" t="s">
         <v>327</v>
       </c>
       <c r="F80" s="1" t="s">
@@ -8242,10 +8242,10 @@
       </c>
       <c r="M80" s="1"/>
       <c r="N80" s="3"/>
-      <c r="O80" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P80" s="9" t="s">
+      <c r="O80" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P80" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8262,7 +8262,7 @@
       <c r="D81" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="16" t="s">
         <v>331</v>
       </c>
       <c r="F81" s="1" t="s">
@@ -8288,10 +8288,10 @@
       </c>
       <c r="M81" s="1"/>
       <c r="N81" s="3"/>
-      <c r="O81" s="9" t="s">
+      <c r="O81" s="8" t="s">
         <v>1077</v>
       </c>
-      <c r="P81" s="9" t="s">
+      <c r="P81" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -8308,13 +8308,13 @@
       <c r="D82" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E82" s="17" t="s">
+      <c r="E82" s="16" t="s">
         <v>871</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="F82" s="17" t="s">
         <v>827</v>
       </c>
-      <c r="G82" s="4">
+      <c r="G82" s="17">
         <v>9</v>
       </c>
       <c r="H82" s="3" t="s">
@@ -8334,10 +8334,10 @@
       </c>
       <c r="M82" s="1"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="9" t="s">
+      <c r="O82" s="8" t="s">
         <v>1078</v>
       </c>
-      <c r="P82" s="9" t="s">
+      <c r="P82" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -8354,7 +8354,7 @@
       <c r="D83" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E83" s="17" t="s">
+      <c r="E83" s="16" t="s">
         <v>338</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -8380,10 +8380,10 @@
       </c>
       <c r="M83" s="1"/>
       <c r="N83" s="3"/>
-      <c r="O83" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P83" s="9" t="s">
+      <c r="O83" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P83" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8400,13 +8400,13 @@
       <c r="D84" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E84" s="17" t="s">
+      <c r="E84" s="16" t="s">
         <v>872</v>
       </c>
-      <c r="F84" s="4" t="s">
+      <c r="F84" s="17" t="s">
         <v>828</v>
       </c>
-      <c r="G84" s="4">
+      <c r="G84" s="17">
         <v>10</v>
       </c>
       <c r="H84" s="3" t="s">
@@ -8426,10 +8426,10 @@
       </c>
       <c r="M84" s="1"/>
       <c r="N84" s="3"/>
-      <c r="O84" s="9" t="s">
+      <c r="O84" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="P84" s="9" t="s">
+      <c r="P84" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -8446,13 +8446,13 @@
       <c r="D85" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E85" s="17" t="s">
+      <c r="E85" s="16" t="s">
         <v>873</v>
       </c>
-      <c r="F85" s="4" t="s">
+      <c r="F85" s="17" t="s">
         <v>806</v>
       </c>
-      <c r="G85" s="4">
+      <c r="G85" s="17">
         <v>11</v>
       </c>
       <c r="H85" s="3" t="s">
@@ -8472,10 +8472,10 @@
       </c>
       <c r="M85" s="1"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="9" t="s">
+      <c r="O85" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="P85" s="9" t="s">
+      <c r="P85" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       <c r="D86" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E86" s="17" t="s">
+      <c r="E86" s="16" t="s">
         <v>347</v>
       </c>
       <c r="F86" s="1" t="s">
@@ -8518,10 +8518,10 @@
       </c>
       <c r="M86" s="1"/>
       <c r="N86" s="3"/>
-      <c r="O86" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P86" s="9" t="s">
+      <c r="O86" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P86" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8538,13 +8538,13 @@
       <c r="D87" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E87" s="17" t="s">
+      <c r="E87" s="16" t="s">
         <v>874</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="F87" s="17" t="s">
         <v>829</v>
       </c>
-      <c r="G87" s="4">
+      <c r="G87" s="17">
         <v>11</v>
       </c>
       <c r="H87" s="3" t="s">
@@ -8564,10 +8564,10 @@
       </c>
       <c r="M87" s="1"/>
       <c r="N87" s="3"/>
-      <c r="O87" s="9" t="s">
+      <c r="O87" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="P87" s="9" t="s">
+      <c r="P87" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -8584,7 +8584,7 @@
       <c r="D88" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E88" s="17" t="s">
+      <c r="E88" s="16" t="s">
         <v>354</v>
       </c>
       <c r="F88" s="1" t="s">
@@ -8610,10 +8610,10 @@
       </c>
       <c r="M88" s="1"/>
       <c r="N88" s="3"/>
-      <c r="O88" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P88" s="9" t="s">
+      <c r="O88" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P88" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8630,13 +8630,13 @@
       <c r="D89" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="16" t="s">
         <v>875</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="F89" s="17" t="s">
         <v>807</v>
       </c>
-      <c r="G89" s="4">
+      <c r="G89" s="17">
         <v>11</v>
       </c>
       <c r="H89" s="3" t="s">
@@ -8656,10 +8656,10 @@
       </c>
       <c r="M89" s="1"/>
       <c r="N89" s="3"/>
-      <c r="O89" s="9" t="s">
+      <c r="O89" s="8" t="s">
         <v>1082</v>
       </c>
-      <c r="P89" s="9" t="s">
+      <c r="P89" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       <c r="D90" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E90" s="17" t="s">
+      <c r="E90" s="16" t="s">
         <v>360</v>
       </c>
       <c r="F90" s="1" t="s">
@@ -8702,10 +8702,10 @@
       </c>
       <c r="M90" s="1"/>
       <c r="N90" s="3"/>
-      <c r="O90" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P90" s="9" t="s">
+      <c r="O90" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P90" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       <c r="D91" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="16" t="s">
         <v>363</v>
       </c>
       <c r="F91" s="1" t="s">
@@ -8748,10 +8748,10 @@
       </c>
       <c r="M91" s="1"/>
       <c r="N91" s="3"/>
-      <c r="O91" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P91" s="9" t="s">
+      <c r="O91" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P91" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8768,7 +8768,7 @@
       <c r="D92" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E92" s="17" t="s">
+      <c r="E92" s="16" t="s">
         <v>366</v>
       </c>
       <c r="F92" s="1" t="s">
@@ -8794,10 +8794,10 @@
       </c>
       <c r="M92" s="1"/>
       <c r="N92" s="3"/>
-      <c r="O92" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P92" s="9" t="s">
+      <c r="O92" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P92" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       <c r="D93" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="16" t="s">
         <v>370</v>
       </c>
       <c r="F93" s="1" t="s">
@@ -8840,10 +8840,10 @@
       </c>
       <c r="M93" s="1"/>
       <c r="N93" s="3"/>
-      <c r="O93" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P93" s="9" t="s">
+      <c r="O93" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P93" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       <c r="D94" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E94" s="17" t="s">
+      <c r="E94" s="16" t="s">
         <v>375</v>
       </c>
       <c r="F94" s="1" t="s">
@@ -8886,10 +8886,10 @@
       </c>
       <c r="M94" s="1"/>
       <c r="N94" s="3"/>
-      <c r="O94" s="9" t="s">
+      <c r="O94" s="8" t="s">
         <v>1083</v>
       </c>
-      <c r="P94" s="9" t="s">
+      <c r="P94" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       <c r="D95" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="16" t="s">
         <v>378</v>
       </c>
       <c r="F95" s="1" t="s">
@@ -8932,10 +8932,10 @@
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="3"/>
-      <c r="O95" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P95" s="9" t="s">
+      <c r="O95" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P95" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8952,7 +8952,7 @@
       <c r="D96" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E96" s="17" t="s">
+      <c r="E96" s="16" t="s">
         <v>382</v>
       </c>
       <c r="F96" s="1" t="s">
@@ -8978,10 +8978,10 @@
       </c>
       <c r="M96" s="1"/>
       <c r="N96" s="3"/>
-      <c r="O96" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P96" s="9" t="s">
+      <c r="O96" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P96" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -8998,7 +8998,7 @@
       <c r="D97" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E97" s="17" t="s">
+      <c r="E97" s="16" t="s">
         <v>386</v>
       </c>
       <c r="F97" s="1" t="s">
@@ -9024,10 +9024,10 @@
       </c>
       <c r="M97" s="1"/>
       <c r="N97" s="3"/>
-      <c r="O97" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P97" s="9" t="s">
+      <c r="O97" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P97" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       <c r="D98" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E98" s="17" t="s">
+      <c r="E98" s="16" t="s">
         <v>390</v>
       </c>
       <c r="F98" s="1" t="s">
@@ -9070,10 +9070,10 @@
       </c>
       <c r="M98" s="1"/>
       <c r="N98" s="3"/>
-      <c r="O98" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P98" s="9" t="s">
+      <c r="O98" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P98" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9090,13 +9090,13 @@
       <c r="D99" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E99" s="17" t="s">
+      <c r="E99" s="16" t="s">
         <v>876</v>
       </c>
-      <c r="F99" s="4" t="s">
+      <c r="F99" s="17" t="s">
         <v>895</v>
       </c>
-      <c r="G99" s="4">
+      <c r="G99" s="17">
         <v>9</v>
       </c>
       <c r="H99" s="3" t="s">
@@ -9116,10 +9116,10 @@
       </c>
       <c r="M99" s="1"/>
       <c r="N99" s="3"/>
-      <c r="O99" s="9" t="s">
+      <c r="O99" s="8" t="s">
         <v>1084</v>
       </c>
-      <c r="P99" s="9" t="s">
+      <c r="P99" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       <c r="D100" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E100" s="17" t="s">
+      <c r="E100" s="16" t="s">
         <v>397</v>
       </c>
       <c r="F100" s="1" t="s">
@@ -9162,10 +9162,10 @@
       </c>
       <c r="M100" s="1"/>
       <c r="N100" s="3"/>
-      <c r="O100" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P100" s="9" t="s">
+      <c r="O100" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P100" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       <c r="D101" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E101" s="17" t="s">
+      <c r="E101" s="16" t="s">
         <v>401</v>
       </c>
       <c r="F101" s="1" t="s">
@@ -9208,10 +9208,10 @@
       </c>
       <c r="M101" s="1"/>
       <c r="N101" s="3"/>
-      <c r="O101" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P101" s="9" t="s">
+      <c r="O101" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P101" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       <c r="D102" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E102" s="17" t="s">
+      <c r="E102" s="16" t="s">
         <v>404</v>
       </c>
       <c r="F102" s="1" t="s">
@@ -9254,10 +9254,10 @@
       </c>
       <c r="M102" s="1"/>
       <c r="N102" s="3"/>
-      <c r="O102" s="9" t="s">
+      <c r="O102" s="8" t="s">
         <v>1085</v>
       </c>
-      <c r="P102" s="9" t="s">
+      <c r="P102" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       <c r="D103" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E103" s="17" t="s">
+      <c r="E103" s="16" t="s">
         <v>407</v>
       </c>
       <c r="F103" s="1" t="s">
@@ -9300,10 +9300,10 @@
       </c>
       <c r="M103" s="1"/>
       <c r="N103" s="3"/>
-      <c r="O103" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P103" s="9" t="s">
+      <c r="O103" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P103" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9320,13 +9320,13 @@
       <c r="D104" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E104" s="17" t="s">
+      <c r="E104" s="16" t="s">
         <v>877</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="F104" s="17" t="s">
         <v>830</v>
       </c>
-      <c r="G104" s="4">
+      <c r="G104" s="17">
         <v>12</v>
       </c>
       <c r="H104" s="3" t="s">
@@ -9346,10 +9346,10 @@
       </c>
       <c r="M104" s="1"/>
       <c r="N104" s="3"/>
-      <c r="O104" s="9" t="s">
+      <c r="O104" s="8" t="s">
         <v>1086</v>
       </c>
-      <c r="P104" s="9" t="s">
+      <c r="P104" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       <c r="D105" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E105" s="17" t="s">
+      <c r="E105" s="16" t="s">
         <v>414</v>
       </c>
       <c r="F105" s="1" t="s">
@@ -9392,14 +9392,14 @@
       </c>
       <c r="M105" s="1"/>
       <c r="N105" s="3"/>
-      <c r="O105" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P105" s="9" t="s">
+      <c r="O105" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P105" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="46.8">
+    <row r="106" spans="1:16" ht="48">
       <c r="A106" s="1" t="s">
         <v>416</v>
       </c>
@@ -9412,7 +9412,7 @@
       <c r="D106" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E106" s="17" t="s">
+      <c r="E106" s="16" t="s">
         <v>417</v>
       </c>
       <c r="F106" s="1" t="s">
@@ -9442,10 +9442,10 @@
       <c r="N106" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="O106" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P106" s="9" t="s">
+      <c r="O106" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P106" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       <c r="D107" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E107" s="17" t="s">
+      <c r="E107" s="16" t="s">
         <v>421</v>
       </c>
       <c r="F107" s="1" t="s">
@@ -9488,10 +9488,10 @@
       </c>
       <c r="M107" s="1"/>
       <c r="N107" s="3"/>
-      <c r="O107" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P107" s="9" t="s">
+      <c r="O107" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P107" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9508,7 +9508,7 @@
       <c r="D108" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E108" s="17" t="s">
+      <c r="E108" s="16" t="s">
         <v>424</v>
       </c>
       <c r="F108" s="1" t="s">
@@ -9534,10 +9534,10 @@
       </c>
       <c r="M108" s="1"/>
       <c r="N108" s="3"/>
-      <c r="O108" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P108" s="9" t="s">
+      <c r="O108" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P108" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       <c r="D109" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E109" s="17" t="s">
+      <c r="E109" s="16" t="s">
         <v>427</v>
       </c>
       <c r="F109" s="1" t="s">
@@ -9580,10 +9580,10 @@
       </c>
       <c r="M109" s="1"/>
       <c r="N109" s="3"/>
-      <c r="O109" s="9" t="s">
+      <c r="O109" s="8" t="s">
         <v>1087</v>
       </c>
-      <c r="P109" s="9" t="s">
+      <c r="P109" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -9600,13 +9600,13 @@
       <c r="D110" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E110" s="17" t="s">
+      <c r="E110" s="16" t="s">
         <v>878</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="F110" s="17" t="s">
         <v>831</v>
       </c>
-      <c r="G110" s="4">
+      <c r="G110" s="17">
         <v>9</v>
       </c>
       <c r="H110" s="3" t="s">
@@ -9626,10 +9626,10 @@
       </c>
       <c r="M110" s="1"/>
       <c r="N110" s="3"/>
-      <c r="O110" s="9" t="s">
+      <c r="O110" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="P110" s="9" t="s">
+      <c r="P110" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -9646,13 +9646,13 @@
       <c r="D111" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E111" s="17" t="s">
+      <c r="E111" s="16" t="s">
         <v>879</v>
       </c>
-      <c r="F111" s="4" t="s">
+      <c r="F111" s="17" t="s">
         <v>832</v>
       </c>
-      <c r="G111" s="4">
+      <c r="G111" s="17">
         <v>11</v>
       </c>
       <c r="H111" s="3" t="s">
@@ -9672,10 +9672,10 @@
       </c>
       <c r="M111" s="1"/>
       <c r="N111" s="3"/>
-      <c r="O111" s="9" t="s">
+      <c r="O111" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="P111" s="9" t="s">
+      <c r="P111" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -9692,13 +9692,13 @@
       <c r="D112" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E112" s="17" t="s">
+      <c r="E112" s="16" t="s">
         <v>880</v>
       </c>
-      <c r="F112" s="4" t="s">
+      <c r="F112" s="17" t="s">
         <v>833</v>
       </c>
-      <c r="G112" s="4">
+      <c r="G112" s="17">
         <v>11</v>
       </c>
       <c r="H112" s="3" t="s">
@@ -9718,10 +9718,10 @@
       </c>
       <c r="M112" s="1"/>
       <c r="N112" s="3"/>
-      <c r="O112" s="9" t="s">
+      <c r="O112" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="P112" s="9" t="s">
+      <c r="P112" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -9738,7 +9738,7 @@
       <c r="D113" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E113" s="17" t="s">
+      <c r="E113" s="16" t="s">
         <v>438</v>
       </c>
       <c r="F113" s="1" t="s">
@@ -9764,10 +9764,10 @@
       </c>
       <c r="M113" s="1"/>
       <c r="N113" s="3"/>
-      <c r="O113" s="9" t="s">
+      <c r="O113" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="P113" s="9" t="s">
+      <c r="P113" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       <c r="D114" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E114" s="17" t="s">
+      <c r="E114" s="16" t="s">
         <v>442</v>
       </c>
       <c r="F114" s="1" t="s">
@@ -9810,10 +9810,10 @@
       </c>
       <c r="M114" s="1"/>
       <c r="N114" s="3"/>
-      <c r="O114" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P114" s="9" t="s">
+      <c r="O114" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P114" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9830,7 +9830,7 @@
       <c r="D115" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E115" s="17" t="s">
+      <c r="E115" s="16" t="s">
         <v>445</v>
       </c>
       <c r="F115" s="1" t="s">
@@ -9856,10 +9856,10 @@
       </c>
       <c r="M115" s="1"/>
       <c r="N115" s="3"/>
-      <c r="O115" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P115" s="9" t="s">
+      <c r="O115" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P115" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -9876,13 +9876,13 @@
       <c r="D116" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E116" s="17" t="s">
+      <c r="E116" s="16" t="s">
         <v>881</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="F116" s="17" t="s">
         <v>834</v>
       </c>
-      <c r="G116" s="4">
+      <c r="G116" s="17">
         <v>12</v>
       </c>
       <c r="H116" s="3" t="s">
@@ -9902,10 +9902,10 @@
       </c>
       <c r="M116" s="1"/>
       <c r="N116" s="3"/>
-      <c r="O116" s="9" t="s">
+      <c r="O116" s="8" t="s">
         <v>1092</v>
       </c>
-      <c r="P116" s="9" t="s">
+      <c r="P116" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -9922,7 +9922,7 @@
       <c r="D117" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E117" s="17" t="s">
+      <c r="E117" s="16" t="s">
         <v>452</v>
       </c>
       <c r="F117" s="1" t="s">
@@ -9948,10 +9948,10 @@
       </c>
       <c r="M117" s="1"/>
       <c r="N117" s="3"/>
-      <c r="O117" s="9" t="s">
+      <c r="O117" s="8" t="s">
         <v>1093</v>
       </c>
-      <c r="P117" s="9" t="s">
+      <c r="P117" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       <c r="D118" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E118" s="17" t="s">
+      <c r="E118" s="16" t="s">
         <v>455</v>
       </c>
       <c r="F118" s="1" t="s">
@@ -9994,10 +9994,10 @@
       </c>
       <c r="M118" s="1"/>
       <c r="N118" s="3"/>
-      <c r="O118" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P118" s="9" t="s">
+      <c r="O118" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P118" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10014,13 +10014,13 @@
       <c r="D119" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E119" s="17" t="s">
+      <c r="E119" s="16" t="s">
         <v>882</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="F119" s="17" t="s">
         <v>835</v>
       </c>
-      <c r="G119" s="4">
+      <c r="G119" s="17">
         <v>10</v>
       </c>
       <c r="H119" s="3" t="s">
@@ -10040,10 +10040,10 @@
       </c>
       <c r="M119" s="1"/>
       <c r="N119" s="3"/>
-      <c r="O119" s="9" t="s">
+      <c r="O119" s="8" t="s">
         <v>1094</v>
       </c>
-      <c r="P119" s="9" t="s">
+      <c r="P119" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10060,13 +10060,13 @@
       <c r="D120" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E120" s="17" t="s">
+      <c r="E120" s="16" t="s">
         <v>883</v>
       </c>
-      <c r="F120" s="4" t="s">
+      <c r="F120" s="17" t="s">
         <v>896</v>
       </c>
-      <c r="G120" s="4">
+      <c r="G120" s="17">
         <v>10</v>
       </c>
       <c r="H120" s="3" t="s">
@@ -10086,10 +10086,10 @@
       </c>
       <c r="M120" s="1"/>
       <c r="N120" s="3"/>
-      <c r="O120" s="9" t="s">
+      <c r="O120" s="8" t="s">
         <v>1095</v>
       </c>
-      <c r="P120" s="9" t="s">
+      <c r="P120" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -10106,7 +10106,7 @@
       <c r="D121" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E121" s="17" t="s">
+      <c r="E121" s="16" t="s">
         <v>463</v>
       </c>
       <c r="F121" s="1" t="s">
@@ -10132,10 +10132,10 @@
       </c>
       <c r="M121" s="1"/>
       <c r="N121" s="3"/>
-      <c r="O121" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P121" s="9" t="s">
+      <c r="O121" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P121" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       <c r="D122" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E122" s="17" t="s">
+      <c r="E122" s="16" t="s">
         <v>466</v>
       </c>
       <c r="F122" s="1" t="s">
@@ -10178,10 +10178,10 @@
       </c>
       <c r="M122" s="1"/>
       <c r="N122" s="3"/>
-      <c r="O122" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P122" s="9" t="s">
+      <c r="O122" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P122" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       <c r="D123" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E123" s="17" t="s">
+      <c r="E123" s="16" t="s">
         <v>470</v>
       </c>
       <c r="F123" s="1" t="s">
@@ -10224,10 +10224,10 @@
       </c>
       <c r="M123" s="1"/>
       <c r="N123" s="3"/>
-      <c r="O123" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P123" s="9" t="s">
+      <c r="O123" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P123" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       <c r="D124" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E124" s="17" t="s">
+      <c r="E124" s="16" t="s">
         <v>473</v>
       </c>
       <c r="F124" s="1" t="s">
@@ -10270,10 +10270,10 @@
       </c>
       <c r="M124" s="1"/>
       <c r="N124" s="3"/>
-      <c r="O124" s="9" t="s">
+      <c r="O124" s="8" t="s">
         <v>1096</v>
       </c>
-      <c r="P124" s="9" t="s">
+      <c r="P124" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -10290,7 +10290,7 @@
       <c r="D125" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E125" s="17" t="s">
+      <c r="E125" s="16" t="s">
         <v>477</v>
       </c>
       <c r="F125" s="1" t="s">
@@ -10316,10 +10316,10 @@
       </c>
       <c r="M125" s="1"/>
       <c r="N125" s="3"/>
-      <c r="O125" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P125" s="9" t="s">
+      <c r="O125" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P125" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       <c r="D126" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E126" s="17" t="s">
+      <c r="E126" s="16" t="s">
         <v>480</v>
       </c>
       <c r="F126" s="1" t="s">
@@ -10362,10 +10362,10 @@
       </c>
       <c r="M126" s="1"/>
       <c r="N126" s="3"/>
-      <c r="O126" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P126" s="9" t="s">
+      <c r="O126" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P126" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10382,7 +10382,7 @@
       <c r="D127" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E127" s="17" t="s">
+      <c r="E127" s="16" t="s">
         <v>483</v>
       </c>
       <c r="F127" s="1" t="s">
@@ -10408,10 +10408,10 @@
       </c>
       <c r="M127" s="1"/>
       <c r="N127" s="3"/>
-      <c r="O127" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P127" s="9" t="s">
+      <c r="O127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P127" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       <c r="D128" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E128" s="17" t="s">
+      <c r="E128" s="16" t="s">
         <v>485</v>
       </c>
       <c r="F128" s="1" t="s">
@@ -10454,10 +10454,10 @@
       </c>
       <c r="M128" s="1"/>
       <c r="N128" s="3"/>
-      <c r="O128" s="9" t="s">
+      <c r="O128" s="8" t="s">
         <v>1097</v>
       </c>
-      <c r="P128" s="9" t="s">
+      <c r="P128" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10474,7 +10474,7 @@
       <c r="D129" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E129" s="17" t="s">
+      <c r="E129" s="16" t="s">
         <v>488</v>
       </c>
       <c r="F129" s="1" t="s">
@@ -10500,10 +10500,10 @@
       </c>
       <c r="M129" s="1"/>
       <c r="N129" s="3"/>
-      <c r="O129" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P129" s="9" t="s">
+      <c r="O129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P129" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       <c r="D130" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E130" s="17" t="s">
+      <c r="E130" s="16" t="s">
         <v>491</v>
       </c>
       <c r="F130" s="1" t="s">
@@ -10546,10 +10546,10 @@
       </c>
       <c r="M130" s="1"/>
       <c r="N130" s="3"/>
-      <c r="O130" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P130" s="9" t="s">
+      <c r="O130" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P130" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       <c r="D131" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E131" s="17" t="s">
+      <c r="E131" s="16" t="s">
         <v>494</v>
       </c>
       <c r="F131" s="1" t="s">
@@ -10592,10 +10592,10 @@
       </c>
       <c r="M131" s="1"/>
       <c r="N131" s="3"/>
-      <c r="O131" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P131" s="9" t="s">
+      <c r="O131" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P131" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       <c r="D132" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E132" s="17" t="s">
+      <c r="E132" s="16" t="s">
         <v>497</v>
       </c>
       <c r="F132" s="1" t="s">
@@ -10638,14 +10638,14 @@
       </c>
       <c r="M132" s="1"/>
       <c r="N132" s="3"/>
-      <c r="O132" s="9" t="s">
+      <c r="O132" s="8" t="s">
         <v>1098</v>
       </c>
-      <c r="P132" s="9" t="s">
+      <c r="P132" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="133" spans="1:16" ht="46.8">
+    <row r="133" spans="1:16" ht="48">
       <c r="A133" s="1" t="s">
         <v>500</v>
       </c>
@@ -10658,7 +10658,7 @@
       <c r="D133" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E133" s="17" t="s">
+      <c r="E133" s="16" t="s">
         <v>501</v>
       </c>
       <c r="F133" s="1" t="s">
@@ -10688,10 +10688,10 @@
       <c r="N133" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="O133" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P133" s="9" t="s">
+      <c r="O133" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P133" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
       <c r="D134" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E134" s="17" t="s">
+      <c r="E134" s="16" t="s">
         <v>507</v>
       </c>
       <c r="F134" s="1" t="s">
@@ -10734,10 +10734,10 @@
       </c>
       <c r="M134" s="1"/>
       <c r="N134" s="3"/>
-      <c r="O134" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P134" s="9" t="s">
+      <c r="O134" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P134" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10754,13 +10754,13 @@
       <c r="D135" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E135" s="17" t="s">
+      <c r="E135" s="16" t="s">
         <v>884</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="F135" s="17" t="s">
         <v>808</v>
       </c>
-      <c r="G135" s="4">
+      <c r="G135" s="17">
         <v>8</v>
       </c>
       <c r="H135" s="3" t="s">
@@ -10780,10 +10780,10 @@
       </c>
       <c r="M135" s="1"/>
       <c r="N135" s="3"/>
-      <c r="O135" s="9" t="s">
+      <c r="O135" s="8" t="s">
         <v>1099</v>
       </c>
-      <c r="P135" s="9" t="s">
+      <c r="P135" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10800,13 +10800,13 @@
       <c r="D136" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E136" s="17" t="s">
+      <c r="E136" s="16" t="s">
         <v>885</v>
       </c>
-      <c r="F136" s="4" t="s">
+      <c r="F136" s="17" t="s">
         <v>836</v>
       </c>
-      <c r="G136" s="4">
+      <c r="G136" s="17">
         <v>12</v>
       </c>
       <c r="H136" s="3" t="s">
@@ -10826,10 +10826,10 @@
       </c>
       <c r="M136" s="1"/>
       <c r="N136" s="3"/>
-      <c r="O136" s="9" t="s">
+      <c r="O136" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="P136" s="9" t="s">
+      <c r="P136" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -10846,7 +10846,7 @@
       <c r="D137" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E137" s="17" t="s">
+      <c r="E137" s="16" t="s">
         <v>514</v>
       </c>
       <c r="F137" s="1" t="s">
@@ -10872,10 +10872,10 @@
       </c>
       <c r="M137" s="1"/>
       <c r="N137" s="3"/>
-      <c r="O137" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P137" s="9" t="s">
+      <c r="O137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P137" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10892,7 +10892,7 @@
       <c r="D138" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E138" s="17" t="s">
+      <c r="E138" s="16" t="s">
         <v>518</v>
       </c>
       <c r="F138" s="1" t="s">
@@ -10918,10 +10918,10 @@
       </c>
       <c r="M138" s="1"/>
       <c r="N138" s="3"/>
-      <c r="O138" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P138" s="9" t="s">
+      <c r="O138" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P138" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10938,7 +10938,7 @@
       <c r="D139" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E139" s="17" t="s">
+      <c r="E139" s="16" t="s">
         <v>522</v>
       </c>
       <c r="F139" s="1" t="s">
@@ -10964,10 +10964,10 @@
       </c>
       <c r="M139" s="1"/>
       <c r="N139" s="3"/>
-      <c r="O139" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P139" s="9" t="s">
+      <c r="O139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P139" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -10984,7 +10984,7 @@
       <c r="D140" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E140" s="17" t="s">
+      <c r="E140" s="16" t="s">
         <v>527</v>
       </c>
       <c r="F140" s="1" t="s">
@@ -11010,10 +11010,10 @@
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="3"/>
-      <c r="O140" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P140" s="9" t="s">
+      <c r="O140" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P140" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11030,7 +11030,7 @@
       <c r="D141" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E141" s="17" t="s">
+      <c r="E141" s="16" t="s">
         <v>531</v>
       </c>
       <c r="F141" s="1" t="s">
@@ -11056,10 +11056,10 @@
       </c>
       <c r="M141" s="1"/>
       <c r="N141" s="3"/>
-      <c r="O141" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P141" s="9" t="s">
+      <c r="O141" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P141" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       <c r="D142" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E142" s="17" t="s">
+      <c r="E142" s="16" t="s">
         <v>534</v>
       </c>
       <c r="F142" s="1" t="s">
@@ -11102,10 +11102,10 @@
       </c>
       <c r="M142" s="1"/>
       <c r="N142" s="3"/>
-      <c r="O142" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P142" s="9" t="s">
+      <c r="O142" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P142" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11122,7 +11122,7 @@
       <c r="D143" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E143" s="17" t="s">
+      <c r="E143" s="16" t="s">
         <v>538</v>
       </c>
       <c r="F143" s="1" t="s">
@@ -11148,10 +11148,10 @@
       </c>
       <c r="M143" s="1"/>
       <c r="N143" s="3"/>
-      <c r="O143" s="9" t="s">
+      <c r="O143" s="8" t="s">
         <v>1101</v>
       </c>
-      <c r="P143" s="9" t="s">
+      <c r="P143" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -11168,7 +11168,7 @@
       <c r="D144" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E144" s="17" t="s">
+      <c r="E144" s="16" t="s">
         <v>542</v>
       </c>
       <c r="F144" s="1" t="s">
@@ -11194,10 +11194,10 @@
       </c>
       <c r="M144" s="1"/>
       <c r="N144" s="3"/>
-      <c r="O144" s="9" t="s">
+      <c r="O144" s="8" t="s">
         <v>1102</v>
       </c>
-      <c r="P144" s="9" t="s">
+      <c r="P144" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -11214,7 +11214,7 @@
       <c r="D145" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E145" s="17" t="s">
+      <c r="E145" s="16" t="s">
         <v>546</v>
       </c>
       <c r="F145" s="1" t="s">
@@ -11240,10 +11240,10 @@
       </c>
       <c r="M145" s="1"/>
       <c r="N145" s="3"/>
-      <c r="O145" s="9" t="s">
+      <c r="O145" s="8" t="s">
         <v>1103</v>
       </c>
-      <c r="P145" s="9" t="s">
+      <c r="P145" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -11260,7 +11260,7 @@
       <c r="D146" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="E146" s="17" t="s">
+      <c r="E146" s="16" t="s">
         <v>549</v>
       </c>
       <c r="F146" s="1" t="s">
@@ -11286,10 +11286,10 @@
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="3"/>
-      <c r="O146" s="9" t="s">
+      <c r="O146" s="8" t="s">
         <v>1104</v>
       </c>
-      <c r="P146" s="9" t="s">
+      <c r="P146" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -11306,7 +11306,7 @@
       <c r="D147" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E147" s="17" t="s">
+      <c r="E147" s="16" t="s">
         <v>554</v>
       </c>
       <c r="F147" s="1" t="s">
@@ -11332,10 +11332,10 @@
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="3"/>
-      <c r="O147" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P147" s="9" t="s">
+      <c r="O147" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P147" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       <c r="D148" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E148" s="17" t="s">
+      <c r="E148" s="16" t="s">
         <v>558</v>
       </c>
       <c r="F148" s="1" t="s">
@@ -11378,14 +11378,14 @@
       </c>
       <c r="M148" s="1"/>
       <c r="N148" s="3"/>
-      <c r="O148" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P148" s="9" t="s">
+      <c r="O148" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P148" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="149" spans="1:16" ht="31.2">
+    <row r="149" spans="1:16" ht="32">
       <c r="A149" s="1" t="s">
         <v>560</v>
       </c>
@@ -11398,7 +11398,7 @@
       <c r="D149" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E149" s="17" t="s">
+      <c r="E149" s="16" t="s">
         <v>561</v>
       </c>
       <c r="F149" s="1" t="s">
@@ -11428,10 +11428,10 @@
       <c r="N149" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="O149" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P149" s="9" t="s">
+      <c r="O149" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P149" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       <c r="D150" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E150" s="17" t="s">
+      <c r="E150" s="16" t="s">
         <v>566</v>
       </c>
       <c r="F150" s="1" t="s">
@@ -11476,10 +11476,10 @@
       <c r="N150" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="O150" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P150" s="9" t="s">
+      <c r="O150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P150" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11496,7 +11496,7 @@
       <c r="D151" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E151" s="17" t="s">
+      <c r="E151" s="16" t="s">
         <v>572</v>
       </c>
       <c r="F151" s="1" t="s">
@@ -11522,10 +11522,10 @@
       </c>
       <c r="M151" s="1"/>
       <c r="N151" s="3"/>
-      <c r="O151" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P151" s="9" t="s">
+      <c r="O151" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P151" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       <c r="D152" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E152" s="17" t="s">
+      <c r="E152" s="16" t="s">
         <v>575</v>
       </c>
       <c r="F152" s="1" t="s">
@@ -11568,10 +11568,10 @@
       </c>
       <c r="M152" s="1"/>
       <c r="N152" s="3"/>
-      <c r="O152" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P152" s="9" t="s">
+      <c r="O152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P152" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11588,7 +11588,7 @@
       <c r="D153" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E153" s="17" t="s">
+      <c r="E153" s="16" t="s">
         <v>578</v>
       </c>
       <c r="F153" s="1" t="s">
@@ -11614,14 +11614,14 @@
       </c>
       <c r="M153" s="1"/>
       <c r="N153" s="3"/>
-      <c r="O153" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P153" s="9" t="s">
+      <c r="O153" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P153" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="154" spans="1:16" ht="46.8">
+    <row r="154" spans="1:16" ht="48">
       <c r="A154" s="1" t="s">
         <v>580</v>
       </c>
@@ -11634,7 +11634,7 @@
       <c r="D154" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E154" s="17" t="s">
+      <c r="E154" s="16" t="s">
         <v>581</v>
       </c>
       <c r="F154" s="1" t="s">
@@ -11662,10 +11662,10 @@
       <c r="N154" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="O154" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P154" s="9" t="s">
+      <c r="O154" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P154" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11682,7 +11682,7 @@
       <c r="D155" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E155" s="17" t="s">
+      <c r="E155" s="16" t="s">
         <v>585</v>
       </c>
       <c r="F155" s="1" t="s">
@@ -11708,10 +11708,10 @@
       </c>
       <c r="M155" s="1"/>
       <c r="N155" s="3"/>
-      <c r="O155" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P155" s="9" t="s">
+      <c r="O155" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P155" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       <c r="D156" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E156" s="17" t="s">
+      <c r="E156" s="16" t="s">
         <v>589</v>
       </c>
       <c r="F156" s="1" t="s">
@@ -11754,14 +11754,14 @@
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="3"/>
-      <c r="O156" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P156" s="9" t="s">
+      <c r="O156" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P156" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="157" spans="1:16" ht="31.2">
+    <row r="157" spans="1:16" ht="32">
       <c r="A157" s="1" t="s">
         <v>592</v>
       </c>
@@ -11774,7 +11774,7 @@
       <c r="D157" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E157" s="17" t="s">
+      <c r="E157" s="16" t="s">
         <v>593</v>
       </c>
       <c r="F157" s="1" t="s">
@@ -11804,10 +11804,10 @@
       <c r="N157" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="O157" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P157" s="9" t="s">
+      <c r="O157" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P157" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       <c r="D158" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E158" s="17" t="s">
+      <c r="E158" s="16" t="s">
         <v>598</v>
       </c>
       <c r="F158" s="1" t="s">
@@ -11850,14 +11850,14 @@
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="3"/>
-      <c r="O158" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P158" s="9" t="s">
+      <c r="O158" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P158" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="159" spans="1:16" ht="31.2">
+    <row r="159" spans="1:16" ht="32">
       <c r="A159" s="1" t="s">
         <v>600</v>
       </c>
@@ -11870,7 +11870,7 @@
       <c r="D159" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E159" s="17" t="s">
+      <c r="E159" s="16" t="s">
         <v>601</v>
       </c>
       <c r="F159" s="1" t="s">
@@ -11898,14 +11898,14 @@
       <c r="N159" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="O159" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P159" s="9" t="s">
+      <c r="O159" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P159" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="160" spans="1:16" ht="46.8">
+    <row r="160" spans="1:16" ht="48">
       <c r="A160" s="1" t="s">
         <v>604</v>
       </c>
@@ -11918,7 +11918,7 @@
       <c r="D160" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E160" s="17" t="s">
+      <c r="E160" s="16" t="s">
         <v>605</v>
       </c>
       <c r="F160" s="1" t="s">
@@ -11948,10 +11948,10 @@
       <c r="N160" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="O160" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P160" s="9" t="s">
+      <c r="O160" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P160" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -11968,7 +11968,7 @@
       <c r="D161" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E161" s="17" t="s">
+      <c r="E161" s="16" t="s">
         <v>609</v>
       </c>
       <c r="F161" s="1" t="s">
@@ -11994,14 +11994,14 @@
       </c>
       <c r="M161" s="1"/>
       <c r="N161" s="3"/>
-      <c r="O161" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P161" s="9" t="s">
+      <c r="O161" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P161" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="162" spans="1:16" ht="31.2">
+    <row r="162" spans="1:16" ht="32">
       <c r="A162" s="1" t="s">
         <v>611</v>
       </c>
@@ -12014,7 +12014,7 @@
       <c r="D162" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E162" s="17" t="s">
+      <c r="E162" s="16" t="s">
         <v>612</v>
       </c>
       <c r="F162" s="1" t="s">
@@ -12044,10 +12044,10 @@
       <c r="N162" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="O162" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P162" s="9" t="s">
+      <c r="O162" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P162" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -12064,13 +12064,13 @@
       <c r="D163" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E163" s="17" t="s">
+      <c r="E163" s="16" t="s">
         <v>886</v>
       </c>
-      <c r="F163" s="4" t="s">
+      <c r="F163" s="17" t="s">
         <v>837</v>
       </c>
-      <c r="G163" s="4">
+      <c r="G163" s="17">
         <v>10</v>
       </c>
       <c r="H163" s="3" t="s">
@@ -12090,10 +12090,10 @@
       </c>
       <c r="M163" s="1"/>
       <c r="N163" s="3"/>
-      <c r="O163" s="9" t="s">
+      <c r="O163" s="8" t="s">
         <v>1105</v>
       </c>
-      <c r="P163" s="9" t="s">
+      <c r="P163" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12110,13 +12110,13 @@
       <c r="D164" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E164" s="17" t="s">
+      <c r="E164" s="16" t="s">
         <v>887</v>
       </c>
-      <c r="F164" s="4" t="s">
+      <c r="F164" s="17" t="s">
         <v>809</v>
       </c>
-      <c r="G164" s="4">
+      <c r="G164" s="17">
         <v>12</v>
       </c>
       <c r="H164" s="3" t="s">
@@ -12136,14 +12136,14 @@
       </c>
       <c r="M164" s="1"/>
       <c r="N164" s="3"/>
-      <c r="O164" s="9" t="s">
+      <c r="O164" s="8" t="s">
         <v>1106</v>
       </c>
-      <c r="P164" s="9" t="s">
+      <c r="P164" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="165" spans="1:16" ht="31.2">
+    <row r="165" spans="1:16" ht="32">
       <c r="A165" s="1" t="s">
         <v>619</v>
       </c>
@@ -12156,7 +12156,7 @@
       <c r="D165" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E165" s="17" t="s">
+      <c r="E165" s="16" t="s">
         <v>620</v>
       </c>
       <c r="F165" s="1" t="s">
@@ -12184,14 +12184,14 @@
       <c r="N165" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="O165" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P165" s="9" t="s">
+      <c r="O165" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P165" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="166" spans="1:16" ht="46.8">
+    <row r="166" spans="1:16" ht="48">
       <c r="A166" s="1" t="s">
         <v>623</v>
       </c>
@@ -12204,7 +12204,7 @@
       <c r="D166" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E166" s="17" t="s">
+      <c r="E166" s="16" t="s">
         <v>624</v>
       </c>
       <c r="F166" s="1" t="s">
@@ -12234,10 +12234,10 @@
       <c r="N166" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="O166" s="9" t="s">
+      <c r="O166" s="8" t="s">
         <v>1107</v>
       </c>
-      <c r="P166" s="9" t="s">
+      <c r="P166" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
       <c r="D167" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E167" s="17" t="s">
+      <c r="E167" s="16" t="s">
         <v>627</v>
       </c>
       <c r="F167" s="1" t="s">
@@ -12280,10 +12280,10 @@
       </c>
       <c r="M167" s="1"/>
       <c r="N167" s="3"/>
-      <c r="O167" s="9" t="s">
+      <c r="O167" s="8" t="s">
         <v>1108</v>
       </c>
-      <c r="P167" s="9" t="s">
+      <c r="P167" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12300,13 +12300,13 @@
       <c r="D168" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E168" s="17" t="s">
+      <c r="E168" s="16" t="s">
         <v>888</v>
       </c>
-      <c r="F168" s="4" t="s">
+      <c r="F168" s="17" t="s">
         <v>897</v>
       </c>
-      <c r="G168" s="4">
+      <c r="G168" s="17">
         <v>12</v>
       </c>
       <c r="H168" s="3" t="s">
@@ -12326,14 +12326,14 @@
       </c>
       <c r="M168" s="1"/>
       <c r="N168" s="3"/>
-      <c r="O168" s="9" t="s">
+      <c r="O168" s="8" t="s">
         <v>1109</v>
       </c>
-      <c r="P168" s="9" t="s">
+      <c r="P168" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="169" spans="1:16" ht="31.2">
+    <row r="169" spans="1:16" ht="32">
       <c r="A169" s="1" t="s">
         <v>633</v>
       </c>
@@ -12346,7 +12346,7 @@
       <c r="D169" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E169" s="17" t="s">
+      <c r="E169" s="16" t="s">
         <v>634</v>
       </c>
       <c r="F169" s="1" t="s">
@@ -12374,10 +12374,10 @@
       <c r="N169" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="O169" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P169" s="9" t="s">
+      <c r="O169" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P169" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -12394,13 +12394,13 @@
       <c r="D170" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E170" s="17" t="s">
+      <c r="E170" s="16" t="s">
         <v>889</v>
       </c>
-      <c r="F170" s="4" t="s">
+      <c r="F170" s="17" t="s">
         <v>810</v>
       </c>
-      <c r="G170" s="4">
+      <c r="G170" s="17">
         <v>12</v>
       </c>
       <c r="H170" s="3" t="s">
@@ -12420,10 +12420,10 @@
       </c>
       <c r="M170" s="1"/>
       <c r="N170" s="3"/>
-      <c r="O170" s="9" t="s">
+      <c r="O170" s="8" t="s">
         <v>1110</v>
       </c>
-      <c r="P170" s="9" t="s">
+      <c r="P170" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12440,13 +12440,13 @@
       <c r="D171" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E171" s="17" t="s">
+      <c r="E171" s="16" t="s">
         <v>890</v>
       </c>
-      <c r="F171" s="4" t="s">
+      <c r="F171" s="17" t="s">
         <v>838</v>
       </c>
-      <c r="G171" s="4">
+      <c r="G171" s="17">
         <v>10</v>
       </c>
       <c r="H171" s="3" t="s">
@@ -12466,10 +12466,10 @@
       </c>
       <c r="M171" s="1"/>
       <c r="N171" s="3"/>
-      <c r="O171" s="9" t="s">
+      <c r="O171" s="8" t="s">
         <v>1111</v>
       </c>
-      <c r="P171" s="9" t="s">
+      <c r="P171" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       <c r="D172" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E172" s="17" t="s">
+      <c r="E172" s="16" t="s">
         <v>642</v>
       </c>
       <c r="F172" s="1" t="s">
@@ -12512,10 +12512,10 @@
       </c>
       <c r="M172" s="1"/>
       <c r="N172" s="3"/>
-      <c r="O172" s="9" t="s">
+      <c r="O172" s="8" t="s">
         <v>1112</v>
       </c>
-      <c r="P172" s="9" t="s">
+      <c r="P172" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12532,13 +12532,13 @@
       <c r="D173" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E173" s="17" t="s">
+      <c r="E173" s="16" t="s">
         <v>891</v>
       </c>
-      <c r="F173" s="4" t="s">
+      <c r="F173" s="17" t="s">
         <v>839</v>
       </c>
-      <c r="G173" s="4">
+      <c r="G173" s="17">
         <v>11</v>
       </c>
       <c r="H173" s="3" t="s">
@@ -12558,10 +12558,10 @@
       </c>
       <c r="M173" s="1"/>
       <c r="N173" s="3"/>
-      <c r="O173" s="9" t="s">
+      <c r="O173" s="8" t="s">
         <v>1113</v>
       </c>
-      <c r="P173" s="9" t="s">
+      <c r="P173" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -12578,7 +12578,7 @@
       <c r="D174" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E174" s="17" t="s">
+      <c r="E174" s="16" t="s">
         <v>647</v>
       </c>
       <c r="F174" s="1" t="s">
@@ -12604,10 +12604,10 @@
       </c>
       <c r="M174" s="1"/>
       <c r="N174" s="3"/>
-      <c r="O174" s="9" t="s">
+      <c r="O174" s="8" t="s">
         <v>1114</v>
       </c>
-      <c r="P174" s="9" t="s">
+      <c r="P174" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       <c r="D175" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E175" s="17" t="s">
+      <c r="E175" s="16" t="s">
         <v>650</v>
       </c>
       <c r="F175" s="1" t="s">
@@ -12650,10 +12650,10 @@
       </c>
       <c r="M175" s="1"/>
       <c r="N175" s="3"/>
-      <c r="O175" s="9" t="s">
+      <c r="O175" s="8" t="s">
         <v>1115</v>
       </c>
-      <c r="P175" s="9" t="s">
+      <c r="P175" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12670,7 +12670,7 @@
       <c r="D176" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E176" s="17" t="s">
+      <c r="E176" s="16" t="s">
         <v>653</v>
       </c>
       <c r="F176" s="1" t="s">
@@ -12696,10 +12696,10 @@
       </c>
       <c r="M176" s="1"/>
       <c r="N176" s="3"/>
-      <c r="O176" s="9" t="s">
+      <c r="O176" s="8" t="s">
         <v>1116</v>
       </c>
-      <c r="P176" s="9" t="s">
+      <c r="P176" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       <c r="D177" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E177" s="17" t="s">
+      <c r="E177" s="16" t="s">
         <v>656</v>
       </c>
       <c r="F177" s="1" t="s">
@@ -12742,10 +12742,10 @@
       </c>
       <c r="M177" s="1"/>
       <c r="N177" s="3"/>
-      <c r="O177" s="9" t="s">
+      <c r="O177" s="8" t="s">
         <v>1117</v>
       </c>
-      <c r="P177" s="9" t="s">
+      <c r="P177" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12762,13 +12762,13 @@
       <c r="D178" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E178" s="17" t="s">
+      <c r="E178" s="16" t="s">
         <v>892</v>
       </c>
-      <c r="F178" s="4" t="s">
+      <c r="F178" s="17" t="s">
         <v>811</v>
       </c>
-      <c r="G178" s="4">
+      <c r="G178" s="17">
         <v>12</v>
       </c>
       <c r="H178" s="3" t="s">
@@ -12788,10 +12788,10 @@
       </c>
       <c r="M178" s="1"/>
       <c r="N178" s="3"/>
-      <c r="O178" s="9" t="s">
+      <c r="O178" s="8" t="s">
         <v>1118</v>
       </c>
-      <c r="P178" s="9" t="s">
+      <c r="P178" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12808,7 +12808,7 @@
       <c r="D179" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E179" s="17" t="s">
+      <c r="E179" s="16" t="s">
         <v>661</v>
       </c>
       <c r="F179" s="1" t="s">
@@ -12834,10 +12834,10 @@
       </c>
       <c r="M179" s="1"/>
       <c r="N179" s="3"/>
-      <c r="O179" s="9" t="s">
+      <c r="O179" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="P179" s="9" t="s">
+      <c r="P179" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12854,7 +12854,7 @@
       <c r="D180" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E180" s="17" t="s">
+      <c r="E180" s="16" t="s">
         <v>664</v>
       </c>
       <c r="F180" s="1" t="s">
@@ -12880,10 +12880,10 @@
       </c>
       <c r="M180" s="1"/>
       <c r="N180" s="3"/>
-      <c r="O180" s="9" t="s">
+      <c r="O180" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="P180" s="9" t="s">
+      <c r="P180" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -12900,7 +12900,7 @@
       <c r="D181" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E181" s="17" t="s">
+      <c r="E181" s="16" t="s">
         <v>667</v>
       </c>
       <c r="F181" s="1" t="s">
@@ -12926,10 +12926,10 @@
       </c>
       <c r="M181" s="1"/>
       <c r="N181" s="3"/>
-      <c r="O181" s="9" t="s">
+      <c r="O181" s="8" t="s">
         <v>1121</v>
       </c>
-      <c r="P181" s="9" t="s">
+      <c r="P181" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       <c r="D182" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E182" s="17" t="s">
+      <c r="E182" s="16" t="s">
         <v>670</v>
       </c>
       <c r="F182" s="1" t="s">
@@ -12972,10 +12972,10 @@
       </c>
       <c r="M182" s="1"/>
       <c r="N182" s="3"/>
-      <c r="O182" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P182" s="9" t="s">
+      <c r="O182" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P182" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -12992,13 +12992,13 @@
       <c r="D183" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E183" s="17" t="s">
+      <c r="E183" s="16" t="s">
         <v>893</v>
       </c>
-      <c r="F183" s="4" t="s">
+      <c r="F183" s="17" t="s">
         <v>840</v>
       </c>
-      <c r="G183" s="4">
+      <c r="G183" s="17">
         <v>10</v>
       </c>
       <c r="H183" s="3" t="s">
@@ -13018,10 +13018,10 @@
       </c>
       <c r="M183" s="1"/>
       <c r="N183" s="3"/>
-      <c r="O183" s="9" t="s">
+      <c r="O183" s="8" t="s">
         <v>1122</v>
       </c>
-      <c r="P183" s="9" t="s">
+      <c r="P183" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -13038,7 +13038,7 @@
       <c r="D184" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E184" s="17" t="s">
+      <c r="E184" s="16" t="s">
         <v>675</v>
       </c>
       <c r="F184" s="1" t="s">
@@ -13064,10 +13064,10 @@
       </c>
       <c r="M184" s="1"/>
       <c r="N184" s="3"/>
-      <c r="O184" s="9" t="s">
+      <c r="O184" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="P184" s="9" t="s">
+      <c r="P184" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -13084,7 +13084,7 @@
       <c r="D185" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E185" s="17" t="s">
+      <c r="E185" s="16" t="s">
         <v>678</v>
       </c>
       <c r="F185" s="1" t="s">
@@ -13110,14 +13110,14 @@
       </c>
       <c r="M185" s="1"/>
       <c r="N185" s="3"/>
-      <c r="O185" s="9" t="s">
+      <c r="O185" s="8" t="s">
         <v>1124</v>
       </c>
-      <c r="P185" s="9" t="s">
+      <c r="P185" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="186" spans="1:16" ht="46.8">
+    <row r="186" spans="1:16" ht="48">
       <c r="A186" s="1" t="s">
         <v>680</v>
       </c>
@@ -13130,13 +13130,13 @@
       <c r="D186" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E186" s="17" t="s">
+      <c r="E186" s="16" t="s">
         <v>894</v>
       </c>
-      <c r="F186" s="4" t="s">
+      <c r="F186" s="17" t="s">
         <v>812</v>
       </c>
-      <c r="G186" s="4">
+      <c r="G186" s="17">
         <v>9</v>
       </c>
       <c r="H186" s="3" t="s">
@@ -13160,10 +13160,10 @@
       <c r="N186" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="O186" s="9" t="s">
+      <c r="O186" s="8" t="s">
         <v>1125</v>
       </c>
-      <c r="P186" s="9" t="s">
+      <c r="P186" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
@@ -13180,7 +13180,7 @@
       <c r="D187" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E187" s="17" t="s">
+      <c r="E187" s="16" t="s">
         <v>683</v>
       </c>
       <c r="F187" s="1" t="s">
@@ -13206,10 +13206,10 @@
       </c>
       <c r="M187" s="1"/>
       <c r="N187" s="3"/>
-      <c r="O187" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P187" s="9" t="s">
+      <c r="O187" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P187" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -13226,7 +13226,7 @@
       <c r="D188" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E188" s="17" t="s">
+      <c r="E188" s="16" t="s">
         <v>686</v>
       </c>
       <c r="F188" s="1" t="s">
@@ -13252,14 +13252,14 @@
       </c>
       <c r="M188" s="1"/>
       <c r="N188" s="3"/>
-      <c r="O188" s="9" t="s">
+      <c r="O188" s="8" t="s">
         <v>1126</v>
       </c>
-      <c r="P188" s="9" t="s">
+      <c r="P188" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="31.2">
+    <row r="189" spans="1:16" ht="32">
       <c r="A189" s="1" t="s">
         <v>689</v>
       </c>
@@ -13272,7 +13272,7 @@
       <c r="D189" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E189" s="17" t="s">
+      <c r="E189" s="16" t="s">
         <v>690</v>
       </c>
       <c r="F189" s="1" t="s">
@@ -13302,10 +13302,10 @@
       <c r="N189" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="O189" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="P189" s="9" t="s">
+      <c r="O189" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="P189" s="8" t="s">
         <v>1030</v>
       </c>
     </row>
@@ -13322,7 +13322,7 @@
       <c r="D190" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E190" s="17" t="s">
+      <c r="E190" s="16" t="s">
         <v>695</v>
       </c>
       <c r="F190" s="1" t="s">
@@ -13348,14 +13348,14 @@
       </c>
       <c r="M190" s="1"/>
       <c r="N190" s="3"/>
-      <c r="O190" s="9" t="s">
+      <c r="O190" s="8" t="s">
         <v>1127</v>
       </c>
-      <c r="P190" s="9" t="s">
+      <c r="P190" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="31.2">
+    <row r="191" spans="1:16" ht="32">
       <c r="A191" s="1" t="s">
         <v>697</v>
       </c>
@@ -13368,13 +13368,13 @@
       <c r="D191" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E191" s="17" t="s">
+      <c r="E191" s="16" t="s">
         <v>698</v>
       </c>
-      <c r="F191" s="4" t="s">
+      <c r="F191" s="17" t="s">
         <v>841</v>
       </c>
-      <c r="G191" s="4">
+      <c r="G191" s="17">
         <v>10</v>
       </c>
       <c r="H191" s="3" t="s">
@@ -13398,1642 +13398,1642 @@
       <c r="N191" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="O191" s="9" t="s">
+      <c r="O191" s="8" t="s">
         <v>1128</v>
       </c>
-      <c r="P191" s="9" t="s">
+      <c r="P191" s="8" t="s">
         <v>1029</v>
       </c>
     </row>
     <row r="192" spans="1:16">
-      <c r="A192" s="9" t="s">
+      <c r="A192" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="B192" s="9" t="s">
+      <c r="B192" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C192" s="9" t="s">
+      <c r="C192" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D192" s="9" t="s">
+      <c r="D192" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E192" s="9" t="s">
+      <c r="E192" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="F192" s="9" t="s">
+      <c r="F192" s="8" t="s">
         <v>900</v>
       </c>
-      <c r="G192" s="9">
+      <c r="G192" s="8">
         <v>11</v>
       </c>
-      <c r="H192" s="10" t="s">
+      <c r="H192" s="9" t="s">
         <v>901</v>
       </c>
-      <c r="I192" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J192" s="9" t="s">
+      <c r="I192" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J192" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="K192" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L192" s="9" t="s">
+      <c r="K192" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L192" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M192" s="9"/>
-      <c r="N192" s="10" t="s">
+      <c r="M192" s="8"/>
+      <c r="N192" s="9" t="s">
         <v>904</v>
       </c>
-      <c r="O192" s="9" t="s">
+      <c r="O192" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="P192" s="9" t="s">
+      <c r="P192" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="193" spans="1:16">
-      <c r="A193" s="9" t="s">
+      <c r="A193" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B193" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C193" s="9" t="s">
+      <c r="C193" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D193" s="9" t="s">
+      <c r="D193" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E193" s="9" t="s">
+      <c r="E193" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="F193" s="9" t="s">
+      <c r="F193" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="G193" s="9">
+      <c r="G193" s="8">
         <v>8</v>
       </c>
-      <c r="H193" s="10" t="s">
+      <c r="H193" s="9" t="s">
         <v>907</v>
       </c>
-      <c r="I193" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J193" s="9" t="s">
+      <c r="I193" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J193" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="K193" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L193" s="9" t="s">
+      <c r="K193" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L193" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M193" s="9"/>
-      <c r="N193" s="10" t="s">
+      <c r="M193" s="8"/>
+      <c r="N193" s="9" t="s">
         <v>909</v>
       </c>
-      <c r="O193" s="9" t="s">
+      <c r="O193" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="P193" s="9" t="s">
+      <c r="P193" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="194" spans="1:16">
-      <c r="A194" s="9" t="s">
+      <c r="A194" s="8" t="s">
         <v>910</v>
       </c>
-      <c r="B194" s="9" t="s">
+      <c r="B194" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C194" s="9" t="s">
+      <c r="C194" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D194" s="9" t="s">
+      <c r="D194" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E194" s="9" t="s">
+      <c r="E194" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="F194" s="9" t="s">
+      <c r="F194" s="8" t="s">
         <v>911</v>
       </c>
-      <c r="G194" s="9">
+      <c r="G194" s="8">
         <v>10</v>
       </c>
-      <c r="H194" s="10" t="s">
+      <c r="H194" s="9" t="s">
         <v>912</v>
       </c>
-      <c r="I194" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J194" s="9" t="s">
+      <c r="I194" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J194" s="8" t="s">
         <v>913</v>
       </c>
-      <c r="K194" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L194" s="9" t="s">
+      <c r="K194" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L194" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M194" s="9"/>
-      <c r="N194" s="10" t="s">
+      <c r="M194" s="8"/>
+      <c r="N194" s="9" t="s">
         <v>914</v>
       </c>
-      <c r="O194" s="9" t="s">
+      <c r="O194" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="P194" s="9" t="s">
+      <c r="P194" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="195" spans="1:16">
-      <c r="A195" s="9" t="s">
+      <c r="A195" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="B195" s="9" t="s">
+      <c r="B195" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C195" s="9" t="s">
+      <c r="C195" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D195" s="9" t="s">
+      <c r="D195" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E195" s="9" t="s">
+      <c r="E195" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="F195" s="9" t="s">
+      <c r="F195" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="G195" s="9">
+      <c r="G195" s="8">
         <v>11</v>
       </c>
-      <c r="H195" s="10" t="s">
+      <c r="H195" s="9" t="s">
         <v>917</v>
       </c>
-      <c r="I195" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J195" s="9" t="s">
+      <c r="I195" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J195" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K195" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L195" s="9" t="s">
+      <c r="K195" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L195" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M195" s="9"/>
-      <c r="N195" s="10" t="s">
+      <c r="M195" s="8"/>
+      <c r="N195" s="9" t="s">
         <v>919</v>
       </c>
-      <c r="O195" s="9" t="s">
+      <c r="O195" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="P195" s="9" t="s">
+      <c r="P195" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="196" spans="1:16">
-      <c r="A196" s="9" t="s">
+      <c r="A196" s="8" t="s">
         <v>920</v>
       </c>
-      <c r="B196" s="9" t="s">
+      <c r="B196" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C196" s="9" t="s">
+      <c r="C196" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D196" s="9" t="s">
+      <c r="D196" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E196" s="9" t="s">
+      <c r="E196" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="F196" s="9" t="s">
+      <c r="F196" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="G196" s="9">
+      <c r="G196" s="8">
         <v>10</v>
       </c>
-      <c r="H196" s="10" t="s">
+      <c r="H196" s="9" t="s">
         <v>922</v>
       </c>
-      <c r="I196" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J196" s="9" t="s">
+      <c r="I196" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J196" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="K196" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L196" s="9" t="s">
+      <c r="K196" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L196" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M196" s="9"/>
-      <c r="N196" s="10" t="s">
+      <c r="M196" s="8"/>
+      <c r="N196" s="9" t="s">
         <v>924</v>
       </c>
-      <c r="O196" s="9" t="s">
+      <c r="O196" s="8" t="s">
         <v>1133</v>
       </c>
-      <c r="P196" s="9" t="s">
+      <c r="P196" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="197" spans="1:16">
-      <c r="A197" s="9" t="s">
+      <c r="A197" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="B197" s="9" t="s">
+      <c r="B197" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C197" s="9" t="s">
+      <c r="C197" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D197" s="9" t="s">
+      <c r="D197" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E197" s="9" t="s">
+      <c r="E197" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="F197" s="9" t="s">
+      <c r="F197" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="G197" s="9">
+      <c r="G197" s="8">
         <v>11</v>
       </c>
-      <c r="H197" s="10" t="s">
+      <c r="H197" s="9" t="s">
         <v>927</v>
       </c>
-      <c r="I197" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J197" s="9" t="s">
+      <c r="I197" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J197" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="K197" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L197" s="9" t="s">
+      <c r="K197" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L197" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M197" s="9"/>
-      <c r="N197" s="10" t="s">
+      <c r="M197" s="8"/>
+      <c r="N197" s="9" t="s">
         <v>929</v>
       </c>
-      <c r="O197" s="9" t="s">
+      <c r="O197" s="8" t="s">
         <v>1134</v>
       </c>
-      <c r="P197" s="9" t="s">
+      <c r="P197" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="198" spans="1:16">
-      <c r="A198" s="9" t="s">
+      <c r="A198" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="B198" s="9" t="s">
+      <c r="B198" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C198" s="9" t="s">
+      <c r="C198" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D198" s="9" t="s">
+      <c r="D198" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E198" s="9" t="s">
+      <c r="E198" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="F198" s="9" t="s">
+      <c r="F198" s="8" t="s">
         <v>931</v>
       </c>
-      <c r="G198" s="9">
+      <c r="G198" s="8">
         <v>10</v>
       </c>
-      <c r="H198" s="10" t="s">
+      <c r="H198" s="9" t="s">
         <v>932</v>
       </c>
-      <c r="I198" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J198" s="9" t="s">
+      <c r="I198" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J198" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="K198" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L198" s="9" t="s">
+      <c r="K198" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L198" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M198" s="9"/>
-      <c r="N198" s="10" t="s">
+      <c r="M198" s="8"/>
+      <c r="N198" s="9" t="s">
         <v>933</v>
       </c>
-      <c r="O198" s="9" t="s">
+      <c r="O198" s="8" t="s">
         <v>1135</v>
       </c>
-      <c r="P198" s="9" t="s">
+      <c r="P198" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="199" spans="1:16">
-      <c r="A199" s="9" t="s">
+      <c r="A199" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="B199" s="9" t="s">
+      <c r="B199" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C199" s="9" t="s">
+      <c r="C199" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D199" s="9" t="s">
+      <c r="D199" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E199" s="9" t="s">
+      <c r="E199" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="F199" s="9" t="s">
+      <c r="F199" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="G199" s="9">
+      <c r="G199" s="8">
         <v>12</v>
       </c>
-      <c r="H199" s="10" t="s">
+      <c r="H199" s="9" t="s">
         <v>936</v>
       </c>
-      <c r="I199" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J199" s="9" t="s">
+      <c r="I199" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J199" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K199" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L199" s="9" t="s">
+      <c r="K199" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L199" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M199" s="9"/>
-      <c r="N199" s="10" t="s">
+      <c r="M199" s="8"/>
+      <c r="N199" s="9" t="s">
         <v>938</v>
       </c>
-      <c r="O199" s="9" t="s">
+      <c r="O199" s="8" t="s">
         <v>1136</v>
       </c>
-      <c r="P199" s="9" t="s">
+      <c r="P199" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="200" spans="1:16">
-      <c r="A200" s="9" t="s">
+      <c r="A200" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="B200" s="9" t="s">
+      <c r="B200" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C200" s="9" t="s">
+      <c r="C200" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D200" s="9" t="s">
+      <c r="D200" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E200" s="9" t="s">
+      <c r="E200" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="F200" s="9" t="s">
+      <c r="F200" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="G200" s="9">
+      <c r="G200" s="8">
         <v>12</v>
       </c>
-      <c r="H200" s="10" t="s">
+      <c r="H200" s="9" t="s">
         <v>941</v>
       </c>
-      <c r="I200" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J200" s="9" t="s">
+      <c r="I200" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J200" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="K200" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L200" s="9" t="s">
+      <c r="K200" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L200" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M200" s="9"/>
-      <c r="N200" s="10" t="s">
+      <c r="M200" s="8"/>
+      <c r="N200" s="9" t="s">
         <v>943</v>
       </c>
-      <c r="O200" s="9" t="s">
+      <c r="O200" s="8" t="s">
         <v>1137</v>
       </c>
-      <c r="P200" s="9" t="s">
+      <c r="P200" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="201" spans="1:16">
-      <c r="A201" s="9" t="s">
+      <c r="A201" s="8" t="s">
         <v>944</v>
       </c>
-      <c r="B201" s="9" t="s">
+      <c r="B201" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C201" s="9" t="s">
+      <c r="C201" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D201" s="9" t="s">
+      <c r="D201" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E201" s="9" t="s">
+      <c r="E201" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="F201" s="9" t="s">
+      <c r="F201" s="8" t="s">
         <v>945</v>
       </c>
-      <c r="G201" s="9">
+      <c r="G201" s="8">
         <v>12</v>
       </c>
-      <c r="H201" s="10" t="s">
+      <c r="H201" s="9" t="s">
         <v>946</v>
       </c>
-      <c r="I201" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J201" s="9" t="s">
+      <c r="I201" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J201" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="K201" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L201" s="9" t="s">
+      <c r="K201" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L201" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M201" s="9"/>
-      <c r="N201" s="10" t="s">
+      <c r="M201" s="8"/>
+      <c r="N201" s="9" t="s">
         <v>947</v>
       </c>
-      <c r="O201" s="9" t="s">
+      <c r="O201" s="8" t="s">
         <v>1138</v>
       </c>
-      <c r="P201" s="9" t="s">
+      <c r="P201" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="202" spans="1:16">
-      <c r="A202" s="9" t="s">
+      <c r="A202" s="8" t="s">
         <v>948</v>
       </c>
-      <c r="B202" s="9" t="s">
+      <c r="B202" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C202" s="9" t="s">
+      <c r="C202" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D202" s="9" t="s">
+      <c r="D202" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E202" s="9" t="s">
+      <c r="E202" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="F202" s="9" t="s">
+      <c r="F202" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="G202" s="9">
+      <c r="G202" s="8">
         <v>11</v>
       </c>
-      <c r="H202" s="10" t="s">
+      <c r="H202" s="9" t="s">
         <v>950</v>
       </c>
-      <c r="I202" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J202" s="9" t="s">
+      <c r="I202" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J202" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="K202" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L202" s="9" t="s">
+      <c r="K202" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L202" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M202" s="9"/>
-      <c r="N202" s="10" t="s">
+      <c r="M202" s="8"/>
+      <c r="N202" s="9" t="s">
         <v>951</v>
       </c>
-      <c r="O202" s="9" t="s">
+      <c r="O202" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="P202" s="9" t="s">
+      <c r="P202" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="203" spans="1:16">
-      <c r="A203" s="9" t="s">
+      <c r="A203" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="B203" s="9" t="s">
+      <c r="B203" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C203" s="9" t="s">
+      <c r="C203" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D203" s="9" t="s">
+      <c r="D203" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E203" s="9" t="s">
+      <c r="E203" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="F203" s="9" t="s">
+      <c r="F203" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="G203" s="9">
+      <c r="G203" s="8">
         <v>10</v>
       </c>
-      <c r="H203" s="10" t="s">
+      <c r="H203" s="9" t="s">
         <v>954</v>
       </c>
-      <c r="I203" s="9" t="s">
+      <c r="I203" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J203" s="9" t="s">
+      <c r="J203" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="K203" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L203" s="9" t="s">
+      <c r="K203" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L203" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M203" s="9"/>
-      <c r="N203" s="10" t="s">
+      <c r="M203" s="8"/>
+      <c r="N203" s="9" t="s">
         <v>955</v>
       </c>
-      <c r="O203" s="9" t="s">
+      <c r="O203" s="8" t="s">
         <v>1140</v>
       </c>
-      <c r="P203" s="9" t="s">
+      <c r="P203" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="204" spans="1:16">
-      <c r="A204" s="9" t="s">
+      <c r="A204" s="8" t="s">
         <v>956</v>
       </c>
-      <c r="B204" s="9" t="s">
+      <c r="B204" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C204" s="9" t="s">
+      <c r="C204" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D204" s="9" t="s">
+      <c r="D204" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E204" s="9" t="s">
+      <c r="E204" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="F204" s="9" t="s">
+      <c r="F204" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="G204" s="9">
+      <c r="G204" s="8">
         <v>10</v>
       </c>
-      <c r="H204" s="10" t="s">
+      <c r="H204" s="9" t="s">
         <v>958</v>
       </c>
-      <c r="I204" s="9" t="s">
+      <c r="I204" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J204" s="9" t="s">
+      <c r="J204" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="K204" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L204" s="9" t="s">
+      <c r="K204" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L204" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M204" s="9"/>
-      <c r="N204" s="10" t="s">
+      <c r="M204" s="8"/>
+      <c r="N204" s="9" t="s">
         <v>959</v>
       </c>
-      <c r="O204" s="9" t="s">
+      <c r="O204" s="8" t="s">
         <v>1141</v>
       </c>
-      <c r="P204" s="9" t="s">
+      <c r="P204" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="205" spans="1:16">
-      <c r="A205" s="9" t="s">
+      <c r="A205" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="B205" s="9" t="s">
+      <c r="B205" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C205" s="9" t="s">
+      <c r="C205" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D205" s="9" t="s">
+      <c r="D205" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E205" s="9" t="s">
+      <c r="E205" s="8" t="s">
         <v>961</v>
       </c>
-      <c r="F205" s="9" t="s">
+      <c r="F205" s="8" t="s">
         <v>961</v>
       </c>
-      <c r="G205" s="9">
+      <c r="G205" s="8">
         <v>10</v>
       </c>
-      <c r="H205" s="10" t="s">
+      <c r="H205" s="9" t="s">
         <v>962</v>
       </c>
-      <c r="I205" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J205" s="9" t="s">
+      <c r="I205" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J205" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="K205" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L205" s="9" t="s">
+      <c r="K205" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L205" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M205" s="9"/>
-      <c r="N205" s="10" t="s">
+      <c r="M205" s="8"/>
+      <c r="N205" s="9" t="s">
         <v>963</v>
       </c>
-      <c r="O205" s="9" t="s">
+      <c r="O205" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="P205" s="9" t="s">
+      <c r="P205" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="206" spans="1:16">
-      <c r="A206" s="9" t="s">
+      <c r="A206" s="8" t="s">
         <v>964</v>
       </c>
-      <c r="B206" s="9" t="s">
+      <c r="B206" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C206" s="9" t="s">
+      <c r="C206" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D206" s="9" t="s">
+      <c r="D206" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E206" s="9" t="s">
+      <c r="E206" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="F206" s="9" t="s">
+      <c r="F206" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="G206" s="9">
+      <c r="G206" s="8">
         <v>10</v>
       </c>
-      <c r="H206" s="10" t="s">
+      <c r="H206" s="9" t="s">
         <v>966</v>
       </c>
-      <c r="I206" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J206" s="9" t="s">
+      <c r="I206" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J206" s="8" t="s">
         <v>923</v>
       </c>
-      <c r="K206" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L206" s="9" t="s">
+      <c r="K206" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L206" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M206" s="9"/>
-      <c r="N206" s="10" t="s">
+      <c r="M206" s="8"/>
+      <c r="N206" s="9" t="s">
         <v>967</v>
       </c>
-      <c r="O206" s="9" t="s">
+      <c r="O206" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="P206" s="9" t="s">
+      <c r="P206" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="207" spans="1:16">
-      <c r="A207" s="9" t="s">
+      <c r="A207" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="B207" s="9" t="s">
+      <c r="B207" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C207" s="9" t="s">
+      <c r="C207" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D207" s="9" t="s">
+      <c r="D207" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E207" s="9" t="s">
+      <c r="E207" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="F207" s="9" t="s">
+      <c r="F207" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="G207" s="9">
+      <c r="G207" s="8">
         <v>9</v>
       </c>
-      <c r="H207" s="10" t="s">
+      <c r="H207" s="9" t="s">
         <v>970</v>
       </c>
-      <c r="I207" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J207" s="9" t="s">
+      <c r="I207" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J207" s="8" t="s">
         <v>971</v>
       </c>
-      <c r="K207" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L207" s="9" t="s">
+      <c r="K207" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L207" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M207" s="9"/>
-      <c r="N207" s="10" t="s">
+      <c r="M207" s="8"/>
+      <c r="N207" s="9" t="s">
         <v>972</v>
       </c>
-      <c r="O207" s="9" t="s">
+      <c r="O207" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="P207" s="9" t="s">
+      <c r="P207" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="208" spans="1:16">
-      <c r="A208" s="9" t="s">
+      <c r="A208" s="8" t="s">
         <v>973</v>
       </c>
-      <c r="B208" s="9" t="s">
+      <c r="B208" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C208" s="9" t="s">
+      <c r="C208" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D208" s="9" t="s">
+      <c r="D208" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E208" s="9" t="s">
+      <c r="E208" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="F208" s="9" t="s">
+      <c r="F208" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="G208" s="9">
+      <c r="G208" s="8">
         <v>10</v>
       </c>
-      <c r="H208" s="10" t="s">
+      <c r="H208" s="9" t="s">
         <v>975</v>
       </c>
-      <c r="I208" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J208" s="9" t="s">
+      <c r="I208" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J208" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K208" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L208" s="9" t="s">
+      <c r="K208" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L208" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M208" s="9"/>
-      <c r="N208" s="10" t="s">
+      <c r="M208" s="8"/>
+      <c r="N208" s="9" t="s">
         <v>976</v>
       </c>
-      <c r="O208" s="9" t="s">
+      <c r="O208" s="8" t="s">
         <v>1145</v>
       </c>
-      <c r="P208" s="9" t="s">
+      <c r="P208" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="209" spans="1:16">
-      <c r="A209" s="9" t="s">
+      <c r="A209" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="B209" s="9" t="s">
+      <c r="B209" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C209" s="9" t="s">
+      <c r="C209" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D209" s="9" t="s">
+      <c r="D209" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E209" s="9" t="s">
+      <c r="E209" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="F209" s="9" t="s">
+      <c r="F209" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="G209" s="9">
+      <c r="G209" s="8">
         <v>11</v>
       </c>
-      <c r="H209" s="10" t="s">
+      <c r="H209" s="9" t="s">
         <v>979</v>
       </c>
-      <c r="I209" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J209" s="9" t="s">
+      <c r="I209" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J209" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K209" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L209" s="9" t="s">
+      <c r="K209" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L209" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M209" s="9"/>
-      <c r="N209" s="10" t="s">
+      <c r="M209" s="8"/>
+      <c r="N209" s="9" t="s">
         <v>980</v>
       </c>
-      <c r="O209" s="9" t="s">
+      <c r="O209" s="8" t="s">
         <v>1146</v>
       </c>
-      <c r="P209" s="9" t="s">
+      <c r="P209" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="210" spans="1:16">
-      <c r="A210" s="9" t="s">
+      <c r="A210" s="8" t="s">
         <v>981</v>
       </c>
-      <c r="B210" s="9" t="s">
+      <c r="B210" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C210" s="9" t="s">
+      <c r="C210" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D210" s="9" t="s">
+      <c r="D210" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E210" s="9" t="s">
+      <c r="E210" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="F210" s="9" t="s">
+      <c r="F210" s="8" t="s">
         <v>982</v>
       </c>
-      <c r="G210" s="9">
+      <c r="G210" s="8">
         <v>8</v>
       </c>
-      <c r="H210" s="10" t="s">
+      <c r="H210" s="9" t="s">
         <v>983</v>
       </c>
-      <c r="I210" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J210" s="9" t="s">
+      <c r="I210" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J210" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K210" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L210" s="9" t="s">
+      <c r="K210" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L210" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M210" s="9"/>
-      <c r="N210" s="10" t="s">
+      <c r="M210" s="8"/>
+      <c r="N210" s="9" t="s">
         <v>984</v>
       </c>
-      <c r="O210" s="9" t="s">
+      <c r="O210" s="8" t="s">
         <v>1147</v>
       </c>
-      <c r="P210" s="9" t="s">
+      <c r="P210" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="211" spans="1:16">
-      <c r="A211" s="9" t="s">
+      <c r="A211" s="8" t="s">
         <v>985</v>
       </c>
-      <c r="B211" s="9" t="s">
+      <c r="B211" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C211" s="9" t="s">
+      <c r="C211" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D211" s="9" t="s">
+      <c r="D211" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E211" s="9" t="s">
+      <c r="E211" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="F211" s="9" t="s">
+      <c r="F211" s="8" t="s">
         <v>986</v>
       </c>
-      <c r="G211" s="9">
+      <c r="G211" s="8">
         <v>10</v>
       </c>
-      <c r="H211" s="10" t="s">
+      <c r="H211" s="9" t="s">
         <v>987</v>
       </c>
-      <c r="I211" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J211" s="9" t="s">
+      <c r="I211" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J211" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="K211" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L211" s="9" t="s">
+      <c r="K211" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L211" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M211" s="9"/>
-      <c r="N211" s="10" t="s">
+      <c r="M211" s="8"/>
+      <c r="N211" s="9" t="s">
         <v>989</v>
       </c>
-      <c r="O211" s="9" t="s">
+      <c r="O211" s="8" t="s">
         <v>1148</v>
       </c>
-      <c r="P211" s="9" t="s">
+      <c r="P211" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="212" spans="1:16">
-      <c r="A212" s="9" t="s">
+      <c r="A212" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="B212" s="9" t="s">
+      <c r="B212" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C212" s="9" t="s">
+      <c r="C212" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D212" s="9" t="s">
+      <c r="D212" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E212" s="9" t="s">
+      <c r="E212" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="F212" s="9" t="s">
+      <c r="F212" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="G212" s="9">
+      <c r="G212" s="8">
         <v>11</v>
       </c>
-      <c r="H212" s="10" t="s">
+      <c r="H212" s="9" t="s">
         <v>992</v>
       </c>
-      <c r="I212" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J212" s="9" t="s">
+      <c r="I212" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J212" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="K212" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L212" s="9" t="s">
+      <c r="K212" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L212" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M212" s="9"/>
-      <c r="N212" s="10" t="s">
+      <c r="M212" s="8"/>
+      <c r="N212" s="9" t="s">
         <v>993</v>
       </c>
-      <c r="O212" s="9" t="s">
+      <c r="O212" s="8" t="s">
         <v>1149</v>
       </c>
-      <c r="P212" s="9" t="s">
+      <c r="P212" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="213" spans="1:16">
-      <c r="A213" s="9" t="s">
+      <c r="A213" s="8" t="s">
         <v>994</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="B213" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C213" s="9" t="s">
+      <c r="C213" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D213" s="9" t="s">
+      <c r="D213" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E213" s="9" t="s">
+      <c r="E213" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="F213" s="9" t="s">
+      <c r="F213" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="G213" s="9">
+      <c r="G213" s="8">
         <v>11</v>
       </c>
-      <c r="H213" s="10" t="s">
+      <c r="H213" s="9" t="s">
         <v>996</v>
       </c>
-      <c r="I213" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J213" s="9" t="s">
+      <c r="I213" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J213" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="K213" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L213" s="9" t="s">
+      <c r="K213" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L213" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M213" s="9"/>
-      <c r="N213" s="10" t="s">
+      <c r="M213" s="8"/>
+      <c r="N213" s="9" t="s">
         <v>997</v>
       </c>
-      <c r="O213" s="9" t="s">
+      <c r="O213" s="8" t="s">
         <v>1150</v>
       </c>
-      <c r="P213" s="9" t="s">
+      <c r="P213" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="214" spans="1:16">
-      <c r="A214" s="9" t="s">
+      <c r="A214" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B214" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C214" s="9" t="s">
+      <c r="C214" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D214" s="9" t="s">
+      <c r="D214" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E214" s="9" t="s">
+      <c r="E214" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="F214" s="9" t="s">
+      <c r="F214" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="G214" s="9">
+      <c r="G214" s="8">
         <v>11</v>
       </c>
-      <c r="H214" s="10" t="s">
+      <c r="H214" s="9" t="s">
         <v>1000</v>
       </c>
-      <c r="I214" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J214" s="9" t="s">
+      <c r="I214" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J214" s="8" t="s">
         <v>942</v>
       </c>
-      <c r="K214" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L214" s="9" t="s">
+      <c r="K214" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L214" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M214" s="9"/>
-      <c r="N214" s="10" t="s">
+      <c r="M214" s="8"/>
+      <c r="N214" s="9" t="s">
         <v>1001</v>
       </c>
-      <c r="O214" s="9" t="s">
+      <c r="O214" s="8" t="s">
         <v>1151</v>
       </c>
-      <c r="P214" s="9" t="s">
+      <c r="P214" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="215" spans="1:16">
-      <c r="A215" s="9" t="s">
+      <c r="A215" s="8" t="s">
         <v>1002</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B215" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C215" s="9" t="s">
+      <c r="C215" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D215" s="9" t="s">
+      <c r="D215" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E215" s="9" t="s">
+      <c r="E215" s="8" t="s">
         <v>1003</v>
       </c>
-      <c r="F215" s="9" t="s">
+      <c r="F215" s="8" t="s">
         <v>1003</v>
       </c>
-      <c r="G215" s="9">
+      <c r="G215" s="8">
         <v>8</v>
       </c>
-      <c r="H215" s="10" t="s">
+      <c r="H215" s="9" t="s">
         <v>1004</v>
       </c>
-      <c r="I215" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J215" s="9" t="s">
+      <c r="I215" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J215" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K215" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L215" s="9" t="s">
+      <c r="K215" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L215" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M215" s="9"/>
-      <c r="N215" s="10" t="s">
+      <c r="M215" s="8"/>
+      <c r="N215" s="9" t="s">
         <v>1005</v>
       </c>
-      <c r="O215" s="9" t="s">
+      <c r="O215" s="8" t="s">
         <v>1152</v>
       </c>
-      <c r="P215" s="9" t="s">
+      <c r="P215" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="216" spans="1:16">
-      <c r="A216" s="9" t="s">
+      <c r="A216" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="B216" s="9" t="s">
+      <c r="B216" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C216" s="9" t="s">
+      <c r="C216" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D216" s="9" t="s">
+      <c r="D216" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E216" s="9" t="s">
+      <c r="E216" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="F216" s="9" t="s">
+      <c r="F216" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="G216" s="9">
+      <c r="G216" s="8">
         <v>10</v>
       </c>
-      <c r="H216" s="10" t="s">
+      <c r="H216" s="9" t="s">
         <v>1008</v>
       </c>
-      <c r="I216" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J216" s="9" t="s">
+      <c r="I216" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J216" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="K216" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L216" s="9" t="s">
+      <c r="K216" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L216" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M216" s="9"/>
-      <c r="N216" s="10" t="s">
+      <c r="M216" s="8"/>
+      <c r="N216" s="9" t="s">
         <v>1009</v>
       </c>
-      <c r="O216" s="9" t="s">
+      <c r="O216" s="8" t="s">
         <v>1153</v>
       </c>
-      <c r="P216" s="9" t="s">
+      <c r="P216" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" s="9" t="s">
+      <c r="A217" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="B217" s="9" t="s">
+      <c r="B217" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C217" s="9" t="s">
+      <c r="C217" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D217" s="9" t="s">
+      <c r="D217" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E217" s="9" t="s">
+      <c r="E217" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="F217" s="9" t="s">
+      <c r="F217" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="G217" s="9">
+      <c r="G217" s="8">
         <v>10</v>
       </c>
-      <c r="H217" s="10" t="s">
+      <c r="H217" s="9" t="s">
         <v>1012</v>
       </c>
-      <c r="I217" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J217" s="9" t="s">
+      <c r="I217" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J217" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="K217" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L217" s="9" t="s">
+      <c r="K217" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L217" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M217" s="9"/>
-      <c r="N217" s="10" t="s">
+      <c r="M217" s="8"/>
+      <c r="N217" s="9" t="s">
         <v>1013</v>
       </c>
-      <c r="O217" s="9" t="s">
+      <c r="O217" s="8" t="s">
         <v>1154</v>
       </c>
-      <c r="P217" s="9" t="s">
+      <c r="P217" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" s="9" t="s">
+      <c r="A218" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="B218" s="9" t="s">
+      <c r="B218" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C218" s="9" t="s">
+      <c r="C218" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D218" s="9" t="s">
+      <c r="D218" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E218" s="9" t="s">
+      <c r="E218" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="F218" s="9" t="s">
+      <c r="F218" s="8" t="s">
         <v>1015</v>
       </c>
-      <c r="G218" s="9">
+      <c r="G218" s="8">
         <v>10</v>
       </c>
-      <c r="H218" s="10" t="s">
+      <c r="H218" s="9" t="s">
         <v>1016</v>
       </c>
-      <c r="I218" s="9" t="s">
+      <c r="I218" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="J218" s="9" t="s">
+      <c r="J218" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="K218" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L218" s="9" t="s">
+      <c r="K218" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L218" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M218" s="9"/>
-      <c r="N218" s="10" t="s">
+      <c r="M218" s="8"/>
+      <c r="N218" s="9" t="s">
         <v>1017</v>
       </c>
-      <c r="O218" s="9" t="s">
+      <c r="O218" s="8" t="s">
         <v>1155</v>
       </c>
-      <c r="P218" s="9" t="s">
+      <c r="P218" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="219" spans="1:16">
-      <c r="A219" s="9" t="s">
+      <c r="A219" s="8" t="s">
         <v>1018</v>
       </c>
-      <c r="B219" s="9" t="s">
+      <c r="B219" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C219" s="9" t="s">
+      <c r="C219" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="D219" s="9" t="s">
+      <c r="D219" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E219" s="9" t="s">
+      <c r="E219" s="8" t="s">
         <v>1019</v>
       </c>
-      <c r="F219" s="9" t="s">
+      <c r="F219" s="8" t="s">
         <v>1019</v>
       </c>
-      <c r="G219" s="9">
+      <c r="G219" s="8">
         <v>11</v>
       </c>
-      <c r="H219" s="10" t="s">
+      <c r="H219" s="9" t="s">
         <v>1020</v>
       </c>
-      <c r="I219" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J219" s="9" t="s">
+      <c r="I219" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J219" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="K219" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L219" s="9" t="s">
+      <c r="K219" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L219" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M219" s="9"/>
-      <c r="N219" s="10" t="s">
+      <c r="M219" s="8"/>
+      <c r="N219" s="9" t="s">
         <v>1021</v>
       </c>
-      <c r="O219" s="9" t="s">
+      <c r="O219" s="8" t="s">
         <v>1156</v>
       </c>
-      <c r="P219" s="9" t="s">
+      <c r="P219" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
     <row r="220" spans="1:16">
-      <c r="A220" s="9" t="s">
+      <c r="A220" s="8" t="s">
         <v>1022</v>
       </c>
-      <c r="B220" s="9" t="s">
+      <c r="B220" s="8" t="s">
         <v>899</v>
       </c>
-      <c r="C220" s="9" t="s">
+      <c r="C220" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="D220" s="9" t="s">
+      <c r="D220" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E220" s="9" t="s">
+      <c r="E220" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="F220" s="9" t="s">
+      <c r="F220" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="G220" s="9">
+      <c r="G220" s="8">
         <v>7</v>
       </c>
-      <c r="H220" s="10" t="s">
+      <c r="H220" s="9" t="s">
         <v>1024</v>
       </c>
-      <c r="I220" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J220" s="9" t="s">
+      <c r="I220" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J220" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="K220" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L220" s="9" t="s">
+      <c r="K220" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L220" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="M220" s="9"/>
-      <c r="N220" s="10" t="s">
+      <c r="M220" s="8"/>
+      <c r="N220" s="9" t="s">
         <v>1025</v>
       </c>
-      <c r="O220" s="9" t="s">
+      <c r="O220" s="8" t="s">
         <v>1157</v>
       </c>
-      <c r="P220" s="9" t="s">
+      <c r="P220" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="221" spans="1:16" ht="46.8">
-      <c r="A221" s="9" t="s">
+    <row r="221" spans="1:16" ht="48">
+      <c r="A221" s="8" t="s">
         <v>1160</v>
       </c>
-      <c r="B221" s="9" t="s">
+      <c r="B221" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="C221" s="9" t="s">
+      <c r="C221" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D221" s="9" t="s">
+      <c r="D221" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E221" s="9" t="s">
+      <c r="E221" s="8" t="s">
         <v>1162</v>
       </c>
-      <c r="F221" s="9" t="s">
+      <c r="F221" s="8" t="s">
         <v>1162</v>
       </c>
-      <c r="G221" s="9">
+      <c r="G221" s="8">
         <v>13</v>
       </c>
-      <c r="H221" s="10" t="s">
+      <c r="H221" s="9" t="s">
         <v>1163</v>
       </c>
-      <c r="I221" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J221" s="9" t="s">
+      <c r="I221" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J221" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="K221" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L221" s="9" t="s">
+      <c r="K221" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L221" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="M221" s="9"/>
-      <c r="N221" s="10" t="s">
+      <c r="M221" s="8"/>
+      <c r="N221" s="9" t="s">
         <v>1184</v>
       </c>
-      <c r="O221" s="9" t="s">
+      <c r="O221" s="8" t="s">
         <v>1185</v>
       </c>
-      <c r="P221" s="9" t="s">
+      <c r="P221" s="8" t="s">
         <v>1186</v>
       </c>
     </row>
-    <row r="222" spans="1:16" ht="46.8">
-      <c r="A222" s="9" t="s">
+    <row r="222" spans="1:16" ht="48">
+      <c r="A222" s="8" t="s">
         <v>1164</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="B222" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="C222" s="9" t="s">
+      <c r="C222" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D222" s="9" t="s">
+      <c r="D222" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E222" s="9" t="s">
+      <c r="E222" s="8" t="s">
         <v>1165</v>
       </c>
-      <c r="F222" s="9" t="s">
+      <c r="F222" s="8" t="s">
         <v>1165</v>
       </c>
-      <c r="G222" s="9">
+      <c r="G222" s="8">
         <v>11</v>
       </c>
-      <c r="H222" s="10" t="s">
+      <c r="H222" s="9" t="s">
         <v>1166</v>
       </c>
-      <c r="I222" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="J222" s="9" t="s">
+      <c r="I222" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J222" s="8" t="s">
         <v>1187</v>
       </c>
-      <c r="K222" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L222" s="9" t="s">
+      <c r="K222" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L222" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="M222" s="9"/>
-      <c r="N222" s="10" t="s">
+      <c r="M222" s="8"/>
+      <c r="N222" s="9" t="s">
         <v>1188</v>
       </c>
-      <c r="O222" s="9" t="s">
+      <c r="O222" s="8" t="s">
         <v>1189</v>
       </c>
-      <c r="P222" s="9" t="s">
+      <c r="P222" s="8" t="s">
         <v>1186</v>
       </c>
     </row>
-    <row r="223" spans="1:16" ht="46.8">
-      <c r="A223" s="9" t="s">
+    <row r="223" spans="1:16" ht="48">
+      <c r="A223" s="8" t="s">
         <v>1167</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B223" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="C223" s="9" t="s">
+      <c r="C223" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D223" s="9" t="s">
+      <c r="D223" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E223" s="9" t="s">
+      <c r="E223" s="8" t="s">
         <v>1168</v>
       </c>
-      <c r="F223" s="9" t="s">
+      <c r="F223" s="8" t="s">
         <v>1168</v>
       </c>
-      <c r="G223" s="9">
+      <c r="G223" s="8">
         <v>13</v>
       </c>
-      <c r="H223" s="10" t="s">
+      <c r="H223" s="9" t="s">
         <v>1169</v>
       </c>
-      <c r="I223" s="9" t="s">
+      <c r="I223" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="J223" s="9" t="s">
+      <c r="J223" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="K223" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L223" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M223" s="9"/>
-      <c r="N223" s="10" t="s">
+      <c r="K223" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L223" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M223" s="8"/>
+      <c r="N223" s="9" t="s">
         <v>1171</v>
       </c>
-      <c r="O223" s="9" t="s">
+      <c r="O223" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="P223" s="9" t="s">
+      <c r="P223" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="224" spans="1:16" ht="46.8">
-      <c r="A224" s="9" t="s">
+    <row r="224" spans="1:16" ht="48">
+      <c r="A224" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="B224" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="C224" s="9" t="s">
+      <c r="C224" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D224" s="9" t="s">
+      <c r="D224" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E224" s="9" t="s">
+      <c r="E224" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="F224" s="9" t="s">
+      <c r="F224" s="8" t="s">
         <v>1174</v>
       </c>
-      <c r="G224" s="9">
+      <c r="G224" s="8">
         <v>14</v>
       </c>
-      <c r="H224" s="10" t="s">
+      <c r="H224" s="9" t="s">
         <v>1175</v>
       </c>
-      <c r="I224" s="9" t="s">
+      <c r="I224" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="J224" s="9" t="s">
+      <c r="J224" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="K224" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L224" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M224" s="9"/>
-      <c r="N224" s="10" t="s">
+      <c r="K224" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L224" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M224" s="8"/>
+      <c r="N224" s="9" t="s">
         <v>1171</v>
       </c>
-      <c r="O224" s="9" t="s">
+      <c r="O224" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="P224" s="9" t="s">
+      <c r="P224" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="225" spans="1:16" ht="46.8">
-      <c r="A225" s="9" t="s">
+    <row r="225" spans="1:16" ht="48">
+      <c r="A225" s="8" t="s">
         <v>1177</v>
       </c>
-      <c r="B225" s="9" t="s">
+      <c r="B225" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="C225" s="9" t="s">
+      <c r="C225" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="D225" s="9" t="s">
+      <c r="D225" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="E225" s="9" t="s">
+      <c r="E225" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="F225" s="9" t="s">
+      <c r="F225" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="G225" s="9">
+      <c r="G225" s="8">
         <v>15</v>
       </c>
-      <c r="H225" s="10" t="s">
+      <c r="H225" s="9" t="s">
         <v>1179</v>
       </c>
-      <c r="I225" s="9" t="s">
+      <c r="I225" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="J225" s="9" t="s">
+      <c r="J225" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="K225" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L225" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M225" s="9"/>
-      <c r="N225" s="10" t="s">
+      <c r="K225" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="L225" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="M225" s="8"/>
+      <c r="N225" s="9" t="s">
         <v>1171</v>
       </c>
-      <c r="O225" s="9" t="s">
+      <c r="O225" s="8" t="s">
         <v>1180</v>
       </c>
-      <c r="P225" s="9" t="s">
+      <c r="P225" s="8" t="s">
         <v>1033</v>
       </c>
     </row>
@@ -15069,14 +15069,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37331E91-9932-4D38-A29A-1DD626050276}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="2" width="22.59765625" customWidth="1"/>
-    <col min="3" max="4" width="60.59765625" customWidth="1"/>
-    <col min="5" max="5" width="48.59765625" customWidth="1"/>
+    <col min="1" max="2" width="22.58203125" customWidth="1"/>
+    <col min="3" max="4" width="60.58203125" customWidth="1"/>
+    <col min="5" max="5" width="48.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+    <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>702</v>
       </c>
@@ -15093,7 +15093,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="46.8">
+    <row r="2" spans="1:5" ht="48">
       <c r="A2" s="1" t="s">
         <v>201</v>
       </c>
@@ -15110,7 +15110,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="62.4">
+    <row r="3" spans="1:5" ht="64">
       <c r="A3" s="1" t="s">
         <v>711</v>
       </c>
@@ -15127,7 +15127,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="46.8">
+    <row r="4" spans="1:5" ht="32">
       <c r="A4" s="1" t="s">
         <v>504</v>
       </c>
@@ -15144,7 +15144,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="31.2">
+    <row r="5" spans="1:5" ht="32">
       <c r="A5" s="1" t="s">
         <v>595</v>
       </c>
@@ -15161,7 +15161,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46.8">
+    <row r="6" spans="1:5" ht="32">
       <c r="A6" s="1" t="s">
         <v>724</v>
       </c>
@@ -15178,7 +15178,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="62.4">
+    <row r="7" spans="1:5" ht="64">
       <c r="A7" s="1" t="s">
         <v>729</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="32">
       <c r="A8" s="1" t="s">
         <v>142</v>
       </c>
@@ -15222,16 +15222,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FA1753-FFCC-443C-BCC8-01CEAAC52676}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
-    <col min="1" max="1" width="10.59765625" customWidth="1"/>
-    <col min="2" max="2" width="27.59765625" customWidth="1"/>
-    <col min="3" max="3" width="46.59765625" customWidth="1"/>
-    <col min="4" max="4" width="60.59765625" customWidth="1"/>
-    <col min="5" max="5" width="12.59765625" customWidth="1"/>
+    <col min="1" max="1" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="27.58203125" customWidth="1"/>
+    <col min="3" max="3" width="46.58203125" customWidth="1"/>
+    <col min="4" max="4" width="60.58203125" customWidth="1"/>
+    <col min="5" max="5" width="12.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1">
+    <row r="1" spans="1:5" ht="28" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>738</v>
       </c>
@@ -15248,7 +15248,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="109.2">
+    <row r="2" spans="1:5" ht="112">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -15265,7 +15265,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="31.2">
+    <row r="3" spans="1:5" ht="32">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -15282,7 +15282,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="31.2">
+    <row r="4" spans="1:5" ht="32">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -15299,7 +15299,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="46.8">
+    <row r="5" spans="1:5" ht="32">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -15316,7 +15316,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="31.2">
+    <row r="6" spans="1:5" ht="32">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -15350,7 +15350,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="31.2">
+    <row r="8" spans="1:5" ht="32">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46.8">
+    <row r="9" spans="1:5" ht="48">
       <c r="A9" s="1">
         <v>8</v>
       </c>

--- a/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
+++ b/outputs/mai-report-policy/식이/maiReport_식이_문구세트_의학검수_v1.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\이사라\Documents\Project_maiReport\outputs\mai-report-policy\식이\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AE80AF-A015-4802-B311-A32AB42086A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA06497-D0FB-46C2-8196-6FC49541E837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38290" yWindow="-810" windowWidth="38620" windowHeight="21100" xr2:uid="{E53919E9-E904-4308-8260-B4355B6CA0A6}"/>
   </bookViews>
@@ -7639,9 +7639,6 @@
     <t>해초샐러드로 저녁 채소를 가볍게 챙겨요. 소스는 절반만 뿌려요.</t>
   </si>
   <si>
-    <t>해조류 문구는 이전 검수에서 삭제 권고(N154) — 요오드 · 칼륨 이유. 쟁점 확인 전까지 신장질환 · 갑상선 질환 사용 주의</t>
-  </si>
-  <si>
     <t>2026-10-13 추가(검수표 226번). 사용자 · Claude 검수: 12자 · 금지 성격 · 상황 전제 · 과일 · 탄수화물 단독 · 나트륨 규칙 확인</t>
   </si>
   <si>
@@ -7671,6 +7668,10 @@
   </si>
   <si>
     <t>maiReport 식이 문구 세트 · 의학 검수 결과 · v1.1.0 · 2026-10-13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해조류 문구는 이전 검수에서 삭제 권고(N154) — 요오드 · 칼륨 이유. 쟁점 확인 전까지 신장질환 · 갑상선 질환 사용 주의 → 10-13 사용 확정(소스 1/2로 나트륨 부담 낮춤)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8243,7 +8244,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="18" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -8251,7 +8252,7 @@
     </row>
     <row r="2" spans="1:4" ht="112">
       <c r="A2" s="17" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -8286,7 +8287,7 @@
       </c>
       <c r="C5" s="1">
         <f>COUNTIF(검수결과!L:L,"승인")</f>
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>773</v>
@@ -8331,7 +8332,7 @@
       </c>
       <c r="C8" s="1">
         <f>COUNTIF(검수결과!L:L,"확인 필요")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>779</v>
@@ -30060,16 +30061,16 @@
         <v>1240</v>
       </c>
       <c r="L451" s="16" t="s">
-        <v>141</v>
+        <v>1180</v>
       </c>
       <c r="M451" s="16" t="s">
+        <v>2501</v>
+      </c>
+      <c r="N451" s="17" t="s">
         <v>2491</v>
       </c>
-      <c r="N451" s="17" t="s">
+      <c r="O451" s="16" t="s">
         <v>2492</v>
-      </c>
-      <c r="O451" s="16" t="s">
-        <v>2493</v>
       </c>
       <c r="P451" s="16" t="s">
         <v>1195</v>
@@ -30077,7 +30078,7 @@
     </row>
     <row r="452" spans="1:16" ht="32">
       <c r="A452" s="16" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B452" s="16" t="s">
         <v>1189</v>
@@ -30089,17 +30090,17 @@
         <v>17</v>
       </c>
       <c r="E452" s="16" t="s">
+        <v>2494</v>
+      </c>
+      <c r="F452" s="16" t="s">
         <v>2495</v>
-      </c>
-      <c r="F452" s="16" t="s">
-        <v>2496</v>
       </c>
       <c r="G452" s="16">
         <f t="shared" si="3"/>
         <v>11</v>
       </c>
       <c r="H452" s="17" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="I452" s="16" t="s">
         <v>207</v>
@@ -30115,10 +30116,10 @@
       </c>
       <c r="M452" s="16"/>
       <c r="N452" s="17" t="s">
+        <v>2497</v>
+      </c>
+      <c r="O452" s="16" t="s">
         <v>2498</v>
-      </c>
-      <c r="O452" s="16" t="s">
-        <v>2499</v>
       </c>
       <c r="P452" s="16" t="s">
         <v>1195</v>
